--- a/python/optimization_summary_slow_charging.xlsx
+++ b/python/optimization_summary_slow_charging.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="141">
   <si>
     <t>Charger 1</t>
   </si>
@@ -439,6 +439,9 @@
   </si>
   <si>
     <t>Bus 20</t>
+  </si>
+  <si>
+    <t>Bus 21</t>
   </si>
 </sst>
 </file>
@@ -896,7 +899,7 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -941,7 +944,7 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2">
         <v>0</v>
@@ -970,7 +973,7 @@
         <v>4</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -1012,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W3">
         <v>0</v>
@@ -1047,50 +1050,50 @@
         <v>4</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
         <v>2</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>1</v>
-      </c>
       <c r="V4">
         <v>0</v>
       </c>
@@ -1098,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4">
         <v>0</v>
@@ -1127,7 +1130,7 @@
         <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1166,10 +1169,10 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5">
         <v>0</v>
@@ -1246,13 +1249,13 @@
         <v>0</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6">
         <v>0</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6">
         <v>0</v>
@@ -1284,10 +1287,10 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>104.5</v>
+        <v>100</v>
       </c>
       <c r="C2">
-        <v>21.77083333333333</v>
+        <v>19.84126984126984</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1295,10 +1298,10 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>33.75</v>
+        <v>34</v>
       </c>
       <c r="C3">
-        <v>7.03125</v>
+        <v>6.746031746031746</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1306,10 +1309,10 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>341.75</v>
+        <v>370</v>
       </c>
       <c r="C4">
-        <v>71.19791666666667</v>
+        <v>73.4126984126984</v>
       </c>
     </row>
   </sheetData>
@@ -1338,10 +1341,10 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C2">
-        <v>28.125</v>
+        <v>28.33333333333333</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1349,10 +1352,10 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C3">
-        <v>71.875</v>
+        <v>71.66666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1378,7 +1381,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>5340</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1386,7 +1389,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>6780</v>
+        <v>7020</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1394,7 +1397,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>8220</v>
+        <v>8460</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1402,7 +1405,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>9660</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1410,7 +1413,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>11100</v>
+        <v>11340</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1418,7 +1421,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>12403.75891301304</v>
+        <v>12679.75891301304</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1426,7 +1429,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>13219.48159247707</v>
+        <v>13423.48159247707</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1434,7 +1437,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>12396.22615746515</v>
+        <v>12564.22615746522</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1442,7 +1445,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>11117.79775020185</v>
+        <v>11285.79775020202</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1450,7 +1453,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>10495.18168846827</v>
+        <v>10663.18168846838</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1458,7 +1461,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>10283.26834452723</v>
+        <v>10451.26834452735</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1466,7 +1469,7 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>10089.64616763462</v>
+        <v>10257.64616763476</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1474,7 +1477,7 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>9567.872343978415</v>
+        <v>9735.872343978559</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1482,7 +1485,7 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>8899.172674055033</v>
+        <v>9067.172674055173</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1490,7 +1493,7 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>8165.373241901958</v>
+        <v>8333.373241902102</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1498,7 +1501,7 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>7495.666561516601</v>
+        <v>7663.666561516754</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1506,7 +1509,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>6771.632627900689</v>
+        <v>6939.632627900834</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1514,7 +1517,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>6164.214792295261</v>
+        <v>6332.21479229541</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1522,7 +1525,7 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>5666.334638743661</v>
+        <v>5834.334638743836</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1530,7 +1533,7 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>5337.576543344397</v>
+        <v>5649.57654334459</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1538,7 +1541,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>5244.410692096139</v>
+        <v>5610.410692096326</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1546,7 +1549,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>5097.403926373467</v>
+        <v>5427.403926373658</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1554,7 +1557,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>4948.082199844096</v>
+        <v>5260.082199844289</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1562,7 +1565,7 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>4861.33285541882</v>
+        <v>5173.332855419012</v>
       </c>
     </row>
   </sheetData>
@@ -1588,7 +1591,7 @@
         <v>18</v>
       </c>
       <c r="B2">
-        <v>16400000</v>
+        <v>25200000</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1596,7 +1599,7 @@
         <v>19</v>
       </c>
       <c r="B3">
-        <v>1750000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1604,7 +1607,7 @@
         <v>20</v>
       </c>
       <c r="B4">
-        <v>1500000</v>
+        <v>350000</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1612,7 +1615,7 @@
         <v>21</v>
       </c>
       <c r="B5">
-        <v>867240.0000000002</v>
+        <v>875124.0000000002</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1628,7 +1631,7 @@
         <v>23</v>
       </c>
       <c r="B7">
-        <v>21101240</v>
+        <v>27909124</v>
       </c>
     </row>
   </sheetData>
@@ -1638,7 +1641,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CS21"/>
+  <dimension ref="A1:CS22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:97">
@@ -1948,280 +1951,280 @@
         <v>0.2</v>
       </c>
       <c r="F2">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="G2">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="H2">
         <v>0.26</v>
       </c>
       <c r="I2">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="J2">
         <v>0.32</v>
       </c>
       <c r="K2">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="L2">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="M2">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="N2">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="O2">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="P2">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="Q2">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="R2">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="S2">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="T2">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="U2">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="V2">
         <v>0.5</v>
       </c>
       <c r="W2">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="X2">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Y2">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="Z2">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="AA2">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="AB2">
-        <v>0.5600000000000001</v>
+        <v>0.6612973578033278</v>
       </c>
       <c r="AC2">
-        <v>0.5600000000000001</v>
+        <v>0.6425947156066555</v>
       </c>
       <c r="AD2">
-        <v>0.5413019258919243</v>
+        <v>0.6238920734099832</v>
       </c>
       <c r="AE2">
-        <v>0.5226038517838997</v>
+        <v>0.6051894312133108</v>
       </c>
       <c r="AF2">
-        <v>0.5039057776758751</v>
+        <v>0.5864867890166385</v>
       </c>
       <c r="AG2">
-        <v>0.4852077035678505</v>
+        <v>0.5652652729419982</v>
       </c>
       <c r="AH2">
-        <v>0.4852077035678505</v>
+        <v>0.544043756867358</v>
       </c>
       <c r="AI2">
-        <v>0.4669474271051228</v>
+        <v>0.5228222407927176</v>
       </c>
       <c r="AJ2">
-        <v>0.4486871506423951</v>
+        <v>0.5016007247180773</v>
       </c>
       <c r="AK2">
-        <v>0.4304268741796673</v>
+        <v>0.5016007247180773</v>
       </c>
       <c r="AL2">
-        <v>0.4121665977169396</v>
+        <v>0.5016007247180773</v>
       </c>
       <c r="AM2">
-        <v>0.3939063212542119</v>
+        <v>0.5016007247180773</v>
       </c>
       <c r="AN2">
-        <v>0.3939063212542119</v>
+        <v>0.5016007247180773</v>
       </c>
       <c r="AO2">
-        <v>0.3939063212542119</v>
+        <v>0.5016007247180773</v>
       </c>
       <c r="AP2">
-        <v>0.3939063212542119</v>
+        <v>0.5016007247180773</v>
       </c>
       <c r="AQ2">
-        <v>0.3939063212542119</v>
+        <v>0.5016007247180773</v>
       </c>
       <c r="AR2">
-        <v>0.3939063212542119</v>
+        <v>0.5016007247180773</v>
       </c>
       <c r="AS2">
-        <v>0.3939063212542119</v>
+        <v>0.5016007247180773</v>
       </c>
       <c r="AT2">
-        <v>0.3893896687823258</v>
+        <v>0.5016007247180773</v>
       </c>
       <c r="AU2">
-        <v>0.3848730163104397</v>
+        <v>0.5016007247180773</v>
       </c>
       <c r="AV2">
-        <v>0.3803563638385536</v>
+        <v>0.4744281462254267</v>
       </c>
       <c r="AW2">
-        <v>0.3758397113666675</v>
+        <v>0.4472555677327762</v>
       </c>
       <c r="AX2">
-        <v>0.3713230588947814</v>
+        <v>0.4200829892401257</v>
       </c>
       <c r="AY2">
-        <v>0.3713230588947814</v>
+        <v>0.4200829892401257</v>
       </c>
       <c r="AZ2">
-        <v>0.3713230588947814</v>
+        <v>0.3973470339677133</v>
       </c>
       <c r="BA2">
-        <v>0.3713230588947814</v>
+        <v>0.374611078695301</v>
       </c>
       <c r="BB2">
-        <v>0.3713230588948039</v>
+        <v>0.374611078695301</v>
       </c>
       <c r="BC2">
-        <v>0.3713230588948039</v>
+        <v>0.374611078695301</v>
       </c>
       <c r="BD2">
-        <v>0.3713230588948039</v>
+        <v>0.343704507136839</v>
       </c>
       <c r="BE2">
-        <v>0.3713230588948039</v>
+        <v>0.343704507136839</v>
       </c>
       <c r="BF2">
-        <v>0.3713230588948039</v>
+        <v>0.3203556284675187</v>
       </c>
       <c r="BG2">
-        <v>0.3713230588948039</v>
+        <v>0.2970067497981985</v>
       </c>
       <c r="BH2">
-        <v>0.3713230588948039</v>
+        <v>0.2970067497981985</v>
       </c>
       <c r="BI2">
-        <v>0.3713230588948039</v>
+        <v>0.2970067497981985</v>
       </c>
       <c r="BJ2">
-        <v>0.3510571743139231</v>
+        <v>0.2970067497981985</v>
       </c>
       <c r="BK2">
-        <v>0.3307912897330423</v>
+        <v>0.2970067497981985</v>
       </c>
       <c r="BL2">
-        <v>0.3307912897330423</v>
+        <v>0.2970067497981985</v>
       </c>
       <c r="BM2">
-        <v>0.3307912897330423</v>
+        <v>0.2970067497981985</v>
       </c>
       <c r="BN2">
-        <v>0.3307912897330424</v>
+        <v>0.2970067497981985</v>
       </c>
       <c r="BO2">
-        <v>0.3178866260540808</v>
+        <v>0.2970067497981985</v>
       </c>
       <c r="BP2">
-        <v>0.3049819623751192</v>
+        <v>0.2970067497981985</v>
       </c>
       <c r="BQ2">
-        <v>0.2920772986961576</v>
+        <v>0.2970067497981985</v>
       </c>
       <c r="BR2">
-        <v>0.2920772986961576</v>
+        <v>0.2743359004041396</v>
       </c>
       <c r="BS2">
-        <v>0.2920772986961576</v>
+        <v>0.2516650510100815</v>
       </c>
       <c r="BT2">
-        <v>0.2920772986961576</v>
+        <v>0.2516650510100815</v>
       </c>
       <c r="BU2">
-        <v>0.2920772986961576</v>
+        <v>0.2516650510100815</v>
       </c>
       <c r="BV2">
-        <v>0.2920772986961576</v>
+        <v>0.2516650510100815</v>
       </c>
       <c r="BW2">
-        <v>0.2920772986961576</v>
+        <v>0.2306101602092255</v>
       </c>
       <c r="BX2">
-        <v>0.2920772986961576</v>
+        <v>0.2095552694083694</v>
       </c>
       <c r="BY2">
-        <v>0.2920772986961576</v>
+        <v>0.2095552694083694</v>
       </c>
       <c r="BZ2">
-        <v>0.2920772986961576</v>
+        <v>0.2095552694083694</v>
       </c>
       <c r="CA2">
-        <v>0.2920772986961576</v>
+        <v>0.2695552694083694</v>
       </c>
       <c r="CB2">
-        <v>0.2920772986961576</v>
+        <v>0.2395126429610256</v>
       </c>
       <c r="CC2">
-        <v>0.2697549364179709</v>
+        <v>0.2094700165136817</v>
       </c>
       <c r="CD2">
-        <v>0.2474325741397844</v>
+        <v>0.2094700165136817</v>
       </c>
       <c r="CE2">
-        <v>0.2249728035812434</v>
+        <v>0.2694700165136813</v>
       </c>
       <c r="CF2">
-        <v>0.2025130330227024</v>
+        <v>0.2694700165136813</v>
       </c>
       <c r="CG2">
-        <v>0.2025130330227024</v>
+        <v>0.2694700165136813</v>
       </c>
       <c r="CH2">
-        <v>0.2025130330227024</v>
+        <v>0.2694700165136813</v>
       </c>
       <c r="CI2">
-        <v>0.2625130330227024</v>
+        <v>0.2694700165136813</v>
       </c>
       <c r="CJ2">
-        <v>0.2314056435999366</v>
+        <v>0.2694700165136813</v>
       </c>
       <c r="CK2">
-        <v>0.2002982541771707</v>
+        <v>0.2694700165136813</v>
       </c>
       <c r="CL2">
-        <v>0.2002982541771707</v>
+        <v>0.2694700165136813</v>
       </c>
       <c r="CM2">
-        <v>0.2002982541771707</v>
+        <v>0.2694700165136813</v>
       </c>
       <c r="CN2">
-        <v>0.2002982541771707</v>
+        <v>0.2365274489466466</v>
       </c>
       <c r="CO2">
-        <v>0.2002982541771707</v>
+        <v>0.2035848813796119</v>
       </c>
       <c r="CP2">
-        <v>0.2002982541771707</v>
+        <v>0.2035848813796119</v>
       </c>
       <c r="CQ2">
-        <v>0.2002982541771707</v>
+        <v>0.2035848813796119</v>
       </c>
       <c r="CR2">
-        <v>0.2002982541771707</v>
+        <v>0.2035848813796119</v>
       </c>
       <c r="CS2">
-        <v>0.2002982541771707</v>
+        <v>0.2035848813796119</v>
       </c>
     </row>
     <row r="3" spans="1:97">
@@ -2250,34 +2253,34 @@
         <v>0.26</v>
       </c>
       <c r="I3">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="J3">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="K3">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="L3">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="M3">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="N3">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="O3">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="P3">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="Q3">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="R3">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="S3">
         <v>0.44</v>
@@ -2289,10 +2292,10 @@
         <v>0.44</v>
       </c>
       <c r="V3">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="W3">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="X3">
         <v>0.5</v>
@@ -2304,217 +2307,217 @@
         <v>0.5</v>
       </c>
       <c r="AA3">
+        <v>0.5</v>
+      </c>
+      <c r="AB3">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AB3">
-        <v>0.5387768192193378</v>
-      </c>
       <c r="AC3">
-        <v>0.5175536384386756</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AD3">
-        <v>0.4963304576580135</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AE3">
-        <v>0.4963304576580135</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AF3">
-        <v>0.4780627762534735</v>
+        <v>0.5442138247966215</v>
       </c>
       <c r="AG3">
-        <v>0.4597950948489335</v>
+        <v>0.5284276495932435</v>
       </c>
       <c r="AH3">
-        <v>0.4597950948489335</v>
+        <v>0.5126414743898655</v>
       </c>
       <c r="AI3">
-        <v>0.4597950948489335</v>
+        <v>0.4968552991864876</v>
       </c>
       <c r="AJ3">
-        <v>0.4597950948489335</v>
+        <v>0.4810691239831095</v>
       </c>
       <c r="AK3">
-        <v>0.4597950948489335</v>
+        <v>0.4652829487797316</v>
       </c>
       <c r="AL3">
-        <v>0.4410283028990094</v>
+        <v>0.4652829487797316</v>
       </c>
       <c r="AM3">
-        <v>0.4222615109490851</v>
+        <v>0.4652829487797305</v>
       </c>
       <c r="AN3">
-        <v>0.4034947189991609</v>
+        <v>0.4652829487797305</v>
       </c>
       <c r="AO3">
-        <v>0.3847279270492367</v>
+        <v>0.4652829487797305</v>
       </c>
       <c r="AP3">
-        <v>0.3847279270492367</v>
+        <v>0.4652829487797305</v>
       </c>
       <c r="AQ3">
-        <v>0.3847279270492367</v>
+        <v>0.4652829487797305</v>
       </c>
       <c r="AR3">
-        <v>0.3847279270492367</v>
+        <v>0.4652829487797305</v>
       </c>
       <c r="AS3">
-        <v>0.3847279270492367</v>
+        <v>0.4652829487797305</v>
       </c>
       <c r="AT3">
-        <v>0.3847279270492367</v>
+        <v>0.4652829487797305</v>
       </c>
       <c r="AU3">
-        <v>0.3847279270492367</v>
+        <v>0.4619020869243086</v>
       </c>
       <c r="AV3">
-        <v>0.3847279270492367</v>
+        <v>0.4585212250688867</v>
       </c>
       <c r="AW3">
-        <v>0.3847279270492367</v>
+        <v>0.4551403632134648</v>
       </c>
       <c r="AX3">
-        <v>0.3610944330687617</v>
+        <v>0.4517595013580429</v>
       </c>
       <c r="AY3">
-        <v>0.3374609390882867</v>
+        <v>0.448378639502621</v>
       </c>
       <c r="AZ3">
-        <v>0.3374609390882867</v>
+        <v>0.4449977776471991</v>
       </c>
       <c r="BA3">
-        <v>0.3374609390882867</v>
+        <v>0.4416169157917772</v>
       </c>
       <c r="BB3">
-        <v>0.31104392171128</v>
+        <v>0.4416169157917772</v>
       </c>
       <c r="BC3">
-        <v>0.31104392171128</v>
+        <v>0.4178067422722279</v>
       </c>
       <c r="BD3">
-        <v>0.3110439217112788</v>
+        <v>0.3939965687526785</v>
       </c>
       <c r="BE3">
-        <v>0.287289948963193</v>
+        <v>0.3939965687526785</v>
       </c>
       <c r="BF3">
-        <v>0.2635359762151073</v>
+        <v>0.3939965687526797</v>
       </c>
       <c r="BG3">
-        <v>0.2635359762151073</v>
+        <v>0.3939965687526809</v>
       </c>
       <c r="BH3">
-        <v>0.2635359762151048</v>
+        <v>0.3939965687526809</v>
       </c>
       <c r="BI3">
-        <v>0.2635359762151048</v>
+        <v>0.3939965687526809</v>
       </c>
       <c r="BJ3">
-        <v>0.2635359762151048</v>
+        <v>0.3737306841718001</v>
       </c>
       <c r="BK3">
-        <v>0.2635359762151048</v>
+        <v>0.3534647995909193</v>
       </c>
       <c r="BL3">
-        <v>0.2635359762151048</v>
+        <v>0.3534647995909193</v>
       </c>
       <c r="BM3">
-        <v>0.2635359762151048</v>
+        <v>0.3534647995909193</v>
       </c>
       <c r="BN3">
-        <v>0.2635359762151048</v>
+        <v>0.3534647995909193</v>
       </c>
       <c r="BO3">
-        <v>0.2635359762151048</v>
+        <v>0.3534647995909193</v>
       </c>
       <c r="BP3">
-        <v>0.2407338555502002</v>
+        <v>0.3534647995909193</v>
       </c>
       <c r="BQ3">
-        <v>0.2179317348852957</v>
+        <v>0.3174346334338564</v>
       </c>
       <c r="BR3">
-        <v>0.2179317348852957</v>
+        <v>0.2814044672767934</v>
       </c>
       <c r="BS3">
-        <v>0.2179317348852957</v>
+        <v>0.2814044672767934</v>
       </c>
       <c r="BT3">
-        <v>0.2179317348853078</v>
+        <v>0.2814044672767934</v>
       </c>
       <c r="BU3">
-        <v>0.2179317348853078</v>
+        <v>0.2607988834852993</v>
       </c>
       <c r="BV3">
-        <v>0.2179317348853078</v>
+        <v>0.2607988834852993</v>
       </c>
       <c r="BW3">
-        <v>0.2179317348853078</v>
+        <v>0.2607988834852993</v>
       </c>
       <c r="BX3">
-        <v>0.2179317348853078</v>
+        <v>0.2607988834852993</v>
       </c>
       <c r="BY3">
-        <v>0.2179317348853078</v>
+        <v>0.2607988834852993</v>
       </c>
       <c r="BZ3">
-        <v>0.2179317348853078</v>
+        <v>0.2607988834852993</v>
       </c>
       <c r="CA3">
-        <v>0.2179317348853078</v>
+        <v>0.2330282371969012</v>
       </c>
       <c r="CB3">
-        <v>0.2179317348853078</v>
+        <v>0.2930282371969011</v>
       </c>
       <c r="CC3">
-        <v>0.2179317348853078</v>
+        <v>0.2707058749187146</v>
       </c>
       <c r="CD3">
-        <v>0.2179317348853078</v>
+        <v>0.2483835126405279</v>
       </c>
       <c r="CE3">
-        <v>0.2179317348853078</v>
+        <v>0.2259237420819774</v>
       </c>
       <c r="CF3">
-        <v>0.2179317348853078</v>
+        <v>0.203463971523427</v>
       </c>
       <c r="CG3">
-        <v>0.2179317348853078</v>
+        <v>0.203463971523427</v>
       </c>
       <c r="CH3">
-        <v>0.2179317348853078</v>
+        <v>0.203463971523427</v>
       </c>
       <c r="CI3">
-        <v>0.2179317348853078</v>
+        <v>0.203463971523427</v>
       </c>
       <c r="CJ3">
-        <v>0.2179317348853078</v>
+        <v>0.203463971523427</v>
       </c>
       <c r="CK3">
-        <v>0.2179317348853078</v>
+        <v>0.203463971523427</v>
       </c>
       <c r="CL3">
-        <v>0.2152115140437559</v>
+        <v>0.203463971523427</v>
       </c>
       <c r="CM3">
-        <v>0.2124912932022039</v>
+        <v>0.203463971523427</v>
       </c>
       <c r="CN3">
-        <v>0.2124912932022039</v>
+        <v>0.203463971523427</v>
       </c>
       <c r="CO3">
-        <v>0.2124912932022039</v>
+        <v>0.203463971523427</v>
       </c>
       <c r="CP3">
-        <v>0.2124912932022039</v>
+        <v>0.203463971523427</v>
       </c>
       <c r="CQ3">
-        <v>0.2124912932022039</v>
+        <v>0.203463971523427</v>
       </c>
       <c r="CR3">
-        <v>0.2124912932022039</v>
+        <v>0.203463971523427</v>
       </c>
       <c r="CS3">
-        <v>0.2124912932022039</v>
+        <v>0.203463971523427</v>
       </c>
     </row>
     <row r="4" spans="1:97">
@@ -2534,37 +2537,37 @@
         <v>0.26</v>
       </c>
       <c r="F4">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="G4">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="H4">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="I4">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="J4">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="K4">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="L4">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="M4">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="N4">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="O4">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="P4">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="Q4">
         <v>0.5</v>
@@ -2591,223 +2594,223 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="Y4">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="Z4">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AA4">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB4">
         <v>0.62</v>
       </c>
-      <c r="Z4">
-        <v>0.62</v>
-      </c>
-      <c r="AA4">
-        <v>0.62</v>
-      </c>
-      <c r="AB4">
-        <v>0.6012973578033145</v>
-      </c>
       <c r="AC4">
-        <v>0.5825947156066376</v>
+        <v>0.6104333071067526</v>
       </c>
       <c r="AD4">
-        <v>0.5638920734099607</v>
+        <v>0.6008666142135062</v>
       </c>
       <c r="AE4">
-        <v>0.545189431213283</v>
+        <v>0.59129992132026</v>
       </c>
       <c r="AF4">
-        <v>0.5264867890166027</v>
+        <v>0.5817332284270137</v>
       </c>
       <c r="AG4">
-        <v>0.5264867890166027</v>
+        <v>0.5721665355337674</v>
       </c>
       <c r="AH4">
-        <v>0.5069817921795178</v>
+        <v>0.562599842640521</v>
       </c>
       <c r="AI4">
-        <v>0.4874767953424328</v>
+        <v>0.5530331497472747</v>
       </c>
       <c r="AJ4">
-        <v>0.4679717985053478</v>
+        <v>0.5249456792370554</v>
       </c>
       <c r="AK4">
-        <v>0.4484668016682627</v>
+        <v>0.496858208726836</v>
       </c>
       <c r="AL4">
-        <v>0.4484668016682398</v>
+        <v>0.4687707382166167</v>
       </c>
       <c r="AM4">
-        <v>0.4484668016682398</v>
+        <v>0.4687707382166167</v>
       </c>
       <c r="AN4">
-        <v>0.4484668016682398</v>
+        <v>0.4687707382166167</v>
       </c>
       <c r="AO4">
-        <v>0.4484668016682398</v>
+        <v>0.4687707382166167</v>
       </c>
       <c r="AP4">
-        <v>0.4484668016682319</v>
+        <v>0.4687707382166167</v>
       </c>
       <c r="AQ4">
-        <v>0.4484668016682301</v>
+        <v>0.4687707382166167</v>
       </c>
       <c r="AR4">
-        <v>0.4484668016682283</v>
+        <v>0.4687707382166167</v>
       </c>
       <c r="AS4">
-        <v>0.4484668016682257</v>
+        <v>0.4687707382166167</v>
       </c>
       <c r="AT4">
-        <v>0.4484668016682228</v>
+        <v>0.4687707382166167</v>
       </c>
       <c r="AU4">
-        <v>0.4484668016682191</v>
+        <v>0.4687707382166167</v>
       </c>
       <c r="AV4">
-        <v>0.4484668016682208</v>
+        <v>0.4687707382166167</v>
       </c>
       <c r="AW4">
-        <v>0.4484668016682208</v>
+        <v>0.4687707382166167</v>
       </c>
       <c r="AX4">
-        <v>0.4484668016682208</v>
+        <v>0.4451372442361417</v>
       </c>
       <c r="AY4">
-        <v>0.4484668016682208</v>
+        <v>0.4215037502556667</v>
       </c>
       <c r="AZ4">
-        <v>0.4205081347189896</v>
+        <v>0.4215037502556667</v>
       </c>
       <c r="BA4">
-        <v>0.3925494677697585</v>
+        <v>0.3858862326048152</v>
       </c>
       <c r="BB4">
-        <v>0.3645908008205272</v>
+        <v>0.3502687149539637</v>
       </c>
       <c r="BC4">
-        <v>0.3645908008205272</v>
+        <v>0.3502687149539637</v>
       </c>
       <c r="BD4">
-        <v>0.3645908008205272</v>
+        <v>0.3502687149539637</v>
       </c>
       <c r="BE4">
-        <v>0.3645908008205272</v>
+        <v>0.3133335114593242</v>
       </c>
       <c r="BF4">
-        <v>0.3290224065472402</v>
+        <v>0.2763983079646846</v>
       </c>
       <c r="BG4">
-        <v>0.3290224065472402</v>
+        <v>0.2763983079646846</v>
       </c>
       <c r="BH4">
-        <v>0.3290224065472402</v>
+        <v>0.2763983079646846</v>
       </c>
       <c r="BI4">
-        <v>0.3290224065472402</v>
+        <v>0.2763983079646846</v>
       </c>
       <c r="BJ4">
-        <v>0.3290224065472402</v>
+        <v>0.2763983079646846</v>
       </c>
       <c r="BK4">
-        <v>0.3290224065472402</v>
+        <v>0.2763983079646846</v>
       </c>
       <c r="BL4">
-        <v>0.3290224065472402</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="BM4">
-        <v>0.3150380175592891</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="BN4">
-        <v>0.3010536285713381</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="BO4">
-        <v>0.2870692395833871</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="BP4">
-        <v>0.287069239583387</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="BQ4">
-        <v>0.287069239583387</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="BR4">
-        <v>0.287069239583387</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="BS4">
-        <v>0.287069239583387</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="BT4">
-        <v>0.2592952652101174</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="BU4">
-        <v>0.2315212908368478</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="BV4">
-        <v>0.2037473164635781</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="BW4">
-        <v>0.2037473164635781</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="BX4">
-        <v>0.2037473164635781</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="BY4">
-        <v>0.2037473164635781</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="BZ4">
-        <v>0.2037473164635781</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="CA4">
-        <v>0.2037473164635781</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="CB4">
-        <v>0.2037473164635781</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="CC4">
-        <v>0.2037473164635781</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="CD4">
-        <v>0.2037473164635781</v>
+        <v>0.2065442574288248</v>
       </c>
       <c r="CE4">
-        <v>0.2037473164635781</v>
+        <v>0.2665442574288248</v>
       </c>
       <c r="CF4">
-        <v>0.2037473164635781</v>
+        <v>0.2337679312967763</v>
       </c>
       <c r="CG4">
-        <v>0.2037473164635781</v>
+        <v>0.2009916051647277</v>
       </c>
       <c r="CH4">
-        <v>0.2037473164635781</v>
+        <v>0.2009916051647277</v>
       </c>
       <c r="CI4">
-        <v>0.2037473164635781</v>
+        <v>0.2009916051647277</v>
       </c>
       <c r="CJ4">
-        <v>0.2037473164635781</v>
+        <v>0.2009916051647277</v>
       </c>
       <c r="CK4">
-        <v>0.2037473164635781</v>
+        <v>0.2009916051647277</v>
       </c>
       <c r="CL4">
-        <v>0.2037473164635781</v>
+        <v>0.2009916051647277</v>
       </c>
       <c r="CM4">
-        <v>0.2037473164635781</v>
+        <v>0.2009916051647277</v>
       </c>
       <c r="CN4">
-        <v>0.2037473164635781</v>
+        <v>0.2009916051647277</v>
       </c>
       <c r="CO4">
-        <v>0.2037473164635781</v>
+        <v>0.2009916051647277</v>
       </c>
       <c r="CP4">
-        <v>0.2037473164635781</v>
+        <v>0.2009916051647277</v>
       </c>
       <c r="CQ4">
-        <v>0.2037473164635781</v>
+        <v>0.2009916051647277</v>
       </c>
       <c r="CR4">
-        <v>0.2037473164635781</v>
+        <v>0.2009916051647277</v>
       </c>
       <c r="CS4">
-        <v>0.2037473164635781</v>
+        <v>0.2009916051647277</v>
       </c>
     </row>
     <row r="5" spans="1:97">
@@ -2818,25 +2821,25 @@
         <v>0.2</v>
       </c>
       <c r="C5">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="D5">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="E5">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="F5">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="G5">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="H5">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="I5">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="J5">
         <v>0.38</v>
@@ -2848,10 +2851,10 @@
         <v>0.38</v>
       </c>
       <c r="M5">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="N5">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="O5">
         <v>0.44</v>
@@ -2863,244 +2866,244 @@
         <v>0.44</v>
       </c>
       <c r="R5">
+        <v>0.44</v>
+      </c>
+      <c r="S5">
+        <v>0.44</v>
+      </c>
+      <c r="T5">
+        <v>0.44</v>
+      </c>
+      <c r="U5">
+        <v>0.44</v>
+      </c>
+      <c r="V5">
+        <v>0.44</v>
+      </c>
+      <c r="W5">
+        <v>0.44</v>
+      </c>
+      <c r="X5">
+        <v>0.44</v>
+      </c>
+      <c r="Y5">
+        <v>0.44</v>
+      </c>
+      <c r="Z5">
         <v>0.5</v>
       </c>
-      <c r="S5">
-        <v>0.5</v>
-      </c>
-      <c r="T5">
-        <v>0.5</v>
-      </c>
-      <c r="U5">
-        <v>0.5</v>
-      </c>
-      <c r="V5">
-        <v>0.5</v>
-      </c>
-      <c r="W5">
-        <v>0.5</v>
-      </c>
-      <c r="X5">
-        <v>0.5</v>
-      </c>
-      <c r="Y5">
-        <v>0.5</v>
-      </c>
-      <c r="Z5">
+      <c r="AA5">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AA5">
-        <v>0.5405900293249397</v>
-      </c>
       <c r="AB5">
-        <v>0.5211800586498884</v>
+        <v>0.5375288550706145</v>
       </c>
       <c r="AC5">
-        <v>0.5017700879748371</v>
+        <v>0.5150577101412291</v>
       </c>
       <c r="AD5">
-        <v>0.4823601172997858</v>
+        <v>0.4925865652118436</v>
       </c>
       <c r="AE5">
-        <v>0.4629501466247346</v>
+        <v>0.4925865652118436</v>
       </c>
       <c r="AF5">
-        <v>0.4469067161737303</v>
+        <v>0.4743188838073036</v>
       </c>
       <c r="AG5">
-        <v>0.4308632857227263</v>
+        <v>0.4560512024027638</v>
       </c>
       <c r="AH5">
-        <v>0.414819855271722</v>
+        <v>0.4560512024027638</v>
       </c>
       <c r="AI5">
-        <v>0.3987764248207179</v>
+        <v>0.4560512024027638</v>
       </c>
       <c r="AJ5">
-        <v>0.3827329943697137</v>
+        <v>0.4560512024027638</v>
       </c>
       <c r="AK5">
-        <v>0.3827329943697137</v>
+        <v>0.4560512024027638</v>
       </c>
       <c r="AL5">
-        <v>0.3827329943697137</v>
+        <v>0.4560512024027638</v>
       </c>
       <c r="AM5">
-        <v>0.3827329943697137</v>
+        <v>0.4560512024027638</v>
       </c>
       <c r="AN5">
-        <v>0.3827329943697126</v>
+        <v>0.4560512024027638</v>
       </c>
       <c r="AO5">
-        <v>0.3827329943697126</v>
+        <v>0.4560512024027638</v>
       </c>
       <c r="AP5">
-        <v>0.3827329943697126</v>
+        <v>0.4560512024027633</v>
       </c>
       <c r="AQ5">
-        <v>0.3827329943697126</v>
+        <v>0.4560512024027633</v>
       </c>
       <c r="AR5">
-        <v>0.3827329943697126</v>
+        <v>0.4560512024027633</v>
       </c>
       <c r="AS5">
-        <v>0.3827329943697126</v>
+        <v>0.4511018577276827</v>
       </c>
       <c r="AT5">
-        <v>0.3827329943697126</v>
+        <v>0.4461525130526022</v>
       </c>
       <c r="AU5">
-        <v>0.3827329943697126</v>
+        <v>0.4412031683775216</v>
       </c>
       <c r="AV5">
-        <v>0.3827329943697137</v>
+        <v>0.4362538237024411</v>
       </c>
       <c r="AW5">
-        <v>0.3827329943697149</v>
+        <v>0.4313044790273605</v>
       </c>
       <c r="AX5">
-        <v>0.3827329943697163</v>
+        <v>0.4022553678161501</v>
       </c>
       <c r="AY5">
-        <v>0.3827329943697163</v>
+        <v>0.3732062566049397</v>
       </c>
       <c r="AZ5">
-        <v>0.3599970390973039</v>
+        <v>0.3732062566049397</v>
       </c>
       <c r="BA5">
-        <v>0.3372610838248916</v>
+        <v>0.3732062566049397</v>
       </c>
       <c r="BB5">
-        <v>0.3372610838248932</v>
+        <v>0.3732062566049397</v>
       </c>
       <c r="BC5">
-        <v>0.3372610838248932</v>
+        <v>0.3732062566049397</v>
       </c>
       <c r="BD5">
-        <v>0.3372610838248951</v>
+        <v>0.3406133239927991</v>
       </c>
       <c r="BE5">
-        <v>0.3372610838248969</v>
+        <v>0.3080203913806587</v>
       </c>
       <c r="BF5">
-        <v>0.3071406737292986</v>
+        <v>0.2754274587685182</v>
       </c>
       <c r="BG5">
-        <v>0.2770202636337003</v>
+        <v>0.2754274587685182</v>
       </c>
       <c r="BH5">
-        <v>0.2770202636337019</v>
+        <v>0.2754274587685182</v>
       </c>
       <c r="BI5">
-        <v>0.2770202636337019</v>
+        <v>0.2754274587685182</v>
       </c>
       <c r="BJ5">
-        <v>0.2770202636337019</v>
+        <v>0.2754274587685182</v>
       </c>
       <c r="BK5">
-        <v>0.2770202636337019</v>
+        <v>0.2754274587685182</v>
       </c>
       <c r="BL5">
-        <v>0.2770202636337019</v>
+        <v>0.2754274587685182</v>
       </c>
       <c r="BM5">
-        <v>0.2770202636337032</v>
+        <v>0.2754274587685182</v>
       </c>
       <c r="BN5">
-        <v>0.2770202636337064</v>
+        <v>0.2754274587685182</v>
       </c>
       <c r="BO5">
-        <v>0.2770202636337097</v>
+        <v>0.2754274587685182</v>
       </c>
       <c r="BP5">
-        <v>0.2770202636337118</v>
+        <v>0.2380553944404421</v>
       </c>
       <c r="BQ5">
-        <v>0.2770202636337141</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="BR5">
-        <v>0.2770202636337162</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="BS5">
-        <v>0.2770202636337162</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="BT5">
-        <v>0.2770202636337185</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="BU5">
-        <v>0.2770202636336913</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="BV5">
-        <v>0.2770202636336913</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="BW5">
-        <v>0.2512893783902551</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="BX5">
-        <v>0.2512893783902551</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="BY5">
-        <v>0.2302423629769222</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="BZ5">
-        <v>0.2091953475635892</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="CA5">
-        <v>0.2091953475635797</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="CB5">
-        <v>0.2091953475635797</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="CC5">
-        <v>0.2091953475635797</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="CD5">
-        <v>0.2691953475635797</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="CE5">
-        <v>0.2691953475635797</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="CF5">
-        <v>0.2691953475635702</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="CG5">
-        <v>0.2450427720116457</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="CH5">
-        <v>0.2450427720116457</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="CI5">
-        <v>0.2450427720116457</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="CJ5">
-        <v>0.2450427720116457</v>
+        <v>0.2006833301123661</v>
       </c>
       <c r="CK5">
-        <v>0.2227193404769886</v>
+        <v>0.2006833301123665</v>
       </c>
       <c r="CL5">
-        <v>0.2003959089423316</v>
+        <v>0.2006833301123665</v>
       </c>
       <c r="CM5">
-        <v>0.2003959089423316</v>
+        <v>0.2006833301123665</v>
       </c>
       <c r="CN5">
-        <v>0.2003959089423316</v>
+        <v>0.2006833301123665</v>
       </c>
       <c r="CO5">
-        <v>0.2003959089423316</v>
+        <v>0.2006833301123665</v>
       </c>
       <c r="CP5">
-        <v>0.2003959089423316</v>
+        <v>0.2006833301123665</v>
       </c>
       <c r="CQ5">
-        <v>0.2003959089423316</v>
+        <v>0.2006833301123665</v>
       </c>
       <c r="CR5">
-        <v>0.2003959089423316</v>
+        <v>0.2006833301123665</v>
       </c>
       <c r="CS5">
-        <v>0.2003959089423316</v>
+        <v>0.2006833301123665</v>
       </c>
     </row>
     <row r="6" spans="1:97">
@@ -3114,61 +3117,61 @@
         <v>0.2</v>
       </c>
       <c r="D6">
+        <v>0.2</v>
+      </c>
+      <c r="E6">
+        <v>0.2</v>
+      </c>
+      <c r="F6">
+        <v>0.2</v>
+      </c>
+      <c r="G6">
+        <v>0.2</v>
+      </c>
+      <c r="H6">
+        <v>0.2</v>
+      </c>
+      <c r="I6">
+        <v>0.2</v>
+      </c>
+      <c r="J6">
+        <v>0.2</v>
+      </c>
+      <c r="K6">
         <v>0.26</v>
       </c>
-      <c r="E6">
+      <c r="L6">
         <v>0.32</v>
       </c>
-      <c r="F6">
-        <v>0.38</v>
-      </c>
-      <c r="G6">
-        <v>0.44</v>
-      </c>
-      <c r="H6">
-        <v>0.44</v>
-      </c>
-      <c r="I6">
-        <v>0.44</v>
-      </c>
-      <c r="J6">
-        <v>0.44</v>
-      </c>
-      <c r="K6">
-        <v>0.44</v>
-      </c>
-      <c r="L6">
+      <c r="M6">
+        <v>0.32</v>
+      </c>
+      <c r="N6">
+        <v>0.32</v>
+      </c>
+      <c r="O6">
+        <v>0.38</v>
+      </c>
+      <c r="P6">
+        <v>0.38</v>
+      </c>
+      <c r="Q6">
+        <v>0.38</v>
+      </c>
+      <c r="R6">
+        <v>0.38</v>
+      </c>
+      <c r="S6">
+        <v>0.38</v>
+      </c>
+      <c r="T6">
+        <v>0.44</v>
+      </c>
+      <c r="U6">
         <v>0.5</v>
       </c>
-      <c r="M6">
+      <c r="V6">
         <v>0.5</v>
-      </c>
-      <c r="N6">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="O6">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="P6">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="Q6">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="R6">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="S6">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="T6">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="U6">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="V6">
-        <v>0.5600000000000001</v>
       </c>
       <c r="W6">
         <v>0.5600000000000001</v>
@@ -3186,214 +3189,214 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AB6">
-        <v>0.62</v>
+        <v>0.5387768192193318</v>
       </c>
       <c r="AC6">
-        <v>0.5997814211239508</v>
+        <v>0.5175536384386697</v>
       </c>
       <c r="AD6">
-        <v>0.579562842247902</v>
+        <v>0.4963304576580075</v>
       </c>
       <c r="AE6">
-        <v>0.5593442633718533</v>
+        <v>0.4963304576580075</v>
       </c>
       <c r="AF6">
-        <v>0.5358242819781803</v>
+        <v>0.4782130915599899</v>
       </c>
       <c r="AG6">
-        <v>0.5123043005845075</v>
+        <v>0.4600957254619721</v>
       </c>
       <c r="AH6">
-        <v>0.4887843191908345</v>
+        <v>0.4419783593639544</v>
       </c>
       <c r="AI6">
-        <v>0.4887843191908345</v>
+        <v>0.4419783593639544</v>
       </c>
       <c r="AJ6">
-        <v>0.4606968486806152</v>
+        <v>0.4419783593639544</v>
       </c>
       <c r="AK6">
-        <v>0.4326093781703959</v>
+        <v>0.4419783593639544</v>
       </c>
       <c r="AL6">
-        <v>0.4045219076601765</v>
+        <v>0.4419783593639544</v>
       </c>
       <c r="AM6">
-        <v>0.4045219076601765</v>
+        <v>0.4419783593639544</v>
       </c>
       <c r="AN6">
-        <v>0.4045219076601765</v>
+        <v>0.4419783593639544</v>
       </c>
       <c r="AO6">
-        <v>0.4045219076601765</v>
+        <v>0.4419783593639544</v>
       </c>
       <c r="AP6">
-        <v>0.4045219076601765</v>
+        <v>0.4419783593639544</v>
       </c>
       <c r="AQ6">
-        <v>0.4045219076601765</v>
+        <v>0.4419783593639544</v>
       </c>
       <c r="AR6">
-        <v>0.4045219076601765</v>
+        <v>0.4419783593639544</v>
       </c>
       <c r="AS6">
-        <v>0.4045219076601765</v>
+        <v>0.4419783593639544</v>
       </c>
       <c r="AT6">
-        <v>0.4045219076601765</v>
+        <v>0.4419783593639544</v>
       </c>
       <c r="AU6">
-        <v>0.4045219076601765</v>
+        <v>0.4419783593639544</v>
       </c>
       <c r="AV6">
-        <v>0.4045219076601765</v>
+        <v>0.4419783593639544</v>
       </c>
       <c r="AW6">
-        <v>0.4045219076601765</v>
+        <v>0.4419783593639544</v>
       </c>
       <c r="AX6">
-        <v>0.4045219076601765</v>
+        <v>0.4419783593639544</v>
       </c>
       <c r="AY6">
-        <v>0.4045219076601765</v>
+        <v>0.4186610819687361</v>
       </c>
       <c r="AZ6">
-        <v>0.4045219076601765</v>
+        <v>0.3953438045735179</v>
       </c>
       <c r="BA6">
-        <v>0.4045219076601765</v>
+        <v>0.3953438045735179</v>
       </c>
       <c r="BB6">
-        <v>0.4045219076601765</v>
+        <v>0.3735586256003169</v>
       </c>
       <c r="BC6">
-        <v>0.4045219076601765</v>
+        <v>0.3517734466271159</v>
       </c>
       <c r="BD6">
-        <v>0.4045219076601765</v>
+        <v>0.3517734466271159</v>
       </c>
       <c r="BE6">
-        <v>0.4045219076601765</v>
+        <v>0.3517734466271159</v>
       </c>
       <c r="BF6">
-        <v>0.4045219076601765</v>
+        <v>0.3517734466271159</v>
       </c>
       <c r="BG6">
-        <v>0.4045219076601765</v>
+        <v>0.3517734466271159</v>
       </c>
       <c r="BH6">
-        <v>0.3697861755796487</v>
+        <v>0.3170377145465882</v>
       </c>
       <c r="BI6">
-        <v>0.3350504434991208</v>
+        <v>0.2823019824660605</v>
       </c>
       <c r="BJ6">
-        <v>0.300314711418593</v>
+        <v>0.2475662503855328</v>
       </c>
       <c r="BK6">
-        <v>0.300314711418593</v>
+        <v>0.2475662503855328</v>
       </c>
       <c r="BL6">
-        <v>0.2304606608827331</v>
+        <v>0.2475662503855328</v>
       </c>
       <c r="BM6">
-        <v>0.2304606608827331</v>
+        <v>0.2335818613975818</v>
       </c>
       <c r="BN6">
-        <v>0.2304606608827331</v>
+        <v>0.2195974724096309</v>
       </c>
       <c r="BO6">
-        <v>0.2304606608827331</v>
+        <v>0.2056130834216799</v>
       </c>
       <c r="BP6">
-        <v>0.2242096417485092</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="BQ6">
-        <v>0.2242096417485092</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="BR6">
-        <v>0.2242096417485092</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="BS6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="BT6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="BU6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="BV6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="BW6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="BX6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="BY6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="BZ6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CA6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CB6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CC6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CD6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CE6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CF6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CG6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CH6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CI6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CJ6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CK6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CL6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CM6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CN6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CO6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CP6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CQ6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CR6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
       <c r="CS6">
-        <v>0.201984436869565</v>
+        <v>0.2056130834216797</v>
       </c>
     </row>
     <row r="7" spans="1:97">
@@ -3407,7 +3410,7 @@
         <v>0.2</v>
       </c>
       <c r="D7">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="E7">
         <v>0.26</v>
@@ -3419,274 +3422,274 @@
         <v>0.26</v>
       </c>
       <c r="H7">
+        <v>0.26</v>
+      </c>
+      <c r="I7">
+        <v>0.26</v>
+      </c>
+      <c r="J7">
         <v>0.32</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>0.32</v>
       </c>
-      <c r="J7">
-        <v>0.38</v>
-      </c>
-      <c r="K7">
-        <v>0.44</v>
-      </c>
       <c r="L7">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="M7">
-        <v>0.5</v>
+        <v>0.32</v>
       </c>
       <c r="N7">
-        <v>0.5</v>
+        <v>0.32</v>
       </c>
       <c r="O7">
-        <v>0.5</v>
+        <v>0.32</v>
       </c>
       <c r="P7">
-        <v>0.5</v>
+        <v>0.32</v>
       </c>
       <c r="Q7">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="R7">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="S7">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="T7">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="U7">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="V7">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="W7">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="X7">
-        <v>0.5</v>
+        <v>0.3600912170101561</v>
       </c>
       <c r="Y7">
-        <v>0.5</v>
+        <v>0.3401824340203123</v>
       </c>
       <c r="Z7">
-        <v>0.5600000000000001</v>
+        <v>0.3202736510304685</v>
       </c>
       <c r="AA7">
-        <v>0.5600000000000001</v>
+        <v>0.3003648680406238</v>
       </c>
       <c r="AB7">
-        <v>0.5600000000000001</v>
+        <v>0.2804560850507781</v>
       </c>
       <c r="AC7">
-        <v>0.5422304216716225</v>
+        <v>0.3404560850507781</v>
       </c>
       <c r="AD7">
-        <v>0.5244608433432449</v>
+        <v>0.3404560850507781</v>
       </c>
       <c r="AE7">
-        <v>0.5066912650148674</v>
+        <v>0.3208060091031095</v>
       </c>
       <c r="AF7">
-        <v>0.4889216866864899</v>
+        <v>0.3011559331554408</v>
       </c>
       <c r="AG7">
-        <v>0.4711521083581124</v>
+        <v>0.2815058572077722</v>
       </c>
       <c r="AH7">
-        <v>0.4711521083581124</v>
+        <v>0.2620008603706872</v>
       </c>
       <c r="AI7">
-        <v>0.4508232061799597</v>
+        <v>0.2424958635336022</v>
       </c>
       <c r="AJ7">
-        <v>0.4304943040018071</v>
+        <v>0.2229908666965172</v>
       </c>
       <c r="AK7">
-        <v>0.4101654018236545</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="AL7">
-        <v>0.3898364996455018</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="AM7">
-        <v>0.3898364996455018</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="AN7">
-        <v>0.3898364996455019</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="AO7">
-        <v>0.3898364996455019</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="AP7">
-        <v>0.3898364996455019</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="AQ7">
-        <v>0.3841035462950422</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="AR7">
-        <v>0.3783705929445826</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="AS7">
-        <v>0.372637639594123</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="AT7">
-        <v>0.3669046862436634</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="AU7">
-        <v>0.3611717328932038</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="AV7">
-        <v>0.3611717328932038</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="AW7">
-        <v>0.3611717328932038</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="AX7">
-        <v>0.3611717328932038</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="AY7">
-        <v>0.3382483084660045</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="AZ7">
-        <v>0.3153248840388053</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BA7">
-        <v>0.2924014596116061</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BB7">
-        <v>0.2924014596116061</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BC7">
-        <v>0.2924014596116061</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BD7">
-        <v>0.2924014596116061</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BE7">
-        <v>0.2924014596116061</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BF7">
-        <v>0.2924014596116061</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BG7">
-        <v>0.2924014596116061</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BH7">
-        <v>0.2924014596116061</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BI7">
-        <v>0.2924014596116061</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BJ7">
-        <v>0.2924014596116061</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BK7">
-        <v>0.2774905322871875</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BL7">
-        <v>0.2774905322871875</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BM7">
-        <v>0.2401859649335139</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BN7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BO7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BP7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BQ7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BR7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BS7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BT7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BU7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BV7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BW7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BX7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BY7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="BZ7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CA7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CB7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CC7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CD7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CE7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CF7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CG7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CH7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CI7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CJ7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CK7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CL7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CM7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CN7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CO7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CP7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CQ7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CR7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
       <c r="CS7">
-        <v>0.2028813975798403</v>
+        <v>0.2034858698594322</v>
       </c>
     </row>
     <row r="8" spans="1:97">
@@ -3700,7 +3703,7 @@
         <v>0.2</v>
       </c>
       <c r="D8">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="E8">
         <v>0.26</v>
@@ -3712,274 +3715,274 @@
         <v>0.26</v>
       </c>
       <c r="H8">
+        <v>0.26</v>
+      </c>
+      <c r="I8">
+        <v>0.26</v>
+      </c>
+      <c r="J8">
+        <v>0.26</v>
+      </c>
+      <c r="K8">
+        <v>0.26</v>
+      </c>
+      <c r="L8">
+        <v>0.26</v>
+      </c>
+      <c r="M8">
+        <v>0.26</v>
+      </c>
+      <c r="N8">
+        <v>0.26</v>
+      </c>
+      <c r="O8">
+        <v>0.26</v>
+      </c>
+      <c r="P8">
         <v>0.32</v>
       </c>
-      <c r="I8">
-        <v>0.32</v>
-      </c>
-      <c r="J8">
-        <v>0.32</v>
-      </c>
-      <c r="K8">
-        <v>0.38</v>
-      </c>
-      <c r="L8">
-        <v>0.38</v>
-      </c>
-      <c r="M8">
-        <v>0.38</v>
-      </c>
-      <c r="N8">
-        <v>0.38</v>
-      </c>
-      <c r="O8">
-        <v>0.38</v>
-      </c>
-      <c r="P8">
-        <v>0.38</v>
-      </c>
       <c r="Q8">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="R8">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="S8">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="T8">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="U8">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="V8">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="W8">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="X8">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="Y8">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="Z8">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="AA8">
-        <v>0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="AB8">
-        <v>0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="AC8">
-        <v>0.5504333071067173</v>
+        <v>0.44</v>
       </c>
       <c r="AD8">
-        <v>0.5408666142134603</v>
+        <v>0.4213019258919735</v>
       </c>
       <c r="AE8">
-        <v>0.531299921320202</v>
+        <v>0.4026038517839489</v>
       </c>
       <c r="AF8">
-        <v>0.5217332284269407</v>
+        <v>0.3839057776759243</v>
       </c>
       <c r="AG8">
-        <v>0.5121665355336817</v>
+        <v>0.3652077035678997</v>
       </c>
       <c r="AH8">
-        <v>0.5025998426404256</v>
+        <v>0.3449736684042762</v>
       </c>
       <c r="AI8">
-        <v>0.4930331497471709</v>
+        <v>0.3247396332406527</v>
       </c>
       <c r="AJ8">
-        <v>0.4930331497471709</v>
+        <v>0.3045055980770293</v>
       </c>
       <c r="AK8">
-        <v>0.4930331497471709</v>
+        <v>0.3045055980770293</v>
       </c>
       <c r="AL8">
-        <v>0.4930331497471709</v>
+        <v>0.3045055980770293</v>
       </c>
       <c r="AM8">
-        <v>0.4930331497471709</v>
+        <v>0.3045055980770293</v>
       </c>
       <c r="AN8">
-        <v>0.4930331497471709</v>
+        <v>0.3045055980770293</v>
       </c>
       <c r="AO8">
-        <v>0.4930331497471709</v>
+        <v>0.3045055980770293</v>
       </c>
       <c r="AP8">
-        <v>0.4930331497471446</v>
+        <v>0.3045055980770293</v>
       </c>
       <c r="AQ8">
-        <v>0.4930331497471421</v>
+        <v>0.3045055980770293</v>
       </c>
       <c r="AR8">
-        <v>0.4930331497471395</v>
+        <v>0.3045055980770293</v>
       </c>
       <c r="AS8">
-        <v>0.493033149747137</v>
+        <v>0.3045055980770293</v>
       </c>
       <c r="AT8">
-        <v>0.4930331497471336</v>
+        <v>0.3045055980770293</v>
       </c>
       <c r="AU8">
-        <v>0.4930331497471299</v>
+        <v>0.3045055980770293</v>
       </c>
       <c r="AV8">
-        <v>0.4930331497471299</v>
+        <v>0.3045055980770293</v>
       </c>
       <c r="AW8">
-        <v>0.4930331497471283</v>
+        <v>0.3045055980770293</v>
       </c>
       <c r="AX8">
-        <v>0.4930331497471283</v>
+        <v>0.3045055980770293</v>
       </c>
       <c r="AY8">
-        <v>0.4930331497471264</v>
+        <v>0.3045055980770293</v>
       </c>
       <c r="AZ8">
-        <v>0.4930331497471233</v>
+        <v>0.3045055980770293</v>
       </c>
       <c r="BA8">
-        <v>0.4574156320962692</v>
+        <v>0.3045055980770293</v>
       </c>
       <c r="BB8">
-        <v>0.4217981144454143</v>
+        <v>0.2780885807000272</v>
       </c>
       <c r="BC8">
-        <v>0.4217981144454143</v>
+        <v>0.2780885807000272</v>
       </c>
       <c r="BD8">
-        <v>0.4217981144454143</v>
+        <v>0.2780885807000272</v>
       </c>
       <c r="BE8">
-        <v>0.4217981144454143</v>
+        <v>0.2780885807000272</v>
       </c>
       <c r="BF8">
-        <v>0.4217981144454143</v>
+        <v>0.2780885807000272</v>
       </c>
       <c r="BG8">
-        <v>0.4217981144454143</v>
+        <v>0.2780885807000272</v>
       </c>
       <c r="BH8">
-        <v>0.3938107126828934</v>
+        <v>0.2780885807000272</v>
       </c>
       <c r="BI8">
-        <v>0.3658233109203725</v>
+        <v>0.2780885807000272</v>
       </c>
       <c r="BJ8">
-        <v>0.3378359091578516</v>
+        <v>0.2780885807000272</v>
       </c>
       <c r="BK8">
-        <v>0.3378359091578516</v>
+        <v>0.2631776533756086</v>
       </c>
       <c r="BL8">
-        <v>0.3378359091578516</v>
+        <v>0.2631776533756086</v>
       </c>
       <c r="BM8">
-        <v>0.3378359091578516</v>
+        <v>0.2468625614419611</v>
       </c>
       <c r="BN8">
-        <v>0.3378359091578516</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="BO8">
-        <v>0.3378359091578516</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="BP8">
-        <v>0.3378359091578516</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="BQ8">
-        <v>0.3378359091578516</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="BR8">
-        <v>0.2582045763676594</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="BS8">
-        <v>0.2582045763676594</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="BT8">
-        <v>0.2295520738490589</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="BU8">
-        <v>0.2008995713304584</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="BV8">
-        <v>0.2008995713304584</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="BW8">
-        <v>0.2008995713304584</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="BX8">
-        <v>0.2008995713304584</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="BY8">
-        <v>0.2008995713304584</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="BZ8">
-        <v>0.2008995713304584</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="CA8">
-        <v>0.2008995713304584</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="CB8">
-        <v>0.2008995713304584</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="CC8">
-        <v>0.2008995713304584</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="CD8">
-        <v>0.2008995713304584</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="CE8">
-        <v>0.2008995713304584</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="CF8">
-        <v>0.2008995713304584</v>
+        <v>0.2305474695083135</v>
       </c>
       <c r="CG8">
-        <v>0.2008995713304584</v>
+        <v>0.2063948939563891</v>
       </c>
       <c r="CH8">
-        <v>0.2008995713304584</v>
+        <v>0.2063948939563891</v>
       </c>
       <c r="CI8">
-        <v>0.2008995713304584</v>
+        <v>0.2063948939563891</v>
       </c>
       <c r="CJ8">
-        <v>0.2008995713304584</v>
+        <v>0.2063948939563891</v>
       </c>
       <c r="CK8">
-        <v>0.2008995713304584</v>
+        <v>0.2063948939563891</v>
       </c>
       <c r="CL8">
-        <v>0.2008995713304584</v>
+        <v>0.2036746731148371</v>
       </c>
       <c r="CM8">
-        <v>0.2008995713304584</v>
+        <v>0.2009544522732852</v>
       </c>
       <c r="CN8">
-        <v>0.2008995713304584</v>
+        <v>0.2009544522732852</v>
       </c>
       <c r="CO8">
-        <v>0.2008995713304584</v>
+        <v>0.2009544522732852</v>
       </c>
       <c r="CP8">
-        <v>0.2008995713304584</v>
+        <v>0.2009544522732852</v>
       </c>
       <c r="CQ8">
-        <v>0.2008995713304584</v>
+        <v>0.2009544522732852</v>
       </c>
       <c r="CR8">
-        <v>0.2008995713304584</v>
+        <v>0.2009544522732852</v>
       </c>
       <c r="CS8">
-        <v>0.2008995713304584</v>
+        <v>0.2009544522732852</v>
       </c>
     </row>
     <row r="9" spans="1:97">
@@ -3990,7 +3993,7 @@
         <v>0.2</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="D9">
         <v>0.26</v>
@@ -3999,7 +4002,7 @@
         <v>0.26</v>
       </c>
       <c r="F9">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="G9">
         <v>0.32</v>
@@ -4017,262 +4020,262 @@
         <v>0.38</v>
       </c>
       <c r="L9">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="M9">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="N9">
+        <v>0.38</v>
+      </c>
+      <c r="O9">
+        <v>0.44</v>
+      </c>
+      <c r="P9">
+        <v>0.44</v>
+      </c>
+      <c r="Q9">
+        <v>0.44</v>
+      </c>
+      <c r="R9">
+        <v>0.44</v>
+      </c>
+      <c r="S9">
+        <v>0.44</v>
+      </c>
+      <c r="T9">
+        <v>0.44</v>
+      </c>
+      <c r="U9">
+        <v>0.44</v>
+      </c>
+      <c r="V9">
+        <v>0.44</v>
+      </c>
+      <c r="W9">
         <v>0.5</v>
       </c>
-      <c r="O9">
+      <c r="X9">
         <v>0.5</v>
       </c>
-      <c r="P9">
+      <c r="Y9">
         <v>0.5</v>
       </c>
-      <c r="Q9">
+      <c r="Z9">
         <v>0.5</v>
       </c>
-      <c r="R9">
-        <v>0.5</v>
-      </c>
-      <c r="S9">
-        <v>0.5</v>
-      </c>
-      <c r="T9">
+      <c r="AA9">
         <v>0.5600000000000001</v>
       </c>
-      <c r="U9">
+      <c r="AB9">
         <v>0.5600000000000001</v>
       </c>
-      <c r="V9">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="W9">
-        <v>0.62</v>
-      </c>
-      <c r="X9">
-        <v>0.68</v>
-      </c>
-      <c r="Y9">
-        <v>0.74</v>
-      </c>
-      <c r="Z9">
-        <v>0.7286415617055514</v>
-      </c>
-      <c r="AA9">
-        <v>0.717283123411115</v>
-      </c>
-      <c r="AB9">
-        <v>0.7059246851166786</v>
-      </c>
       <c r="AC9">
-        <v>0.6945662468222431</v>
+        <v>0.5422304216716025</v>
       </c>
       <c r="AD9">
-        <v>0.683207808527807</v>
+        <v>0.5244608433432156</v>
       </c>
       <c r="AE9">
-        <v>0.6718493702333697</v>
+        <v>0.5066912650148272</v>
       </c>
       <c r="AF9">
-        <v>0.6604909319389284</v>
+        <v>0.4889216866864359</v>
       </c>
       <c r="AG9">
-        <v>0.6491324936444867</v>
+        <v>0.471152108358046</v>
       </c>
       <c r="AH9">
-        <v>0.6288984584808552</v>
+        <v>0.471152108358046</v>
       </c>
       <c r="AI9">
-        <v>0.608664423317223</v>
+        <v>0.4577562424539473</v>
       </c>
       <c r="AJ9">
-        <v>0.5884303881535914</v>
+        <v>0.4443603765498485</v>
       </c>
       <c r="AK9">
-        <v>0.5884303881535844</v>
+        <v>0.4309645106457498</v>
       </c>
       <c r="AL9">
-        <v>0.588430388153578</v>
+        <v>0.4175686447416511</v>
       </c>
       <c r="AM9">
-        <v>0.5884303881535735</v>
+        <v>0.4175686447416511</v>
       </c>
       <c r="AN9">
-        <v>0.5884303881535735</v>
+        <v>0.4175686447415992</v>
       </c>
       <c r="AO9">
-        <v>0.5884303881535735</v>
+        <v>0.4175686447415954</v>
       </c>
       <c r="AP9">
-        <v>0.5884303881535616</v>
+        <v>0.4175686447415954</v>
       </c>
       <c r="AQ9">
-        <v>0.5884303881535586</v>
+        <v>0.4175686447415954</v>
       </c>
       <c r="AR9">
-        <v>0.5884303881535586</v>
+        <v>0.4175686447415871</v>
       </c>
       <c r="AS9">
-        <v>0.5884303881535509</v>
+        <v>0.4175686447415833</v>
       </c>
       <c r="AT9">
-        <v>0.5884303881535472</v>
+        <v>0.4175686447415796</v>
       </c>
       <c r="AU9">
-        <v>0.5884303881535439</v>
+        <v>0.4175686447415769</v>
       </c>
       <c r="AV9">
-        <v>0.5884303881535413</v>
+        <v>0.4175686447415741</v>
       </c>
       <c r="AW9">
-        <v>0.5884303881535384</v>
+        <v>0.4175686447415714</v>
       </c>
       <c r="AX9">
-        <v>0.559381276942324</v>
+        <v>0.4175686447415698</v>
       </c>
       <c r="AY9">
-        <v>0.530332165731109</v>
+        <v>0.417568644741567</v>
       </c>
       <c r="AZ9">
-        <v>0.4971365188705387</v>
+        <v>0.417568644741567</v>
       </c>
       <c r="BA9">
-        <v>0.4639408720099673</v>
+        <v>0.417568644741567</v>
       </c>
       <c r="BB9">
-        <v>0.4307452251493954</v>
+        <v>0.417568644741567</v>
       </c>
       <c r="BC9">
-        <v>0.4307452251493954</v>
+        <v>0.417568644741567</v>
       </c>
       <c r="BD9">
-        <v>0.4307452251493954</v>
+        <v>0.417568644741567</v>
       </c>
       <c r="BE9">
-        <v>0.4307452251493954</v>
+        <v>0.417568644741567</v>
       </c>
       <c r="BF9">
-        <v>0.4307452251493954</v>
+        <v>0.417568644741567</v>
       </c>
       <c r="BG9">
-        <v>0.404025232258412</v>
+        <v>0.417568644741567</v>
       </c>
       <c r="BH9">
-        <v>0.3773052393674285</v>
+        <v>0.417568644741567</v>
       </c>
       <c r="BI9">
-        <v>0.3773052393674285</v>
+        <v>0.417568644741567</v>
       </c>
       <c r="BJ9">
-        <v>0.3773052393674285</v>
+        <v>0.417568644741567</v>
       </c>
       <c r="BK9">
-        <v>0.3773052393674275</v>
+        <v>0.417568644741567</v>
       </c>
       <c r="BL9">
-        <v>0.3532945381721761</v>
+        <v>0.417568644741567</v>
       </c>
       <c r="BM9">
-        <v>0.3292838369769248</v>
+        <v>0.3802640773878935</v>
       </c>
       <c r="BN9">
-        <v>0.3052731357816735</v>
+        <v>0.3429595100342199</v>
       </c>
       <c r="BO9">
-        <v>0.3052731357816735</v>
+        <v>0.3429595100342199</v>
       </c>
       <c r="BP9">
-        <v>0.2770976471128763</v>
+        <v>0.3429595100342199</v>
       </c>
       <c r="BQ9">
-        <v>0.2489221584440791</v>
+        <v>0.3429595100342199</v>
       </c>
       <c r="BR9">
-        <v>0.220746669775282</v>
+        <v>0.3429595100342199</v>
       </c>
       <c r="BS9">
-        <v>0.2207466697752812</v>
+        <v>0.3429595100342199</v>
       </c>
       <c r="BT9">
-        <v>0.2207466697752832</v>
+        <v>0.3429595100342199</v>
       </c>
       <c r="BU9">
-        <v>0.2001410859837891</v>
+        <v>0.3429595100342199</v>
       </c>
       <c r="BV9">
-        <v>0.2001410859837891</v>
+        <v>0.3142560252716685</v>
       </c>
       <c r="BW9">
-        <v>0.2001410859837891</v>
+        <v>0.285552540509117</v>
       </c>
       <c r="BX9">
-        <v>0.2001410859837891</v>
+        <v>0.2487847432396542</v>
       </c>
       <c r="BY9">
-        <v>0.2001410859837891</v>
+        <v>0.2120169459701909</v>
       </c>
       <c r="BZ9">
-        <v>0.2001410859837891</v>
+        <v>0.2120169459701909</v>
       </c>
       <c r="CA9">
-        <v>0.2001410859837891</v>
+        <v>0.2120169459701909</v>
       </c>
       <c r="CB9">
-        <v>0.2001410859837891</v>
+        <v>0.2120169459701904</v>
       </c>
       <c r="CC9">
-        <v>0.2001410859837891</v>
+        <v>0.2120169459701904</v>
       </c>
       <c r="CD9">
-        <v>0.2001410859837891</v>
+        <v>0.2092855918772766</v>
       </c>
       <c r="CE9">
-        <v>0.2001410859837891</v>
+        <v>0.2065542377843627</v>
       </c>
       <c r="CF9">
-        <v>0.2001410859837891</v>
+        <v>0.2065542377843627</v>
       </c>
       <c r="CG9">
-        <v>0.2001410859837891</v>
+        <v>0.2065542377843634</v>
       </c>
       <c r="CH9">
-        <v>0.2001410859837891</v>
+        <v>0.2065542377843634</v>
       </c>
       <c r="CI9">
-        <v>0.2001410859837891</v>
+        <v>0.2065542377843634</v>
       </c>
       <c r="CJ9">
-        <v>0.2001410859837891</v>
+        <v>0.2065542377843634</v>
       </c>
       <c r="CK9">
-        <v>0.2001410859837891</v>
+        <v>0.2065542377843634</v>
       </c>
       <c r="CL9">
-        <v>0.2001410859837891</v>
+        <v>0.2065542377843634</v>
       </c>
       <c r="CM9">
-        <v>0.2001410859837891</v>
+        <v>0.2065542377843634</v>
       </c>
       <c r="CN9">
-        <v>0.2001410859837891</v>
+        <v>0.2065542377843634</v>
       </c>
       <c r="CO9">
-        <v>0.2001410859837891</v>
+        <v>0.2665542377843634</v>
       </c>
       <c r="CP9">
-        <v>0.2001410859837891</v>
+        <v>0.2336116702173287</v>
       </c>
       <c r="CQ9">
-        <v>0.2001410859837891</v>
+        <v>0.2006691026502939</v>
       </c>
       <c r="CR9">
-        <v>0.2001410859837891</v>
+        <v>0.2006691026502939</v>
       </c>
       <c r="CS9">
-        <v>0.2001410859837891</v>
+        <v>0.2006691026502939</v>
       </c>
     </row>
     <row r="10" spans="1:97">
@@ -4292,280 +4295,280 @@
         <v>0.26</v>
       </c>
       <c r="F10">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="G10">
         <v>0.32</v>
       </c>
       <c r="H10">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="I10">
         <v>0.38</v>
       </c>
       <c r="J10">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="K10">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="L10">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="M10">
         <v>0.44</v>
       </c>
       <c r="N10">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="O10">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P10">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="Q10">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="R10">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="S10">
-        <v>0.44</v>
+        <v>0.68</v>
       </c>
       <c r="T10">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="U10">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="V10">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="W10">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="X10">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Y10">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Z10">
-        <v>0.5</v>
+        <v>0.7811378983886593</v>
       </c>
       <c r="AA10">
-        <v>0.5600000000000001</v>
+        <v>0.7622757967773179</v>
       </c>
       <c r="AB10">
-        <v>0.5375288550706585</v>
+        <v>0.7434136951659767</v>
       </c>
       <c r="AC10">
-        <v>0.515057710141273</v>
+        <v>0.7245515935546353</v>
       </c>
       <c r="AD10">
-        <v>0.4925865652118875</v>
+        <v>0.7089812901007391</v>
       </c>
       <c r="AE10">
-        <v>0.4925865652118875</v>
+        <v>0.6934109866468429</v>
       </c>
       <c r="AF10">
-        <v>0.4768003900085095</v>
+        <v>0.6778406831929467</v>
       </c>
       <c r="AG10">
-        <v>0.4610142148051316</v>
+        <v>0.6622703797390505</v>
       </c>
       <c r="AH10">
-        <v>0.4452280396017536</v>
+        <v>0.6467000762851542</v>
       </c>
       <c r="AI10">
-        <v>0.4294418643983755</v>
+        <v>0.6284397998224265</v>
       </c>
       <c r="AJ10">
-        <v>0.4136556891949976</v>
+        <v>0.6101795233596988</v>
       </c>
       <c r="AK10">
-        <v>0.3978695139916196</v>
+        <v>0.5919192468969712</v>
       </c>
       <c r="AL10">
-        <v>0.3978695139916196</v>
+        <v>0.5736589704342434</v>
       </c>
       <c r="AM10">
-        <v>0.3978695139916196</v>
+        <v>0.5553986939715158</v>
       </c>
       <c r="AN10">
-        <v>0.3978695139916196</v>
+        <v>0.5553986939715158</v>
       </c>
       <c r="AO10">
-        <v>0.3978695139916196</v>
+        <v>0.5553986939715158</v>
       </c>
       <c r="AP10">
-        <v>0.3978695139916196</v>
+        <v>0.5553986939715158</v>
       </c>
       <c r="AQ10">
-        <v>0.3978695139916196</v>
+        <v>0.5553986939715158</v>
       </c>
       <c r="AR10">
-        <v>0.3978695139916196</v>
+        <v>0.5553986939715158</v>
       </c>
       <c r="AS10">
-        <v>0.3929201693165391</v>
+        <v>0.5553986939715158</v>
       </c>
       <c r="AT10">
-        <v>0.3879708246414585</v>
+        <v>0.5553986939715158</v>
       </c>
       <c r="AU10">
-        <v>0.383021479966378</v>
+        <v>0.5553986939715158</v>
       </c>
       <c r="AV10">
-        <v>0.3780721352912974</v>
+        <v>0.5553986939715158</v>
       </c>
       <c r="AW10">
-        <v>0.3731227906162168</v>
+        <v>0.5553986939715158</v>
       </c>
       <c r="AX10">
-        <v>0.3731227906162168</v>
+        <v>0.5368887957298368</v>
       </c>
       <c r="AY10">
-        <v>0.3731227906162168</v>
+        <v>0.5368887957298368</v>
       </c>
       <c r="AZ10">
-        <v>0.3731227906162168</v>
+        <v>0.5368887957298368</v>
       </c>
       <c r="BA10">
-        <v>0.3731227906162168</v>
+        <v>0.5368887957298368</v>
       </c>
       <c r="BB10">
-        <v>0.3731227906162168</v>
+        <v>0.5368887957298368</v>
       </c>
       <c r="BC10">
-        <v>0.3731227906162168</v>
+        <v>0.5368887957298368</v>
       </c>
       <c r="BD10">
-        <v>0.3731227906162168</v>
+        <v>0.5368887957298368</v>
       </c>
       <c r="BE10">
-        <v>0.3403631116695749</v>
+        <v>0.509327590748287</v>
       </c>
       <c r="BF10">
-        <v>0.3076034327229329</v>
+        <v>0.4817663857667374</v>
       </c>
       <c r="BG10">
-        <v>0.3076034327229329</v>
+        <v>0.4817663857667374</v>
       </c>
       <c r="BH10">
-        <v>0.2714924376965032</v>
+        <v>0.4817663857667374</v>
       </c>
       <c r="BI10">
-        <v>0.2714924376965032</v>
+        <v>0.4817663857667374</v>
       </c>
       <c r="BJ10">
-        <v>0.2714924376965031</v>
+        <v>0.4473217334264062</v>
       </c>
       <c r="BK10">
-        <v>0.2714924376965031</v>
+        <v>0.4128770810860751</v>
       </c>
       <c r="BL10">
-        <v>0.2714924376965031</v>
+        <v>0.3816508446431845</v>
       </c>
       <c r="BM10">
-        <v>0.2714924376965031</v>
+        <v>0.350424608200294</v>
       </c>
       <c r="BN10">
-        <v>0.2714924376965031</v>
+        <v>0.350424608200294</v>
       </c>
       <c r="BO10">
-        <v>0.2714924376965031</v>
+        <v>0.350424608200294</v>
       </c>
       <c r="BP10">
-        <v>0.2714924376965031</v>
+        <v>0.350424608200294</v>
       </c>
       <c r="BQ10">
-        <v>0.2714924376965031</v>
+        <v>0.350424608200294</v>
       </c>
       <c r="BR10">
-        <v>0.2684314806233365</v>
+        <v>0.350424608200294</v>
       </c>
       <c r="BS10">
-        <v>0.2684314806233365</v>
+        <v>0.350424608200294</v>
       </c>
       <c r="BT10">
-        <v>0.2684314806233365</v>
+        <v>0.3126082669428175</v>
       </c>
       <c r="BU10">
-        <v>0.2684314806233365</v>
+        <v>0.2747919256853411</v>
       </c>
       <c r="BV10">
-        <v>0.2684314806233365</v>
+        <v>0.2747919256853411</v>
       </c>
       <c r="BW10">
-        <v>0.2473765898224805</v>
+        <v>0.2490610404419049</v>
       </c>
       <c r="BX10">
-        <v>0.2263216990216245</v>
+        <v>0.2490610404419049</v>
       </c>
       <c r="BY10">
-        <v>0.2017672301061697</v>
+        <v>0.2490610404419049</v>
       </c>
       <c r="BZ10">
-        <v>0.2017672301061697</v>
+        <v>0.2490610404419049</v>
       </c>
       <c r="CA10">
-        <v>0.2017672301061697</v>
+        <v>0.2490610404419049</v>
       </c>
       <c r="CB10">
-        <v>0.2017672301061697</v>
+        <v>0.2490610404419049</v>
       </c>
       <c r="CC10">
-        <v>0.2017672301061697</v>
+        <v>0.2490610404419049</v>
       </c>
       <c r="CD10">
-        <v>0.2017672301061697</v>
+        <v>0.2490610404419049</v>
       </c>
       <c r="CE10">
-        <v>0.2017672301061697</v>
+        <v>0.2490610404419054</v>
       </c>
       <c r="CF10">
-        <v>0.2017672301061697</v>
+        <v>0.2490610404419054</v>
       </c>
       <c r="CG10">
-        <v>0.2017672301061697</v>
+        <v>0.2267386781637188</v>
       </c>
       <c r="CH10">
-        <v>0.2017672301061697</v>
+        <v>0.2044163158855322</v>
       </c>
       <c r="CI10">
-        <v>0.2017672301061697</v>
+        <v>0.2044163158855322</v>
       </c>
       <c r="CJ10">
-        <v>0.2017672301061697</v>
+        <v>0.2044163158855322</v>
       </c>
       <c r="CK10">
-        <v>0.2017672301061602</v>
+        <v>0.2044163158855322</v>
       </c>
       <c r="CL10">
-        <v>0.2017672301061508</v>
+        <v>0.2044163158855322</v>
       </c>
       <c r="CM10">
-        <v>0.2017672301061508</v>
+        <v>0.2044163158855322</v>
       </c>
       <c r="CN10">
-        <v>0.2017672301061508</v>
+        <v>0.2044163158855322</v>
       </c>
       <c r="CO10">
-        <v>0.2017672301061508</v>
+        <v>0.2044163158855322</v>
       </c>
       <c r="CP10">
-        <v>0.2017672301061508</v>
+        <v>0.2044163158855322</v>
       </c>
       <c r="CQ10">
-        <v>0.2017672301061508</v>
+        <v>0.2044163158855322</v>
       </c>
       <c r="CR10">
-        <v>0.2017672301061508</v>
+        <v>0.2044163158855322</v>
       </c>
       <c r="CS10">
-        <v>0.2017672301061508</v>
+        <v>0.2044163158855322</v>
       </c>
     </row>
     <row r="11" spans="1:97">
@@ -4588,277 +4591,277 @@
         <v>0.26</v>
       </c>
       <c r="G11">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="H11">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="I11">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="J11">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="K11">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="L11">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="M11">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="N11">
-        <v>0.26</v>
+        <v>0.44</v>
       </c>
       <c r="O11">
-        <v>0.26</v>
+        <v>0.44</v>
       </c>
       <c r="P11">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="Q11">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="R11">
-        <v>0.32</v>
+        <v>0.5</v>
       </c>
       <c r="S11">
-        <v>0.32</v>
+        <v>0.5</v>
       </c>
       <c r="T11">
-        <v>0.32</v>
+        <v>0.5</v>
       </c>
       <c r="U11">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="V11">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="W11">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="X11">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Y11">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z11">
-        <v>0.44</v>
+        <v>0.5486415617055684</v>
       </c>
       <c r="AA11">
-        <v>0.44</v>
+        <v>0.537283123411137</v>
       </c>
       <c r="AB11">
-        <v>0.4212057227035149</v>
+        <v>0.5259246851167055</v>
       </c>
       <c r="AC11">
-        <v>0.4024114454070296</v>
+        <v>0.5145662468222741</v>
       </c>
       <c r="AD11">
-        <v>0.3836171681105443</v>
+        <v>0.5032078085278426</v>
       </c>
       <c r="AE11">
-        <v>0.364822890814059</v>
+        <v>0.4918493702334111</v>
       </c>
       <c r="AF11">
-        <v>0.3460286135175737</v>
+        <v>0.4804909319389797</v>
       </c>
       <c r="AG11">
-        <v>0.3270540677448907</v>
+        <v>0.4691324936445482</v>
       </c>
       <c r="AH11">
-        <v>0.3080795219722077</v>
+        <v>0.4691324936445482</v>
       </c>
       <c r="AI11">
-        <v>0.3080795219722077</v>
+        <v>0.4691324936445482</v>
       </c>
       <c r="AJ11">
-        <v>0.3080795219722077</v>
+        <v>0.4691324936445482</v>
       </c>
       <c r="AK11">
-        <v>0.3080795219722077</v>
+        <v>0.4526316235931956</v>
       </c>
       <c r="AL11">
-        <v>0.3080795219722077</v>
+        <v>0.4361307535418431</v>
       </c>
       <c r="AM11">
-        <v>0.3080795219722077</v>
+        <v>0.4196298834904904</v>
       </c>
       <c r="AN11">
-        <v>0.3080795219722077</v>
+        <v>0.4196298834904904</v>
       </c>
       <c r="AO11">
-        <v>0.3080795219722077</v>
+        <v>0.4196298834904904</v>
       </c>
       <c r="AP11">
-        <v>0.3080795219722077</v>
+        <v>0.4196298834904904</v>
       </c>
       <c r="AQ11">
-        <v>0.3080795219722077</v>
+        <v>0.4196298834904904</v>
       </c>
       <c r="AR11">
-        <v>0.3080795219722077</v>
+        <v>0.4196298834904904</v>
       </c>
       <c r="AS11">
-        <v>0.3080795219722077</v>
+        <v>0.4196298834904904</v>
       </c>
       <c r="AT11">
-        <v>0.3080795219722077</v>
+        <v>0.4196298834904904</v>
       </c>
       <c r="AU11">
-        <v>0.3080795219722077</v>
+        <v>0.4196298834904904</v>
       </c>
       <c r="AV11">
-        <v>0.3080795219722077</v>
+        <v>0.3902111793655425</v>
       </c>
       <c r="AW11">
-        <v>0.3080795219722077</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="AX11">
-        <v>0.3080795219722077</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="AY11">
-        <v>0.3080795219722077</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="AZ11">
-        <v>0.3080795219722077</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="BA11">
-        <v>0.3080795219722077</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="BB11">
-        <v>0.3080795219722076</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="BC11">
-        <v>0.3080795219722076</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="BD11">
-        <v>0.3080795219722076</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="BE11">
-        <v>0.3080795219722076</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="BF11">
-        <v>0.3080795219722076</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="BG11">
-        <v>0.3080795219722076</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="BH11">
-        <v>0.3080795219722076</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="BI11">
-        <v>0.3080795219722076</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="BJ11">
-        <v>0.3080795219722076</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="BK11">
-        <v>0.3080795219722076</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="BL11">
-        <v>0.3080795219722076</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="BM11">
-        <v>0.2799080837030324</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="BN11">
-        <v>0.2799080837030324</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="BO11">
-        <v>0.2628349308641378</v>
+        <v>0.3607924752405945</v>
       </c>
       <c r="BP11">
-        <v>0.2457617780252433</v>
+        <v>0.2897916544298277</v>
       </c>
       <c r="BQ11">
-        <v>0.2457617780252433</v>
+        <v>0.2897916544298277</v>
       </c>
       <c r="BR11">
-        <v>0.2230909286311845</v>
+        <v>0.2867306973566611</v>
       </c>
       <c r="BS11">
-        <v>0.2004200792371257</v>
+        <v>0.2867306973566611</v>
       </c>
       <c r="BT11">
-        <v>0.2004200792371257</v>
+        <v>0.2867306973566611</v>
       </c>
       <c r="BU11">
-        <v>0.2004200792371257</v>
+        <v>0.2867306973566611</v>
       </c>
       <c r="BV11">
-        <v>0.2004200792371257</v>
+        <v>0.2867306973566611</v>
       </c>
       <c r="BW11">
-        <v>0.2004200792371257</v>
+        <v>0.2867306973566611</v>
       </c>
       <c r="BX11">
-        <v>0.2004200792371257</v>
+        <v>0.2547049505573767</v>
       </c>
       <c r="BY11">
-        <v>0.2004200792371257</v>
+        <v>0.2226792037580924</v>
       </c>
       <c r="BZ11">
-        <v>0.2004200792371257</v>
+        <v>0.2226792037580924</v>
       </c>
       <c r="CA11">
-        <v>0.2004200792371257</v>
+        <v>0.2226792037580924</v>
       </c>
       <c r="CB11">
-        <v>0.2004200792371257</v>
+        <v>0.2826792037580925</v>
       </c>
       <c r="CC11">
-        <v>0.2004200792371257</v>
+        <v>0.2826792037580925</v>
       </c>
       <c r="CD11">
-        <v>0.2004200792371257</v>
+        <v>0.2826792037580925</v>
       </c>
       <c r="CE11">
-        <v>0.2004200792371257</v>
+        <v>0.2615919779254638</v>
       </c>
       <c r="CF11">
-        <v>0.2004200792371257</v>
+        <v>0.2615919779254638</v>
       </c>
       <c r="CG11">
-        <v>0.2004200792371257</v>
+        <v>0.2615919779254638</v>
       </c>
       <c r="CH11">
-        <v>0.2004200792371257</v>
+        <v>0.2615919779254638</v>
       </c>
       <c r="CI11">
-        <v>0.2004200792371257</v>
+        <v>0.2615919779254638</v>
       </c>
       <c r="CJ11">
-        <v>0.2004200792371257</v>
+        <v>0.2615919779254638</v>
       </c>
       <c r="CK11">
-        <v>0.2004200792371257</v>
+        <v>0.2392685463907973</v>
       </c>
       <c r="CL11">
-        <v>0.2004200792371257</v>
+        <v>0.2169451148561308</v>
       </c>
       <c r="CM11">
-        <v>0.2004200792371257</v>
+        <v>0.2169451148561308</v>
       </c>
       <c r="CN11">
-        <v>0.2004200792371257</v>
+        <v>0.2169451148561308</v>
       </c>
       <c r="CO11">
-        <v>0.2004200792371257</v>
+        <v>0.2169451148561308</v>
       </c>
       <c r="CP11">
-        <v>0.2004200792371257</v>
+        <v>0.2169451148561308</v>
       </c>
       <c r="CQ11">
-        <v>0.2004200792371257</v>
+        <v>0.2169451148561308</v>
       </c>
       <c r="CR11">
-        <v>0.2004200792371257</v>
+        <v>0.2169451148561308</v>
       </c>
       <c r="CS11">
-        <v>0.2004200792371257</v>
+        <v>0.2169451148561308</v>
       </c>
     </row>
     <row r="12" spans="1:97">
@@ -4869,13 +4872,13 @@
         <v>0.2</v>
       </c>
       <c r="C12">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="D12">
         <v>0.26</v>
       </c>
       <c r="E12">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="F12">
         <v>0.32</v>
@@ -4893,10 +4896,10 @@
         <v>0.32</v>
       </c>
       <c r="K12">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="L12">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="M12">
         <v>0.38</v>
@@ -4905,253 +4908,253 @@
         <v>0.38</v>
       </c>
       <c r="O12">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="P12">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="Q12">
+        <v>0.38</v>
+      </c>
+      <c r="R12">
+        <v>0.38</v>
+      </c>
+      <c r="S12">
+        <v>0.38</v>
+      </c>
+      <c r="T12">
+        <v>0.38</v>
+      </c>
+      <c r="U12">
+        <v>0.44</v>
+      </c>
+      <c r="V12">
+        <v>0.44</v>
+      </c>
+      <c r="W12">
+        <v>0.44</v>
+      </c>
+      <c r="X12">
         <v>0.5</v>
       </c>
-      <c r="R12">
-        <v>0.5</v>
-      </c>
-      <c r="S12">
-        <v>0.5</v>
-      </c>
-      <c r="T12">
-        <v>0.5</v>
-      </c>
-      <c r="U12">
-        <v>0.5</v>
-      </c>
-      <c r="V12">
-        <v>0.5</v>
-      </c>
-      <c r="W12">
-        <v>0.5</v>
-      </c>
-      <c r="X12">
+      <c r="Y12">
         <v>0.5600000000000001</v>
       </c>
-      <c r="Y12">
-        <v>0.62</v>
-      </c>
       <c r="Z12">
-        <v>0.6011378983886542</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AA12">
-        <v>0.5822757967773097</v>
+        <v>0.5405900293249486</v>
       </c>
       <c r="AB12">
-        <v>0.5634136951659655</v>
+        <v>0.5211800586498972</v>
       </c>
       <c r="AC12">
-        <v>0.5445515935546212</v>
+        <v>0.501770087974846</v>
       </c>
       <c r="AD12">
-        <v>0.544551593554619</v>
+        <v>0.4823601172997947</v>
       </c>
       <c r="AE12">
-        <v>0.5261216491353077</v>
+        <v>0.4629501466247435</v>
       </c>
       <c r="AF12">
-        <v>0.5076917047159928</v>
+        <v>0.4374079292756606</v>
       </c>
       <c r="AG12">
-        <v>0.4892617602966762</v>
+        <v>0.4118657119265776</v>
       </c>
       <c r="AH12">
-        <v>0.470831815877358</v>
+        <v>0.4118657119265776</v>
       </c>
       <c r="AI12">
-        <v>0.452401871458039</v>
+        <v>0.4118657119265776</v>
       </c>
       <c r="AJ12">
-        <v>0.45240187145803</v>
+        <v>0.4118657119265776</v>
       </c>
       <c r="AK12">
-        <v>0.4524018714580233</v>
+        <v>0.4118657119265776</v>
       </c>
       <c r="AL12">
-        <v>0.4524018714580173</v>
+        <v>0.4118657119265776</v>
       </c>
       <c r="AM12">
-        <v>0.4524018714580132</v>
+        <v>0.4118657119265776</v>
       </c>
       <c r="AN12">
-        <v>0.4524018714580132</v>
+        <v>0.3833999768374609</v>
       </c>
       <c r="AO12">
-        <v>0.4524018714580132</v>
+        <v>0.3549342417483441</v>
       </c>
       <c r="AP12">
-        <v>0.4524018714580025</v>
+        <v>0.3264685066592273</v>
       </c>
       <c r="AQ12">
-        <v>0.452401871458</v>
+        <v>0.3264685066592273</v>
       </c>
       <c r="AR12">
-        <v>0.4524018714579967</v>
+        <v>0.3264685066592273</v>
       </c>
       <c r="AS12">
-        <v>0.4524018714579926</v>
+        <v>0.3264685066592273</v>
       </c>
       <c r="AT12">
-        <v>0.4524018714579882</v>
+        <v>0.3264685066592273</v>
       </c>
       <c r="AU12">
-        <v>0.4490210096025617</v>
+        <v>0.3264685066592273</v>
       </c>
       <c r="AV12">
-        <v>0.4456401477471354</v>
+        <v>0.3264685066592273</v>
       </c>
       <c r="AW12">
-        <v>0.4422592858917088</v>
+        <v>0.3264685066592273</v>
       </c>
       <c r="AX12">
-        <v>0.4388784240362827</v>
+        <v>0.3264685066592273</v>
       </c>
       <c r="AY12">
-        <v>0.4354975621808558</v>
+        <v>0.3264685066592273</v>
       </c>
       <c r="AZ12">
-        <v>0.4321167003254264</v>
+        <v>0.3264685066592273</v>
       </c>
       <c r="BA12">
-        <v>0.4287358384699972</v>
+        <v>0.3264685066592273</v>
       </c>
       <c r="BB12">
-        <v>0.4287358384699972</v>
+        <v>0.3264685066592273</v>
       </c>
       <c r="BC12">
-        <v>0.4287358384699972</v>
+        <v>0.2937088277125853</v>
       </c>
       <c r="BD12">
-        <v>0.4287358384699972</v>
+        <v>0.2609491487659433</v>
       </c>
       <c r="BE12">
-        <v>0.3918006349753577</v>
+        <v>0.2609491487659433</v>
       </c>
       <c r="BF12">
-        <v>0.3548654314807181</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BG12">
-        <v>0.3548654314807181</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BH12">
-        <v>0.3548654314807181</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BI12">
-        <v>0.3548654314807181</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BJ12">
-        <v>0.3548654314807181</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BK12">
-        <v>0.3548654314807181</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BL12">
-        <v>0.3548654314807181</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BM12">
-        <v>0.3548654314807181</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BN12">
-        <v>0.3548654314807181</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BO12">
-        <v>0.3548654314807181</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BP12">
-        <v>0.3174933671526421</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BQ12">
-        <v>0.2801213028245661</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BR12">
-        <v>0.2801213028245661</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BS12">
-        <v>0.2801213028245661</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BT12">
-        <v>0.2801213028245661</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BU12">
-        <v>0.2801213028245661</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BV12">
-        <v>0.2801213028245661</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BW12">
-        <v>0.2801213028245661</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BX12">
-        <v>0.2433535055551033</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BY12">
-        <v>0.2065857082856404</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="BZ12">
-        <v>0.2065857082856404</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="CA12">
-        <v>0.2065857082856404</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="CB12">
-        <v>0.2065857082856404</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="CC12">
-        <v>0.2065857082856404</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="CD12">
-        <v>0.2065857082856404</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="CE12">
-        <v>0.2065857082856404</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="CF12">
-        <v>0.2065857082856404</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="CG12">
-        <v>0.2065857082856404</v>
+        <v>0.2253807544926562</v>
       </c>
       <c r="CH12">
-        <v>0.2065857082856404</v>
+        <v>0.2226192612797028</v>
       </c>
       <c r="CI12">
-        <v>0.2065857082856404</v>
+        <v>0.2198577680667494</v>
       </c>
       <c r="CJ12">
-        <v>0.2065857082856405</v>
+        <v>0.2198577680667494</v>
       </c>
       <c r="CK12">
-        <v>0.2065857082856405</v>
+        <v>0.2198577680667494</v>
       </c>
       <c r="CL12">
-        <v>0.2065857082856405</v>
+        <v>0.2198577680667494</v>
       </c>
       <c r="CM12">
-        <v>0.2065857082856404</v>
+        <v>0.2198577680667494</v>
       </c>
       <c r="CN12">
-        <v>0.2065857082856404</v>
+        <v>0.2198577680667494</v>
       </c>
       <c r="CO12">
-        <v>0.2665857082856404</v>
+        <v>0.2198577680667494</v>
       </c>
       <c r="CP12">
-        <v>0.2336431407186057</v>
+        <v>0.2198577680667494</v>
       </c>
       <c r="CQ12">
-        <v>0.200700573151571</v>
+        <v>0.2198577680667494</v>
       </c>
       <c r="CR12">
-        <v>0.200700573151571</v>
+        <v>0.2198577680667494</v>
       </c>
       <c r="CS12">
-        <v>0.200700573151571</v>
+        <v>0.2198577680667494</v>
       </c>
     </row>
     <row r="13" spans="1:97">
@@ -5162,10 +5165,10 @@
         <v>0.2</v>
       </c>
       <c r="C13">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="D13">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="E13">
         <v>0.26</v>
@@ -5177,37 +5180,37 @@
         <v>0.26</v>
       </c>
       <c r="H13">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="I13">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="J13">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="K13">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="L13">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="M13">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="N13">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="O13">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="P13">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="Q13">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="R13">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="S13">
         <v>0.5</v>
@@ -5216,235 +5219,235 @@
         <v>0.5</v>
       </c>
       <c r="U13">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="V13">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="W13">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="X13">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="Y13">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="Z13">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="AA13">
-        <v>0.62</v>
+        <v>0.4811761303758739</v>
       </c>
       <c r="AB13">
-        <v>0.62</v>
+        <v>0.4623522607517479</v>
       </c>
       <c r="AC13">
-        <v>0.6017424237088689</v>
+        <v>0.4435283911276218</v>
       </c>
       <c r="AD13">
-        <v>0.5834848474177379</v>
+        <v>0.4247045215034957</v>
       </c>
       <c r="AE13">
-        <v>0.5652272711266066</v>
+        <v>0.4093858324055403</v>
       </c>
       <c r="AF13">
-        <v>0.5469696948354755</v>
+        <v>0.3940671433075849</v>
       </c>
       <c r="AG13">
-        <v>0.5257481787608352</v>
+        <v>0.3787484542096295</v>
       </c>
       <c r="AH13">
-        <v>0.5045266626861949</v>
+        <v>0.3634297651116741</v>
       </c>
       <c r="AI13">
-        <v>0.4833051466115546</v>
+        <v>0.3481110760137187</v>
       </c>
       <c r="AJ13">
-        <v>0.4620836305369143</v>
+        <v>0.3481110760137187</v>
       </c>
       <c r="AK13">
-        <v>0.4455827604855617</v>
+        <v>0.3481110760137187</v>
       </c>
       <c r="AL13">
-        <v>0.4290818904342091</v>
+        <v>0.3481110760137187</v>
       </c>
       <c r="AM13">
-        <v>0.4125810203828565</v>
+        <v>0.3481110760137187</v>
       </c>
       <c r="AN13">
-        <v>0.4125810203828565</v>
+        <v>0.3481110760137187</v>
       </c>
       <c r="AO13">
-        <v>0.4125810203828565</v>
+        <v>0.3481110760137187</v>
       </c>
       <c r="AP13">
-        <v>0.4125810203828565</v>
+        <v>0.3481110760137187</v>
       </c>
       <c r="AQ13">
-        <v>0.4125810203828565</v>
+        <v>0.3481110760137187</v>
       </c>
       <c r="AR13">
-        <v>0.4125810203828565</v>
+        <v>0.3481110760137187</v>
       </c>
       <c r="AS13">
-        <v>0.4125810203828565</v>
+        <v>0.3481110760137187</v>
       </c>
       <c r="AT13">
-        <v>0.4125810203828565</v>
+        <v>0.3481110760137187</v>
       </c>
       <c r="AU13">
-        <v>0.4125810203828565</v>
+        <v>0.3481110760137187</v>
       </c>
       <c r="AV13">
-        <v>0.4125810203828565</v>
+        <v>0.3481110760137187</v>
       </c>
       <c r="AW13">
-        <v>0.4125810203828565</v>
+        <v>0.3481110760137187</v>
       </c>
       <c r="AX13">
-        <v>0.4125810203828565</v>
+        <v>0.3481110760137187</v>
       </c>
       <c r="AY13">
-        <v>0.4125810203828565</v>
+        <v>0.3251876515865195</v>
       </c>
       <c r="AZ13">
-        <v>0.3810502501249827</v>
+        <v>0.3022642271593202</v>
       </c>
       <c r="BA13">
-        <v>0.3810502501249827</v>
+        <v>0.279340802732121</v>
       </c>
       <c r="BB13">
-        <v>0.3810502501249827</v>
+        <v>0.279340802732121</v>
       </c>
       <c r="BC13">
-        <v>0.3810502501249827</v>
+        <v>0.279340802732121</v>
       </c>
       <c r="BD13">
-        <v>0.3810502501249827</v>
+        <v>0.279340802732121</v>
       </c>
       <c r="BE13">
-        <v>0.3810502501249827</v>
+        <v>0.279340802732121</v>
       </c>
       <c r="BF13">
-        <v>0.3810502501249827</v>
+        <v>0.279340802732121</v>
       </c>
       <c r="BG13">
-        <v>0.3810502501249827</v>
+        <v>0.279340802732121</v>
       </c>
       <c r="BH13">
-        <v>0.3810502501249827</v>
+        <v>0.279340802732121</v>
       </c>
       <c r="BI13">
-        <v>0.3810502501249827</v>
+        <v>0.2418496593983724</v>
       </c>
       <c r="BJ13">
-        <v>0.3810502501249827</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="BK13">
-        <v>0.3810502501249827</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="BL13">
-        <v>0.3810502501249827</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="BM13">
-        <v>0.3624690008962941</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="BN13">
-        <v>0.279920789179224</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="BO13">
-        <v>0.279920789179224</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="BP13">
-        <v>0.279920789179224</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="BQ13">
-        <v>0.279920789179224</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="BR13">
-        <v>0.279920789179224</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="BS13">
-        <v>0.279920789179224</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="BT13">
-        <v>0.279920789179224</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="BU13">
-        <v>0.279920789179224</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="BV13">
-        <v>0.279920789179224</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="BW13">
-        <v>0.279920789179224</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="BX13">
-        <v>0.279920789179224</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="BY13">
-        <v>0.279920789179224</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="BZ13">
-        <v>0.279920789179224</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CA13">
-        <v>0.3399207891792242</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CB13">
-        <v>0.3399207891792242</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CC13">
-        <v>0.3399207891792242</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CD13">
-        <v>0.3399207891792242</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CE13">
-        <v>0.3399207891792242</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CF13">
-        <v>0.3399207891792242</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CG13">
-        <v>0.3175984269010376</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CH13">
-        <v>0.295276064622851</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CI13">
-        <v>0.2730255215727009</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CJ13">
-        <v>0.2507749785225509</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CK13">
-        <v>0.2507749785225509</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CL13">
-        <v>0.2507749785225509</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CM13">
-        <v>0.2270638285986774</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CN13">
-        <v>0.2033526786748037</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CO13">
-        <v>0.2033526786748037</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CP13">
-        <v>0.2033526786748037</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CQ13">
-        <v>0.2033526786748037</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CR13">
-        <v>0.2033526786748037</v>
+        <v>0.2043585160646238</v>
       </c>
       <c r="CS13">
-        <v>0.2033526786748037</v>
+        <v>0.2043585160646238</v>
       </c>
     </row>
     <row r="14" spans="1:97">
@@ -5461,37 +5464,37 @@
         <v>0.26</v>
       </c>
       <c r="E14">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="F14">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="G14">
         <v>0.32</v>
       </c>
       <c r="H14">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="I14">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="J14">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="K14">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="L14">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="M14">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="N14">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="O14">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="P14">
         <v>0.44</v>
@@ -5509,235 +5512,235 @@
         <v>0.5</v>
       </c>
       <c r="U14">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V14">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="W14">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="X14">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="Y14">
-        <v>0.4783365331301955</v>
+        <v>0.62</v>
       </c>
       <c r="Z14">
-        <v>0.4566730662603909</v>
+        <v>0.68</v>
       </c>
       <c r="AA14">
-        <v>0.4350095993905865</v>
+        <v>0.68</v>
       </c>
       <c r="AB14">
-        <v>0.413346132520782</v>
+        <v>0.68</v>
       </c>
       <c r="AC14">
-        <v>0.4733461325207819</v>
+        <v>0.68</v>
       </c>
       <c r="AD14">
-        <v>0.4577758290668857</v>
+        <v>0.6648658210516531</v>
       </c>
       <c r="AE14">
-        <v>0.4422055256129895</v>
+        <v>0.6497316421033053</v>
       </c>
       <c r="AF14">
-        <v>0.4266352221590933</v>
+        <v>0.6345974631549574</v>
       </c>
       <c r="AG14">
-        <v>0.4110649187051971</v>
+        <v>0.6194632842066096</v>
       </c>
       <c r="AH14">
-        <v>0.3954946152513009</v>
+        <v>0.6043291052582618</v>
       </c>
       <c r="AI14">
-        <v>0.3954946152513009</v>
+        <v>0.5891949263099139</v>
       </c>
       <c r="AJ14">
-        <v>0.3954946152513009</v>
+        <v>0.5891949263099139</v>
       </c>
       <c r="AK14">
-        <v>0.3954946152513009</v>
+        <v>0.5891949263099139</v>
       </c>
       <c r="AL14">
-        <v>0.3954946152513009</v>
+        <v>0.5891949263099139</v>
       </c>
       <c r="AM14">
-        <v>0.3954946152513009</v>
+        <v>0.5891949263099139</v>
       </c>
       <c r="AN14">
-        <v>0.3670288801621842</v>
+        <v>0.5640545242626964</v>
       </c>
       <c r="AO14">
-        <v>0.3385631450730674</v>
+        <v>0.5389141222154789</v>
       </c>
       <c r="AP14">
-        <v>0.3100974099839506</v>
+        <v>0.5389141222154789</v>
       </c>
       <c r="AQ14">
-        <v>0.3100974099839506</v>
+        <v>0.5389141222154789</v>
       </c>
       <c r="AR14">
-        <v>0.3100974099839506</v>
+        <v>0.5110559753777918</v>
       </c>
       <c r="AS14">
-        <v>0.3100974099839506</v>
+        <v>0.4831978285401049</v>
       </c>
       <c r="AT14">
-        <v>0.3100974099839506</v>
+        <v>0.4553396817024179</v>
       </c>
       <c r="AU14">
-        <v>0.3100974099839506</v>
+        <v>0.4553396817024179</v>
       </c>
       <c r="AV14">
-        <v>0.3100974099839506</v>
+        <v>0.4553396817024179</v>
       </c>
       <c r="AW14">
-        <v>0.3100974099839506</v>
+        <v>0.4553396817024179</v>
       </c>
       <c r="AX14">
-        <v>0.3100974099839506</v>
+        <v>0.4553396817024179</v>
       </c>
       <c r="AY14">
-        <v>0.3100974099839506</v>
+        <v>0.4553396817024179</v>
       </c>
       <c r="AZ14">
-        <v>0.3100974099839506</v>
+        <v>0.4553396817024179</v>
       </c>
       <c r="BA14">
-        <v>0.3100974099839506</v>
+        <v>0.4553396817024179</v>
       </c>
       <c r="BB14">
-        <v>0.3100974099839506</v>
+        <v>0.4553396817024179</v>
       </c>
       <c r="BC14">
-        <v>0.3100974099839506</v>
+        <v>0.4553396817024179</v>
       </c>
       <c r="BD14">
-        <v>0.3100974099839506</v>
+        <v>0.4553396817024179</v>
       </c>
       <c r="BE14">
-        <v>0.3100974099839506</v>
+        <v>0.4553396817024179</v>
       </c>
       <c r="BF14">
-        <v>0.3100974099839506</v>
+        <v>0.4553396817024179</v>
       </c>
       <c r="BG14">
-        <v>0.3100974099839506</v>
+        <v>0.4286196888114345</v>
       </c>
       <c r="BH14">
-        <v>0.3100974099839506</v>
+        <v>0.401899695920451</v>
       </c>
       <c r="BI14">
-        <v>0.3100974099839506</v>
+        <v>0.401899695920451</v>
       </c>
       <c r="BJ14">
-        <v>0.3100974099839506</v>
+        <v>0.401899695920451</v>
       </c>
       <c r="BK14">
-        <v>0.3100974099839506</v>
+        <v>0.401899695920451</v>
       </c>
       <c r="BL14">
-        <v>0.3100974099839506</v>
+        <v>0.401899695920451</v>
       </c>
       <c r="BM14">
-        <v>0.2937823180503031</v>
+        <v>0.401899695920451</v>
       </c>
       <c r="BN14">
-        <v>0.2774672261166555</v>
+        <v>0.3761331828449474</v>
       </c>
       <c r="BO14">
-        <v>0.2774672261166555</v>
+        <v>0.3503666697694438</v>
       </c>
       <c r="BP14">
-        <v>0.2774672261166555</v>
+        <v>0.3221911811006466</v>
       </c>
       <c r="BQ14">
-        <v>0.2774672261166555</v>
+        <v>0.2940156924318495</v>
       </c>
       <c r="BR14">
-        <v>0.2774672261166555</v>
+        <v>0.2658402037630523</v>
       </c>
       <c r="BS14">
-        <v>0.2774672261166555</v>
+        <v>0.2658402037630523</v>
       </c>
       <c r="BT14">
-        <v>0.2774672261166555</v>
+        <v>0.2371877012444518</v>
       </c>
       <c r="BU14">
-        <v>0.2774672261166555</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="BV14">
-        <v>0.2774672261166555</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="BW14">
-        <v>0.2774672261166555</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="BX14">
-        <v>0.2454414793173712</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="BY14">
-        <v>0.2134157325180868</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="BZ14">
-        <v>0.210684378425173</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CA14">
-        <v>0.2079530243322591</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CB14">
-        <v>0.2079530243322591</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CC14">
-        <v>0.2079530243322591</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CD14">
-        <v>0.2079530243322591</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CE14">
-        <v>0.2679530243322591</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CF14">
-        <v>0.2351766982002106</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CG14">
-        <v>0.202400372068162</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CH14">
-        <v>0.202400372068162</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CI14">
-        <v>0.202400372068162</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CJ14">
-        <v>0.202400372068162</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CK14">
-        <v>0.202400372068162</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CL14">
-        <v>0.202400372068162</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CM14">
-        <v>0.202400372068162</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CN14">
-        <v>0.202400372068162</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CO14">
-        <v>0.202400372068162</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CP14">
-        <v>0.202400372068162</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CQ14">
-        <v>0.202400372068162</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CR14">
-        <v>0.202400372068162</v>
+        <v>0.2085351987258514</v>
       </c>
       <c r="CS14">
-        <v>0.202400372068162</v>
+        <v>0.2085351987258514</v>
       </c>
     </row>
     <row r="15" spans="1:97">
@@ -5751,7 +5754,7 @@
         <v>0.26</v>
       </c>
       <c r="D15">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="E15">
         <v>0.32</v>
@@ -5760,22 +5763,22 @@
         <v>0.32</v>
       </c>
       <c r="G15">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="H15">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="I15">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="J15">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="K15">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="L15">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="M15">
         <v>0.44</v>
@@ -5790,247 +5793,247 @@
         <v>0.44</v>
       </c>
       <c r="Q15">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="R15">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="S15">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="T15">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="U15">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="V15">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W15">
-        <v>0.5600000000000001</v>
+        <v>0.5378754765360211</v>
       </c>
       <c r="X15">
-        <v>0.5400912170101594</v>
+        <v>0.5157509530720421</v>
       </c>
       <c r="Y15">
-        <v>0.5201824340203188</v>
+        <v>0.4936264296080631</v>
       </c>
       <c r="Z15">
-        <v>0.5002736510304783</v>
+        <v>0.4715019061440842</v>
       </c>
       <c r="AA15">
-        <v>0.4803648680406377</v>
+        <v>0.5315019061440842</v>
       </c>
       <c r="AB15">
-        <v>0.460456085050797</v>
+        <v>0.5315019061440842</v>
       </c>
       <c r="AC15">
-        <v>0.520456085050797</v>
+        <v>0.5315019061440842</v>
       </c>
       <c r="AD15">
-        <v>0.5053219061024492</v>
+        <v>0.5315019061440842</v>
       </c>
       <c r="AE15">
-        <v>0.4901877271541014</v>
+        <v>0.5315019061440842</v>
       </c>
       <c r="AF15">
-        <v>0.4750535482057535</v>
+        <v>0.5315019061440842</v>
       </c>
       <c r="AG15">
-        <v>0.4599193692574056</v>
+        <v>0.5315019061440842</v>
       </c>
       <c r="AH15">
-        <v>0.4447851903090577</v>
+        <v>0.5315019061440842</v>
       </c>
       <c r="AI15">
-        <v>0.4296510113607098</v>
+        <v>0.5315019061440842</v>
       </c>
       <c r="AJ15">
-        <v>0.4296510113607098</v>
+        <v>0.5315019061440842</v>
       </c>
       <c r="AK15">
-        <v>0.4296510113607098</v>
+        <v>0.5315019061440842</v>
       </c>
       <c r="AL15">
-        <v>0.42965101136071</v>
+        <v>0.51273511419416</v>
       </c>
       <c r="AM15">
-        <v>0.42965101136071</v>
+        <v>0.4939683222442358</v>
       </c>
       <c r="AN15">
-        <v>0.42965101136071</v>
+        <v>0.4752015302943116</v>
       </c>
       <c r="AO15">
-        <v>0.42965101136071</v>
+        <v>0.4564347383443874</v>
       </c>
       <c r="AP15">
-        <v>0.42965101136071</v>
+        <v>0.4564347383443874</v>
       </c>
       <c r="AQ15">
-        <v>0.42965101136071</v>
+        <v>0.4564347383443874</v>
       </c>
       <c r="AR15">
-        <v>0.42965101136071</v>
+        <v>0.4564347383443874</v>
       </c>
       <c r="AS15">
-        <v>0.42965101136071</v>
+        <v>0.4564347383443874</v>
       </c>
       <c r="AT15">
-        <v>0.42965101136071</v>
+        <v>0.4564347383443874</v>
       </c>
       <c r="AU15">
-        <v>0.42965101136071</v>
+        <v>0.4564347383443874</v>
       </c>
       <c r="AV15">
-        <v>0.42965101136071</v>
+        <v>0.4564347383443874</v>
       </c>
       <c r="AW15">
-        <v>0.42965101136071</v>
+        <v>0.4564347383443874</v>
       </c>
       <c r="AX15">
-        <v>0.42965101136071</v>
+        <v>0.4564347383443874</v>
       </c>
       <c r="AY15">
-        <v>0.42965101136071</v>
+        <v>0.4564347383443874</v>
       </c>
       <c r="AZ15">
-        <v>0.42965101136071</v>
+        <v>0.4564347383443874</v>
       </c>
       <c r="BA15">
-        <v>0.4081552407644353</v>
+        <v>0.4349389677481126</v>
       </c>
       <c r="BB15">
-        <v>0.3866594701681606</v>
+        <v>0.4134431971518378</v>
       </c>
       <c r="BC15">
-        <v>0.3866594701681606</v>
+        <v>0.4134431971518378</v>
       </c>
       <c r="BD15">
-        <v>0.3866594701681606</v>
+        <v>0.4134431971518378</v>
       </c>
       <c r="BE15">
-        <v>0.3590982651866109</v>
+        <v>0.4134431971518378</v>
       </c>
       <c r="BF15">
-        <v>0.3315370602050611</v>
+        <v>0.3833227870562395</v>
       </c>
       <c r="BG15">
-        <v>0.3315370602050611</v>
+        <v>0.3532023769606412</v>
       </c>
       <c r="BH15">
-        <v>0.3315370602050611</v>
+        <v>0.3532023769606412</v>
       </c>
       <c r="BI15">
-        <v>0.3315370602050611</v>
+        <v>0.3532023769606412</v>
       </c>
       <c r="BJ15">
-        <v>0.3315370602050611</v>
+        <v>0.3532023769606412</v>
       </c>
       <c r="BK15">
-        <v>0.3315370602050611</v>
+        <v>0.3373641209554557</v>
       </c>
       <c r="BL15">
-        <v>0.3315370602050611</v>
+        <v>0.3215258649502702</v>
       </c>
       <c r="BM15">
-        <v>0.3315370602050611</v>
+        <v>0.3215258649502702</v>
       </c>
       <c r="BN15">
-        <v>0.3315370602050611</v>
+        <v>0.3215258649502702</v>
       </c>
       <c r="BO15">
-        <v>0.3315370602050611</v>
+        <v>0.3044527121113758</v>
       </c>
       <c r="BP15">
-        <v>0.3315370602050611</v>
+        <v>0.2873795592724812</v>
       </c>
       <c r="BQ15">
-        <v>0.3315370602050611</v>
+        <v>0.2873795592724812</v>
       </c>
       <c r="BR15">
-        <v>0.3315370602050611</v>
+        <v>0.2873795592724812</v>
       </c>
       <c r="BS15">
-        <v>0.3315370602050611</v>
+        <v>0.2873795592724812</v>
       </c>
       <c r="BT15">
-        <v>0.3315370602050611</v>
+        <v>0.2596055848992115</v>
       </c>
       <c r="BU15">
-        <v>0.2958492082358995</v>
+        <v>0.2318316105259417</v>
       </c>
       <c r="BV15">
-        <v>0.2601613562667379</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="BW15">
-        <v>0.2601613562667379</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="BX15">
-        <v>0.2601613562667379</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="BY15">
-        <v>0.2601613562667379</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="BZ15">
-        <v>0.2601613562667379</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CA15">
-        <v>0.2601613562667378</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CB15">
-        <v>0.230118729819394</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CC15">
-        <v>0.2000761033720501</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CD15">
-        <v>0.2000761033720501</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CE15">
-        <v>0.2000761033720501</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CF15">
-        <v>0.2000761033720501</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CG15">
-        <v>0.2000761033720501</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CH15">
-        <v>0.2000761033720501</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CI15">
-        <v>0.2000761033720501</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CJ15">
-        <v>0.2000761033720501</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CK15">
-        <v>0.2000761033720501</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CL15">
-        <v>0.2000761033720501</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CM15">
-        <v>0.2000761033720501</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CN15">
-        <v>0.2000761033720501</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CO15">
-        <v>0.2000761033720501</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CP15">
-        <v>0.2000761033720501</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CQ15">
-        <v>0.2000761033720501</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CR15">
-        <v>0.2000761033720501</v>
+        <v>0.204057636152672</v>
       </c>
       <c r="CS15">
-        <v>0.2000761033720501</v>
+        <v>0.204057636152672</v>
       </c>
     </row>
     <row r="16" spans="1:97">
@@ -6080,25 +6083,25 @@
         <v>0.32</v>
       </c>
       <c r="P16">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="Q16">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="R16">
         <v>0.38</v>
       </c>
       <c r="S16">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="T16">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="U16">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="V16">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="W16">
         <v>0.5</v>
@@ -6116,214 +6119,214 @@
         <v>0.5</v>
       </c>
       <c r="AB16">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AC16">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="AD16">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="AE16">
-        <v>0.6046813109020445</v>
+        <v>0.4815700555806904</v>
       </c>
       <c r="AF16">
-        <v>0.5893626218040892</v>
+        <v>0.4631401111613822</v>
       </c>
       <c r="AG16">
-        <v>0.5740439327061337</v>
+        <v>0.444710166742074</v>
       </c>
       <c r="AH16">
-        <v>0.5587252436081783</v>
+        <v>0.4262802223227657</v>
       </c>
       <c r="AI16">
-        <v>0.5434065545102229</v>
+        <v>0.4078502779034575</v>
       </c>
       <c r="AJ16">
-        <v>0.5253396266456015</v>
+        <v>0.4078502779034575</v>
       </c>
       <c r="AK16">
-        <v>0.5072726987809802</v>
+        <v>0.4078502779034575</v>
       </c>
       <c r="AL16">
-        <v>0.4892057709163589</v>
+        <v>0.4078502779034575</v>
       </c>
       <c r="AM16">
-        <v>0.4711388430517376</v>
+        <v>0.4078502779034575</v>
       </c>
       <c r="AN16">
-        <v>0.4530719151871163</v>
+        <v>0.4078502779034575</v>
       </c>
       <c r="AO16">
-        <v>0.4530719151871163</v>
+        <v>0.4078502779034575</v>
       </c>
       <c r="AP16">
-        <v>0.4530719151871163</v>
+        <v>0.4078502779034575</v>
       </c>
       <c r="AQ16">
-        <v>0.4530719151871163</v>
+        <v>0.4078502779034575</v>
       </c>
       <c r="AR16">
-        <v>0.4530719151871163</v>
+        <v>0.4078502779034575</v>
       </c>
       <c r="AS16">
-        <v>0.4530719151871163</v>
+        <v>0.4078502779034575</v>
       </c>
       <c r="AT16">
-        <v>0.4530719151871163</v>
+        <v>0.4033336254315714</v>
       </c>
       <c r="AU16">
-        <v>0.4530719151871163</v>
+        <v>0.3988169729596853</v>
       </c>
       <c r="AV16">
-        <v>0.4530719151871163</v>
+        <v>0.3943003204877991</v>
       </c>
       <c r="AW16">
-        <v>0.4530719151871163</v>
+        <v>0.389783668015913</v>
       </c>
       <c r="AX16">
-        <v>0.4530719151871163</v>
+        <v>0.3852670155440269</v>
       </c>
       <c r="AY16">
-        <v>0.4530719151871163</v>
+        <v>0.3852670155440269</v>
       </c>
       <c r="AZ16">
-        <v>0.4530719151871163</v>
+        <v>0.3852670155440269</v>
       </c>
       <c r="BA16">
-        <v>0.4530719151871163</v>
+        <v>0.3852670155440269</v>
       </c>
       <c r="BB16">
-        <v>0.4530719151871163</v>
+        <v>0.3852670155440269</v>
       </c>
       <c r="BC16">
-        <v>0.4530719151871163</v>
+        <v>0.3852670155440269</v>
       </c>
       <c r="BD16">
-        <v>0.4204789825749758</v>
+        <v>0.3852670155440271</v>
       </c>
       <c r="BE16">
-        <v>0.3878860499628353</v>
+        <v>0.3852670155440271</v>
       </c>
       <c r="BF16">
-        <v>0.3552931173506948</v>
+        <v>0.3852670155440271</v>
       </c>
       <c r="BG16">
-        <v>0.3552931173506948</v>
+        <v>0.3852670155440271</v>
       </c>
       <c r="BH16">
-        <v>0.3552931173506948</v>
+        <v>0.3567162942635915</v>
       </c>
       <c r="BI16">
-        <v>0.3552931173506948</v>
+        <v>0.3281655729831559</v>
       </c>
       <c r="BJ16">
-        <v>0.3208484650103637</v>
+        <v>0.3281655729831559</v>
       </c>
       <c r="BK16">
-        <v>0.2864038126700325</v>
+        <v>0.3281655729831559</v>
       </c>
       <c r="BL16">
-        <v>0.2864038126700325</v>
+        <v>0.3041548717879045</v>
       </c>
       <c r="BM16">
-        <v>0.2864038126700325</v>
+        <v>0.2801441705926532</v>
       </c>
       <c r="BN16">
-        <v>0.2864038126700325</v>
+        <v>0.2561334693974019</v>
       </c>
       <c r="BO16">
-        <v>0.2864038126700325</v>
+        <v>0.2561334693974019</v>
       </c>
       <c r="BP16">
-        <v>0.2864038126700325</v>
+        <v>0.2561334693974019</v>
       </c>
       <c r="BQ16">
-        <v>0.2864038126700325</v>
+        <v>0.2561334693974019</v>
       </c>
       <c r="BR16">
-        <v>0.2864038126700325</v>
+        <v>0.2561334693974019</v>
       </c>
       <c r="BS16">
-        <v>0.2864038126700325</v>
+        <v>0.2561334693974019</v>
       </c>
       <c r="BT16">
-        <v>0.2864038126700325</v>
+        <v>0.2561334693974019</v>
       </c>
       <c r="BU16">
-        <v>0.2864038126700325</v>
+        <v>0.2561334693974019</v>
       </c>
       <c r="BV16">
-        <v>0.2864038126700325</v>
+        <v>0.2561334693974019</v>
       </c>
       <c r="BW16">
-        <v>0.2864038126700325</v>
+        <v>0.2561334693974019</v>
       </c>
       <c r="BX16">
-        <v>0.2864038126700325</v>
+        <v>0.2561334693974019</v>
       </c>
       <c r="BY16">
-        <v>0.2864038126700325</v>
+        <v>0.2315790004819591</v>
       </c>
       <c r="BZ16">
-        <v>0.2864038126700325</v>
+        <v>0.2915790004819591</v>
       </c>
       <c r="CA16">
-        <v>0.2864038126700325</v>
+        <v>0.2705241096811035</v>
       </c>
       <c r="CB16">
-        <v>0.2864038126700325</v>
+        <v>0.2494692188802475</v>
       </c>
       <c r="CC16">
-        <v>0.2694262888836933</v>
+        <v>0.2494692188802475</v>
       </c>
       <c r="CD16">
-        <v>0.2694262888836933</v>
+        <v>0.2494692188802475</v>
       </c>
       <c r="CE16">
-        <v>0.2694262888836933</v>
+        <v>0.2494692188802475</v>
       </c>
       <c r="CF16">
-        <v>0.2694262888836933</v>
+        <v>0.2494692188802475</v>
       </c>
       <c r="CG16">
-        <v>0.2694262888836933</v>
+        <v>0.2494692188802475</v>
       </c>
       <c r="CH16">
-        <v>0.2694262888836933</v>
+        <v>0.2494692188802475</v>
       </c>
       <c r="CI16">
-        <v>0.2694262888836933</v>
+        <v>0.2494692188802475</v>
       </c>
       <c r="CJ16">
-        <v>0.2694262888836933</v>
+        <v>0.2494692188802473</v>
       </c>
       <c r="CK16">
-        <v>0.2694262888836933</v>
+        <v>0.2494692188802473</v>
       </c>
       <c r="CL16">
-        <v>0.2694262888836933</v>
+        <v>0.2494692188802473</v>
       </c>
       <c r="CM16">
-        <v>0.2694262888836933</v>
+        <v>0.2257580689563737</v>
       </c>
       <c r="CN16">
-        <v>0.2364837213166586</v>
+        <v>0.2020469190325001</v>
       </c>
       <c r="CO16">
-        <v>0.2035411537496239</v>
+        <v>0.2020469190325001</v>
       </c>
       <c r="CP16">
-        <v>0.2035411537496239</v>
+        <v>0.2020469190325001</v>
       </c>
       <c r="CQ16">
-        <v>0.2035411537496239</v>
+        <v>0.2020469190325001</v>
       </c>
       <c r="CR16">
-        <v>0.2035411537496239</v>
+        <v>0.2020469190325001</v>
       </c>
       <c r="CS16">
-        <v>0.2035411537496239</v>
+        <v>0.2020469190325001</v>
       </c>
     </row>
     <row r="17" spans="1:97">
@@ -6340,55 +6343,55 @@
         <v>0.2</v>
       </c>
       <c r="E17">
+        <v>0.2</v>
+      </c>
+      <c r="F17">
+        <v>0.2</v>
+      </c>
+      <c r="G17">
+        <v>0.2</v>
+      </c>
+      <c r="H17">
+        <v>0.2</v>
+      </c>
+      <c r="I17">
         <v>0.26</v>
       </c>
-      <c r="F17">
+      <c r="J17">
         <v>0.26</v>
       </c>
-      <c r="G17">
+      <c r="K17">
         <v>0.26</v>
       </c>
-      <c r="H17">
+      <c r="L17">
         <v>0.26</v>
       </c>
-      <c r="I17">
+      <c r="M17">
+        <v>0.26</v>
+      </c>
+      <c r="N17">
+        <v>0.26</v>
+      </c>
+      <c r="O17">
         <v>0.32</v>
       </c>
-      <c r="J17">
+      <c r="P17">
         <v>0.32</v>
       </c>
-      <c r="K17">
+      <c r="Q17">
         <v>0.32</v>
       </c>
-      <c r="L17">
-        <v>0.38</v>
-      </c>
-      <c r="M17">
-        <v>0.38</v>
-      </c>
-      <c r="N17">
-        <v>0.38</v>
-      </c>
-      <c r="O17">
-        <v>0.38</v>
-      </c>
-      <c r="P17">
-        <v>0.44</v>
-      </c>
-      <c r="Q17">
-        <v>0.44</v>
-      </c>
       <c r="R17">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="S17">
         <v>0.44</v>
       </c>
       <c r="T17">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="U17">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="V17">
         <v>0.5</v>
@@ -6400,223 +6403,223 @@
         <v>0.5</v>
       </c>
       <c r="Y17">
-        <v>0.5600000000000001</v>
+        <v>0.4783365331301933</v>
       </c>
       <c r="Z17">
-        <v>0.62</v>
+        <v>0.4566730662603888</v>
       </c>
       <c r="AA17">
-        <v>0.6011761303758711</v>
+        <v>0.4350095993905843</v>
       </c>
       <c r="AB17">
-        <v>0.5823522607517451</v>
+        <v>0.4133461325207798</v>
       </c>
       <c r="AC17">
-        <v>0.563528391127619</v>
+        <v>0.3931275536447311</v>
       </c>
       <c r="AD17">
-        <v>0.5447045215034929</v>
+        <v>0.3729089747686823</v>
       </c>
       <c r="AE17">
-        <v>0.5447045215034928</v>
+        <v>0.3526903958926336</v>
       </c>
       <c r="AF17">
-        <v>0.5191623041544099</v>
+        <v>0.3366469654416295</v>
       </c>
       <c r="AG17">
-        <v>0.493620086805327</v>
+        <v>0.3206035349906253</v>
       </c>
       <c r="AH17">
-        <v>0.4742318243372201</v>
+        <v>0.3045601045396211</v>
       </c>
       <c r="AI17">
-        <v>0.4548435618691133</v>
+        <v>0.288516674088617</v>
       </c>
       <c r="AJ17">
-        <v>0.4548435618691133</v>
+        <v>0.2724732436376128</v>
       </c>
       <c r="AK17">
-        <v>0.4548435618691133</v>
+        <v>0.2724732436376128</v>
       </c>
       <c r="AL17">
-        <v>0.4548435618691133</v>
+        <v>0.2724732436376128</v>
       </c>
       <c r="AM17">
-        <v>0.4548435618691133</v>
+        <v>0.2724732436375227</v>
       </c>
       <c r="AN17">
-        <v>0.4548435618691133</v>
+        <v>0.2724732436375227</v>
       </c>
       <c r="AO17">
-        <v>0.4548435618691133</v>
+        <v>0.2724732436375227</v>
       </c>
       <c r="AP17">
-        <v>0.4548435618691133</v>
+        <v>0.2724732436375227</v>
       </c>
       <c r="AQ17">
-        <v>0.4548435618691133</v>
+        <v>0.2724732436375227</v>
       </c>
       <c r="AR17">
-        <v>0.4548435618691133</v>
+        <v>0.2724732436375227</v>
       </c>
       <c r="AS17">
-        <v>0.4548435618691133</v>
+        <v>0.2724732436375227</v>
       </c>
       <c r="AT17">
-        <v>0.4548435618691133</v>
+        <v>0.2724732436375227</v>
       </c>
       <c r="AU17">
-        <v>0.4548435618691133</v>
+        <v>0.2724732436375104</v>
       </c>
       <c r="AV17">
-        <v>0.4276709833764629</v>
+        <v>0.2724732436375104</v>
       </c>
       <c r="AW17">
-        <v>0.4004984048838123</v>
+        <v>0.2724732436375104</v>
       </c>
       <c r="AX17">
-        <v>0.3733258263911619</v>
+        <v>0.2724732436375104</v>
       </c>
       <c r="AY17">
-        <v>0.3733258263911619</v>
+        <v>0.2724732436375104</v>
       </c>
       <c r="AZ17">
-        <v>0.3733258263911619</v>
+        <v>0.2724732436375089</v>
       </c>
       <c r="BA17">
-        <v>0.3733258263911619</v>
+        <v>0.2724732436375089</v>
       </c>
       <c r="BB17">
-        <v>0.3733258263911619</v>
+        <v>0.2724732436375089</v>
       </c>
       <c r="BC17">
-        <v>0.3495156528716125</v>
+        <v>0.2724732436375089</v>
       </c>
       <c r="BD17">
-        <v>0.3257054793520632</v>
+        <v>0.2724732436375089</v>
       </c>
       <c r="BE17">
-        <v>0.3257054793520632</v>
+        <v>0.2724732436375089</v>
       </c>
       <c r="BF17">
-        <v>0.3257054793520632</v>
+        <v>0.2724732436375089</v>
       </c>
       <c r="BG17">
-        <v>0.3257054793520632</v>
+        <v>0.2724732436375089</v>
       </c>
       <c r="BH17">
-        <v>0.3257054793520632</v>
+        <v>0.2724732436375089</v>
       </c>
       <c r="BI17">
-        <v>0.3257054793520632</v>
+        <v>0.2724732436375089</v>
       </c>
       <c r="BJ17">
-        <v>0.3257054793520632</v>
+        <v>0.2724732436375089</v>
       </c>
       <c r="BK17">
-        <v>0.3257054793520632</v>
+        <v>0.2724732436375104</v>
       </c>
       <c r="BL17">
-        <v>0.2944792429091727</v>
+        <v>0.2724732436375104</v>
       </c>
       <c r="BM17">
-        <v>0.2632530064662821</v>
+        <v>0.2724732436375104</v>
       </c>
       <c r="BN17">
-        <v>0.2632530064662821</v>
+        <v>0.2724732436375104</v>
       </c>
       <c r="BO17">
-        <v>0.2632530064662821</v>
+        <v>0.2724732436375104</v>
       </c>
       <c r="BP17">
-        <v>0.2632530064662821</v>
+        <v>0.2724732436375149</v>
       </c>
       <c r="BQ17">
-        <v>0.2632530064662821</v>
+        <v>0.272473243637518</v>
       </c>
       <c r="BR17">
-        <v>0.2632530064662821</v>
+        <v>0.2724732436375201</v>
       </c>
       <c r="BS17">
-        <v>0.2632530064662821</v>
+        <v>0.2724732436375218</v>
       </c>
       <c r="BT17">
-        <v>0.2632530064662821</v>
+        <v>0.2724732436375237</v>
       </c>
       <c r="BU17">
-        <v>0.2632530064662821</v>
+        <v>0.2367853916683621</v>
       </c>
       <c r="BV17">
-        <v>0.2345495217037307</v>
+        <v>0.2010975396992006</v>
       </c>
       <c r="BW17">
-        <v>0.2058460369411793</v>
+        <v>0.2010975396992018</v>
       </c>
       <c r="BX17">
-        <v>0.2058460369411793</v>
+        <v>0.2010975396992018</v>
       </c>
       <c r="BY17">
-        <v>0.2058460369411793</v>
+        <v>0.2010975396992018</v>
       </c>
       <c r="BZ17">
-        <v>0.2058460369411793</v>
+        <v>0.2010975396992018</v>
       </c>
       <c r="CA17">
-        <v>0.2058460369411793</v>
+        <v>0.2010975396992012</v>
       </c>
       <c r="CB17">
-        <v>0.2058460369411793</v>
+        <v>0.2010975396992012</v>
       </c>
       <c r="CC17">
-        <v>0.2058460369411793</v>
+        <v>0.2010975396992012</v>
       </c>
       <c r="CD17">
-        <v>0.2031146828482654</v>
+        <v>0.2010975396992012</v>
       </c>
       <c r="CE17">
-        <v>0.2003833287553516</v>
+        <v>0.2010975396992012</v>
       </c>
       <c r="CF17">
-        <v>0.2003833287553516</v>
+        <v>0.2010975396992012</v>
       </c>
       <c r="CG17">
-        <v>0.2003833287553516</v>
+        <v>0.2010975396992012</v>
       </c>
       <c r="CH17">
-        <v>0.2003833287553516</v>
+        <v>0.2010975396992012</v>
       </c>
       <c r="CI17">
-        <v>0.2003833287553516</v>
+        <v>0.2010975396992012</v>
       </c>
       <c r="CJ17">
-        <v>0.2003833287553516</v>
+        <v>0.2010975396992012</v>
       </c>
       <c r="CK17">
-        <v>0.2003833287553516</v>
+        <v>0.2010975396992012</v>
       </c>
       <c r="CL17">
-        <v>0.2003833287553516</v>
+        <v>0.2010975396992012</v>
       </c>
       <c r="CM17">
-        <v>0.2003833287553516</v>
+        <v>0.2010975396992012</v>
       </c>
       <c r="CN17">
-        <v>0.2003833287553516</v>
+        <v>0.2010975396992012</v>
       </c>
       <c r="CO17">
-        <v>0.2003833287553516</v>
+        <v>0.2010975396992012</v>
       </c>
       <c r="CP17">
-        <v>0.2003833287553516</v>
+        <v>0.2010975396992012</v>
       </c>
       <c r="CQ17">
-        <v>0.2003833287553516</v>
+        <v>0.2010975396992012</v>
       </c>
       <c r="CR17">
-        <v>0.2003833287553516</v>
+        <v>0.2010975396992012</v>
       </c>
       <c r="CS17">
-        <v>0.2003833287553516</v>
+        <v>0.2010975396992012</v>
       </c>
     </row>
     <row r="18" spans="1:97">
@@ -6645,55 +6648,55 @@
         <v>0.2</v>
       </c>
       <c r="I18">
+        <v>0.2</v>
+      </c>
+      <c r="J18">
+        <v>0.2</v>
+      </c>
+      <c r="K18">
         <v>0.26</v>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>0.26</v>
       </c>
-      <c r="K18">
-        <v>0.32</v>
-      </c>
-      <c r="L18">
-        <v>0.32</v>
-      </c>
       <c r="M18">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="N18">
         <v>0.32</v>
       </c>
       <c r="O18">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="P18">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="Q18">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="R18">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="S18">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="T18">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="U18">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="V18">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="W18">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="X18">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="Y18">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="Z18">
         <v>0.5</v>
@@ -6702,214 +6705,214 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AB18">
-        <v>0.5600000000000001</v>
+        <v>0.541205722703498</v>
       </c>
       <c r="AC18">
-        <v>0.5600000000000001</v>
+        <v>0.5224114454070048</v>
       </c>
       <c r="AD18">
-        <v>0.5600000000000001</v>
+        <v>0.5036171681105107</v>
       </c>
       <c r="AE18">
-        <v>0.5429309994750059</v>
+        <v>0.4848228908140172</v>
       </c>
       <c r="AF18">
-        <v>0.5258619989500116</v>
+        <v>0.4660286135175221</v>
       </c>
       <c r="AG18">
-        <v>0.5064074025989824</v>
+        <v>0.4660286135175221</v>
       </c>
       <c r="AH18">
-        <v>0.4869528062479533</v>
+        <v>0.4466403510494152</v>
       </c>
       <c r="AI18">
-        <v>0.4674982098969241</v>
+        <v>0.4272520885813084</v>
       </c>
       <c r="AJ18">
-        <v>0.4674982098969241</v>
+        <v>0.4272520885813084</v>
       </c>
       <c r="AK18">
-        <v>0.4674982098969241</v>
+        <v>0.4272520885812885</v>
       </c>
       <c r="AL18">
-        <v>0.4674982098969241</v>
+        <v>0.427252088581285</v>
       </c>
       <c r="AM18">
-        <v>0.4674982098969241</v>
+        <v>0.4272520885812814</v>
       </c>
       <c r="AN18">
-        <v>0.4423578078497066</v>
+        <v>0.4272520885812814</v>
       </c>
       <c r="AO18">
-        <v>0.4172174058024892</v>
+        <v>0.4272520885812814</v>
       </c>
       <c r="AP18">
-        <v>0.4172174058024892</v>
+        <v>0.4272520885812814</v>
       </c>
       <c r="AQ18">
-        <v>0.4172174058024892</v>
+        <v>0.4272520885812814</v>
       </c>
       <c r="AR18">
-        <v>0.4172174058024892</v>
+        <v>0.4272520885812814</v>
       </c>
       <c r="AS18">
-        <v>0.4172174058024892</v>
+        <v>0.4272520885812814</v>
       </c>
       <c r="AT18">
-        <v>0.4172174058024892</v>
+        <v>0.4272520885812814</v>
       </c>
       <c r="AU18">
-        <v>0.4172174058024892</v>
+        <v>0.4272520885812525</v>
       </c>
       <c r="AV18">
-        <v>0.4172174058024892</v>
+        <v>0.4272520885812469</v>
       </c>
       <c r="AW18">
-        <v>0.4172174058024892</v>
+        <v>0.4272520885812463</v>
       </c>
       <c r="AX18">
-        <v>0.4172174058024892</v>
+        <v>0.4272520885812463</v>
       </c>
       <c r="AY18">
-        <v>0.4172174058024892</v>
+        <v>0.4272520885812455</v>
       </c>
       <c r="AZ18">
-        <v>0.4172174058024892</v>
+        <v>0.3957213183233718</v>
       </c>
       <c r="BA18">
-        <v>0.4172174058024892</v>
+        <v>0.395721318323371</v>
       </c>
       <c r="BB18">
-        <v>0.4172174058024892</v>
+        <v>0.395721318323371</v>
       </c>
       <c r="BC18">
-        <v>0.3844577268558471</v>
+        <v>0.395721318323371</v>
       </c>
       <c r="BD18">
-        <v>0.3516980479092051</v>
+        <v>0.3957213183233691</v>
       </c>
       <c r="BE18">
-        <v>0.3516980479092051</v>
+        <v>0.362961639376727</v>
       </c>
       <c r="BF18">
-        <v>0.3283491692398849</v>
+        <v>0.330201960430085</v>
       </c>
       <c r="BG18">
-        <v>0.3050002905705647</v>
+        <v>0.3302019604300833</v>
       </c>
       <c r="BH18">
-        <v>0.3050002905705647</v>
+        <v>0.3022145586675624</v>
       </c>
       <c r="BI18">
-        <v>0.3050002905705647</v>
+        <v>0.2742271569050415</v>
       </c>
       <c r="BJ18">
-        <v>0.3050002905705647</v>
+        <v>0.2462397551425206</v>
       </c>
       <c r="BK18">
-        <v>0.2891620345653793</v>
+        <v>0.2462397551425206</v>
       </c>
       <c r="BL18">
-        <v>0.2733237785601938</v>
+        <v>0.2462397551425206</v>
       </c>
       <c r="BM18">
-        <v>0.2733237785601938</v>
+        <v>0.2462397551425193</v>
       </c>
       <c r="BN18">
-        <v>0.2733237785601938</v>
+        <v>0.2462397551425182</v>
       </c>
       <c r="BO18">
-        <v>0.2733237785601938</v>
+        <v>0.2462397551425182</v>
       </c>
       <c r="BP18">
-        <v>0.2023229577494269</v>
+        <v>0.2399887360082943</v>
       </c>
       <c r="BQ18">
-        <v>0.2023229577494269</v>
+        <v>0.2399887360082943</v>
       </c>
       <c r="BR18">
-        <v>0.2023229577494269</v>
+        <v>0.2399887360082943</v>
       </c>
       <c r="BS18">
-        <v>0.2023229577494269</v>
+        <v>0.2177635311293499</v>
       </c>
       <c r="BT18">
-        <v>0.2023229577494269</v>
+        <v>0.2177635311293499</v>
       </c>
       <c r="BU18">
-        <v>0.2023229577494269</v>
+        <v>0.2177635311293499</v>
       </c>
       <c r="BV18">
-        <v>0.2023229577494269</v>
+        <v>0.2177635311293499</v>
       </c>
       <c r="BW18">
-        <v>0.2023229577494269</v>
+        <v>0.2177635311293499</v>
       </c>
       <c r="BX18">
-        <v>0.2023229577494269</v>
+        <v>0.2177635311293499</v>
       </c>
       <c r="BY18">
-        <v>0.2023229577494269</v>
+        <v>0.2177635311293499</v>
       </c>
       <c r="BZ18">
-        <v>0.2023229577494269</v>
+        <v>0.2177635311293499</v>
       </c>
       <c r="CA18">
-        <v>0.2023229577494269</v>
+        <v>0.2177635311293499</v>
       </c>
       <c r="CB18">
-        <v>0.2023229577494269</v>
+        <v>0.2177635311293499</v>
       </c>
       <c r="CC18">
-        <v>0.2023229577494269</v>
+        <v>0.2007860073430107</v>
       </c>
       <c r="CD18">
-        <v>0.2023229577494269</v>
+        <v>0.2007860073430107</v>
       </c>
       <c r="CE18">
-        <v>0.2023229577494269</v>
+        <v>0.2007860073430107</v>
       </c>
       <c r="CF18">
-        <v>0.2023229577494269</v>
+        <v>0.2007860073430107</v>
       </c>
       <c r="CG18">
-        <v>0.2023229577494269</v>
+        <v>0.2007860073430107</v>
       </c>
       <c r="CH18">
-        <v>0.2023229577494269</v>
+        <v>0.2007860073430107</v>
       </c>
       <c r="CI18">
-        <v>0.2023229577494269</v>
+        <v>0.2007860073430107</v>
       </c>
       <c r="CJ18">
-        <v>0.2023229577494269</v>
+        <v>0.2007860073430107</v>
       </c>
       <c r="CK18">
-        <v>0.2023229577494269</v>
+        <v>0.2007860073430107</v>
       </c>
       <c r="CL18">
-        <v>0.2023229577494269</v>
+        <v>0.2007860073430107</v>
       </c>
       <c r="CM18">
-        <v>0.2023229577494269</v>
+        <v>0.2007860073430107</v>
       </c>
       <c r="CN18">
-        <v>0.2023229577494269</v>
+        <v>0.2007860073430107</v>
       </c>
       <c r="CO18">
-        <v>0.2023229577494269</v>
+        <v>0.2007860073430107</v>
       </c>
       <c r="CP18">
-        <v>0.2023229577494269</v>
+        <v>0.2007860073430107</v>
       </c>
       <c r="CQ18">
-        <v>0.2023229577494269</v>
+        <v>0.2007860073430107</v>
       </c>
       <c r="CR18">
-        <v>0.2023229577494269</v>
+        <v>0.2007860073430107</v>
       </c>
       <c r="CS18">
-        <v>0.2023229577494269</v>
+        <v>0.2007860073430107</v>
       </c>
     </row>
     <row r="19" spans="1:97">
@@ -6935,274 +6938,274 @@
         <v>0.2</v>
       </c>
       <c r="H19">
+        <v>0.2</v>
+      </c>
+      <c r="I19">
+        <v>0.2</v>
+      </c>
+      <c r="J19">
+        <v>0.2</v>
+      </c>
+      <c r="K19">
+        <v>0.2</v>
+      </c>
+      <c r="L19">
+        <v>0.2</v>
+      </c>
+      <c r="M19">
         <v>0.26</v>
       </c>
-      <c r="I19">
+      <c r="N19">
         <v>0.26</v>
       </c>
-      <c r="J19">
+      <c r="O19">
         <v>0.26</v>
       </c>
-      <c r="K19">
-        <v>0.26</v>
-      </c>
-      <c r="L19">
+      <c r="P19">
         <v>0.32</v>
       </c>
-      <c r="M19">
+      <c r="Q19">
         <v>0.32</v>
       </c>
-      <c r="N19">
+      <c r="R19">
         <v>0.32</v>
       </c>
-      <c r="O19">
-        <v>0.38</v>
-      </c>
-      <c r="P19">
-        <v>0.38</v>
-      </c>
-      <c r="Q19">
-        <v>0.38</v>
-      </c>
-      <c r="R19">
-        <v>0.44</v>
-      </c>
       <c r="S19">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="T19">
+        <v>0.44</v>
+      </c>
+      <c r="U19">
+        <v>0.44</v>
+      </c>
+      <c r="V19">
+        <v>0.44</v>
+      </c>
+      <c r="W19">
+        <v>0.44</v>
+      </c>
+      <c r="X19">
+        <v>0.44</v>
+      </c>
+      <c r="Y19">
         <v>0.5</v>
-      </c>
-      <c r="U19">
-        <v>0.5</v>
-      </c>
-      <c r="V19">
-        <v>0.5</v>
-      </c>
-      <c r="W19">
-        <v>0.5</v>
-      </c>
-      <c r="X19">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="Y19">
-        <v>0.5600000000000001</v>
       </c>
       <c r="Z19">
         <v>0.5600000000000001</v>
       </c>
       <c r="AA19">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="AB19">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="AC19">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="AD19">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="AE19">
-        <v>0.5403499240523313</v>
+        <v>0.6029309994750058</v>
       </c>
       <c r="AF19">
-        <v>0.5206998481046626</v>
+        <v>0.5858619989500117</v>
       </c>
       <c r="AG19">
-        <v>0.501049772156994</v>
+        <v>0.5668874531773287</v>
       </c>
       <c r="AH19">
-        <v>0.501049772156994</v>
+        <v>0.5479129074046457</v>
       </c>
       <c r="AI19">
-        <v>0.501049772156994</v>
+        <v>0.5479129074046457</v>
       </c>
       <c r="AJ19">
-        <v>0.501049772156994</v>
+        <v>0.5479129074046457</v>
       </c>
       <c r="AK19">
-        <v>0.501049772156994</v>
+        <v>0.5479129074046457</v>
       </c>
       <c r="AL19">
-        <v>0.501049772156994</v>
+        <v>0.5479129074046457</v>
       </c>
       <c r="AM19">
-        <v>0.501049772156994</v>
+        <v>0.5479129074046457</v>
       </c>
       <c r="AN19">
-        <v>0.501049772156994</v>
+        <v>0.5479129074046457</v>
       </c>
       <c r="AO19">
-        <v>0.501049772156994</v>
+        <v>0.5479129074046457</v>
       </c>
       <c r="AP19">
-        <v>0.501049772156994</v>
+        <v>0.5479129074046457</v>
       </c>
       <c r="AQ19">
-        <v>0.501049772156994</v>
+        <v>0.5421799540541861</v>
       </c>
       <c r="AR19">
-        <v>0.501049772156994</v>
+        <v>0.5364470007037264</v>
       </c>
       <c r="AS19">
-        <v>0.501049772156994</v>
+        <v>0.5307140473532669</v>
       </c>
       <c r="AT19">
-        <v>0.501049772156994</v>
+        <v>0.5249810940028072</v>
       </c>
       <c r="AU19">
-        <v>0.501049772156994</v>
+        <v>0.5192481406523477</v>
       </c>
       <c r="AV19">
-        <v>0.501049772156994</v>
+        <v>0.5192481406523477</v>
       </c>
       <c r="AW19">
-        <v>0.4804612554239331</v>
+        <v>0.4986596239192866</v>
       </c>
       <c r="AX19">
-        <v>0.4598727386908721</v>
+        <v>0.4780711071862256</v>
       </c>
       <c r="AY19">
-        <v>0.4365554612956538</v>
+        <v>0.4780711071862256</v>
       </c>
       <c r="AZ19">
-        <v>0.4132381839004355</v>
+        <v>0.4448754603256553</v>
       </c>
       <c r="BA19">
-        <v>0.4132381839004355</v>
+        <v>0.411679813465085</v>
       </c>
       <c r="BB19">
-        <v>0.4132381839004355</v>
+        <v>0.3784841666045146</v>
       </c>
       <c r="BC19">
-        <v>0.4132381839004355</v>
+        <v>0.3784841666045146</v>
       </c>
       <c r="BD19">
-        <v>0.4132381839004355</v>
+        <v>0.3784841666045146</v>
       </c>
       <c r="BE19">
-        <v>0.4132381839004355</v>
+        <v>0.3784841666045146</v>
       </c>
       <c r="BF19">
-        <v>0.4132381839004355</v>
+        <v>0.3784841666045146</v>
       </c>
       <c r="BG19">
-        <v>0.4132381839004355</v>
+        <v>0.3784841666045146</v>
       </c>
       <c r="BH19">
-        <v>0.4132381839004355</v>
+        <v>0.3423731715780991</v>
       </c>
       <c r="BI19">
-        <v>0.375747040566687</v>
+        <v>0.3423731715780991</v>
       </c>
       <c r="BJ19">
-        <v>0.3382558972329385</v>
+        <v>0.3423731715780991</v>
       </c>
       <c r="BK19">
-        <v>0.3382558972329385</v>
+        <v>0.3423731715780991</v>
       </c>
       <c r="BL19">
-        <v>0.3382558972329385</v>
+        <v>0.3423731715780991</v>
       </c>
       <c r="BM19">
-        <v>0.3382558972329385</v>
+        <v>0.3423731715780991</v>
       </c>
       <c r="BN19">
-        <v>0.3124893841574347</v>
+        <v>0.3423731715780991</v>
       </c>
       <c r="BO19">
-        <v>0.2867228710819311</v>
+        <v>0.3423731715780991</v>
       </c>
       <c r="BP19">
-        <v>0.2867228710819311</v>
+        <v>0.3423731715780991</v>
       </c>
       <c r="BQ19">
-        <v>0.2867228710819311</v>
+        <v>0.3423731715780991</v>
       </c>
       <c r="BR19">
-        <v>0.2867228710819311</v>
+        <v>0.2627418387879069</v>
       </c>
       <c r="BS19">
-        <v>0.286722871081931</v>
+        <v>0.2627418387879069</v>
       </c>
       <c r="BT19">
-        <v>0.286722871081931</v>
+        <v>0.2627418387879069</v>
       </c>
       <c r="BU19">
-        <v>0.286722871081931</v>
+        <v>0.2627418387879069</v>
       </c>
       <c r="BV19">
-        <v>0.286722871081931</v>
+        <v>0.2627418387879069</v>
       </c>
       <c r="BW19">
-        <v>0.286722871081931</v>
+        <v>0.2627418387879069</v>
       </c>
       <c r="BX19">
-        <v>0.2582598262286972</v>
+        <v>0.2627418387879069</v>
       </c>
       <c r="BY19">
-        <v>0.2297967813754635</v>
+        <v>0.2627418387879069</v>
       </c>
       <c r="BZ19">
-        <v>0.2013337365222297</v>
+        <v>0.2627418387879069</v>
       </c>
       <c r="CA19">
-        <v>0.2013337365222297</v>
+        <v>0.2627418387879069</v>
       </c>
       <c r="CB19">
-        <v>0.2013337365222297</v>
+        <v>0.2627418387879069</v>
       </c>
       <c r="CC19">
-        <v>0.2013337365222297</v>
+        <v>0.2627418387879069</v>
       </c>
       <c r="CD19">
-        <v>0.2013337365222297</v>
+        <v>0.2627418387879069</v>
       </c>
       <c r="CE19">
-        <v>0.2013337365222297</v>
+        <v>0.2627418387879069</v>
       </c>
       <c r="CF19">
-        <v>0.2013337365222297</v>
+        <v>0.2627418387879069</v>
       </c>
       <c r="CG19">
-        <v>0.2013337365222297</v>
+        <v>0.2627418387879069</v>
       </c>
       <c r="CH19">
-        <v>0.2013337365222297</v>
+        <v>0.2627418387879069</v>
       </c>
       <c r="CI19">
-        <v>0.2013337365222297</v>
+        <v>0.2627418387879069</v>
       </c>
       <c r="CJ19">
-        <v>0.2013337365222297</v>
+        <v>0.231634449365141</v>
       </c>
       <c r="CK19">
-        <v>0.2013337365222297</v>
+        <v>0.2005270599423751</v>
       </c>
       <c r="CL19">
-        <v>0.2013337365222297</v>
+        <v>0.2005270599423751</v>
       </c>
       <c r="CM19">
-        <v>0.2013337365222297</v>
+        <v>0.2005270599423751</v>
       </c>
       <c r="CN19">
-        <v>0.2013337365222297</v>
+        <v>0.2005270599423751</v>
       </c>
       <c r="CO19">
-        <v>0.2013337365222297</v>
+        <v>0.2005270599423751</v>
       </c>
       <c r="CP19">
-        <v>0.2013337365222297</v>
+        <v>0.2005270599423751</v>
       </c>
       <c r="CQ19">
-        <v>0.2013337365222297</v>
+        <v>0.2005270599423751</v>
       </c>
       <c r="CR19">
-        <v>0.2013337365222297</v>
+        <v>0.2005270599423751</v>
       </c>
       <c r="CS19">
-        <v>0.2013337365222297</v>
+        <v>0.2005270599423751</v>
       </c>
     </row>
     <row r="20" spans="1:97">
@@ -7213,13 +7216,13 @@
         <v>0.2</v>
       </c>
       <c r="C20">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="D20">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="E20">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="F20">
         <v>0.26</v>
@@ -7234,13 +7237,13 @@
         <v>0.26</v>
       </c>
       <c r="J20">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="K20">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="L20">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="M20">
         <v>0.32</v>
@@ -7255,247 +7258,247 @@
         <v>0.38</v>
       </c>
       <c r="Q20">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="R20">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="S20">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="T20">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="U20">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="V20">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="W20">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="X20">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="Y20">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="Z20">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AA20">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AB20">
-        <v>0.5600000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="AC20">
-        <v>0.5600000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="AD20">
-        <v>0.5380117751607617</v>
+        <v>0.44</v>
       </c>
       <c r="AE20">
-        <v>0.5160235503215234</v>
+        <v>0.44</v>
       </c>
       <c r="AF20">
-        <v>0.4940353254822851</v>
+        <v>0.4164800186063271</v>
       </c>
       <c r="AG20">
-        <v>0.4940353254822851</v>
+        <v>0.3929600372126542</v>
       </c>
       <c r="AH20">
-        <v>0.4940353254822851</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="AI20">
-        <v>0.4806394595781864</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="AJ20">
-        <v>0.4672435936740876</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="AK20">
-        <v>0.4538477277699889</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="AL20">
-        <v>0.4404518618658901</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="AM20">
-        <v>0.4404518618658901</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="AN20">
-        <v>0.4404518618658901</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="AO20">
-        <v>0.4404518618658901</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="AP20">
-        <v>0.4404518618658901</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="AQ20">
-        <v>0.4404518618658901</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="AR20">
-        <v>0.4404518618658901</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="AS20">
-        <v>0.4404518618658901</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="AT20">
-        <v>0.4404518618658901</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="AU20">
-        <v>0.4404518618658901</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="AV20">
-        <v>0.4110331577409419</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="AW20">
-        <v>0.3816144536159936</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="AX20">
-        <v>0.3816144536159936</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="AY20">
-        <v>0.3816144536159936</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="AZ20">
-        <v>0.3816144536159936</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="BA20">
-        <v>0.3816144536159936</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="BB20">
-        <v>0.3816144536159936</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="BC20">
-        <v>0.3816144536159936</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="BD20">
-        <v>0.3816144536159936</v>
+        <v>0.3694400558189813</v>
       </c>
       <c r="BE20">
-        <v>0.3816144536159936</v>
+        <v>0.3456860830708955</v>
       </c>
       <c r="BF20">
-        <v>0.3816144536159936</v>
+        <v>0.3219321103228098</v>
       </c>
       <c r="BG20">
-        <v>0.3816144536159936</v>
+        <v>0.3219321103228098</v>
       </c>
       <c r="BH20">
-        <v>0.3816144536159936</v>
+        <v>0.3219321103228098</v>
       </c>
       <c r="BI20">
-        <v>0.3630243022929953</v>
+        <v>0.3219321103228098</v>
       </c>
       <c r="BJ20">
-        <v>0.344434150969997</v>
+        <v>0.3219321103228098</v>
       </c>
       <c r="BK20">
-        <v>0.344434150969997</v>
+        <v>0.3219321103228098</v>
       </c>
       <c r="BL20">
-        <v>0.344434150969997</v>
+        <v>0.3219321103228098</v>
       </c>
       <c r="BM20">
-        <v>0.344434150969997</v>
+        <v>0.2937606720536345</v>
       </c>
       <c r="BN20">
-        <v>0.344434150969997</v>
+        <v>0.2937606720536345</v>
       </c>
       <c r="BO20">
-        <v>0.344434150969997</v>
+        <v>0.2808560083746729</v>
       </c>
       <c r="BP20">
-        <v>0.344434150969997</v>
+        <v>0.2679513446957114</v>
       </c>
       <c r="BQ20">
-        <v>0.3444341509699969</v>
+        <v>0.2550466810167498</v>
       </c>
       <c r="BR20">
-        <v>0.3444341509699969</v>
+        <v>0.2550466810167498</v>
       </c>
       <c r="BS20">
-        <v>0.3444341509699969</v>
+        <v>0.2550466810167498</v>
       </c>
       <c r="BT20">
-        <v>0.3066178097125205</v>
+        <v>0.2550466810167498</v>
       </c>
       <c r="BU20">
-        <v>0.268801468455044</v>
+        <v>0.2550466810167498</v>
       </c>
       <c r="BV20">
-        <v>0.268801468455044</v>
+        <v>0.2550466810167498</v>
       </c>
       <c r="BW20">
-        <v>0.268801468455044</v>
+        <v>0.2550466810167498</v>
       </c>
       <c r="BX20">
-        <v>0.268801468455044</v>
+        <v>0.2550466810167498</v>
       </c>
       <c r="BY20">
-        <v>0.268801468455044</v>
+        <v>0.2550466810167498</v>
       </c>
       <c r="BZ20">
-        <v>0.2688014684550448</v>
+        <v>0.252315326923836</v>
       </c>
       <c r="CA20">
-        <v>0.2477465776541888</v>
+        <v>0.2495839728309221</v>
       </c>
       <c r="CB20">
-        <v>0.2266916868533327</v>
+        <v>0.2495839728309221</v>
       </c>
       <c r="CC20">
-        <v>0.2266916868533327</v>
+        <v>0.2495839728309221</v>
       </c>
       <c r="CD20">
-        <v>0.2266916868533327</v>
+        <v>0.2495839728309221</v>
       </c>
       <c r="CE20">
-        <v>0.2056044610207043</v>
+        <v>0.2495839728309221</v>
       </c>
       <c r="CF20">
-        <v>0.2056044610207043</v>
+        <v>0.2495839728309221</v>
       </c>
       <c r="CG20">
-        <v>0.2056044610207043</v>
+        <v>0.2495839728309221</v>
       </c>
       <c r="CH20">
-        <v>0.2028429678077509</v>
+        <v>0.2495839728309221</v>
       </c>
       <c r="CI20">
-        <v>0.2000814745947975</v>
+        <v>0.227333429780772</v>
       </c>
       <c r="CJ20">
-        <v>0.2000814745947975</v>
+        <v>0.205082886730622</v>
       </c>
       <c r="CK20">
-        <v>0.2000814745947975</v>
+        <v>0.205082886730622</v>
       </c>
       <c r="CL20">
-        <v>0.2000814745947975</v>
+        <v>0.205082886730622</v>
       </c>
       <c r="CM20">
-        <v>0.2000814745947975</v>
+        <v>0.205082886730622</v>
       </c>
       <c r="CN20">
-        <v>0.2000814745947975</v>
+        <v>0.205082886730622</v>
       </c>
       <c r="CO20">
-        <v>0.2000814745947975</v>
+        <v>0.2050828867306218</v>
       </c>
       <c r="CP20">
-        <v>0.2000814745947975</v>
+        <v>0.2050828867306218</v>
       </c>
       <c r="CQ20">
-        <v>0.2000814745947975</v>
+        <v>0.2050828867306218</v>
       </c>
       <c r="CR20">
-        <v>0.2000814745947975</v>
+        <v>0.2050828867306218</v>
       </c>
       <c r="CS20">
-        <v>0.2000814745947975</v>
+        <v>0.2050828867306218</v>
       </c>
     </row>
     <row r="21" spans="1:97">
@@ -7506,25 +7509,25 @@
         <v>0.2</v>
       </c>
       <c r="C21">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="D21">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="E21">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="F21">
         <v>0.26</v>
       </c>
       <c r="G21">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="H21">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="I21">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="J21">
         <v>0.32</v>
@@ -7545,16 +7548,16 @@
         <v>0.38</v>
       </c>
       <c r="P21">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="Q21">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="R21">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="S21">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="T21">
         <v>0.5</v>
@@ -7566,229 +7569,522 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="W21">
-        <v>0.5378754765360211</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="X21">
-        <v>0.5157509530720421</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Y21">
-        <v>0.4936264296080631</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z21">
-        <v>0.4715019061440842</v>
+        <v>0.62</v>
       </c>
       <c r="AA21">
-        <v>0.5315019061440842</v>
+        <v>0.62</v>
       </c>
       <c r="AB21">
-        <v>0.5915019061440842</v>
+        <v>0.62</v>
       </c>
       <c r="AC21">
-        <v>0.591501906144084</v>
+        <v>0.6017424237088631</v>
       </c>
       <c r="AD21">
-        <v>0.591501906144084</v>
+        <v>0.583484847417732</v>
       </c>
       <c r="AE21">
-        <v>0.591501906144084</v>
+        <v>0.5652272711266009</v>
       </c>
       <c r="AF21">
-        <v>0.5733845400460664</v>
+        <v>0.5469696948354698</v>
       </c>
       <c r="AG21">
-        <v>0.5552671739480487</v>
+        <v>0.5275150984844407</v>
       </c>
       <c r="AH21">
-        <v>0.537149807850031</v>
+        <v>0.5080605021334115</v>
       </c>
       <c r="AI21">
-        <v>0.537149807850031</v>
+        <v>0.4886059057823823</v>
       </c>
       <c r="AJ21">
-        <v>0.537149807850031</v>
+        <v>0.470538977917761</v>
       </c>
       <c r="AK21">
-        <v>0.537149807850031</v>
+        <v>0.4524720500531397</v>
       </c>
       <c r="AL21">
-        <v>0.537149807850031</v>
+        <v>0.4344051221885183</v>
       </c>
       <c r="AM21">
-        <v>0.537149807850031</v>
+        <v>0.416338194323897</v>
       </c>
       <c r="AN21">
-        <v>0.537149807850031</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="AO21">
-        <v>0.537149807850031</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="AP21">
-        <v>0.537149807850031</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="AQ21">
-        <v>0.537149807850031</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="AR21">
-        <v>0.5092916610123439</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="AS21">
-        <v>0.4814335141746569</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="AT21">
-        <v>0.45357536733697</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="AU21">
-        <v>0.45357536733697</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="AV21">
-        <v>0.45357536733697</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="AW21">
-        <v>0.45357536733697</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="AX21">
-        <v>0.4350654690952911</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="AY21">
-        <v>0.4350654690952911</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="AZ21">
-        <v>0.4350654690952911</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="BA21">
-        <v>0.4350654690952911</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="BB21">
-        <v>0.4132802901220901</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="BC21">
-        <v>0.3914951111488891</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="BD21">
-        <v>0.3605885395904271</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="BE21">
-        <v>0.3605885395904271</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="BF21">
-        <v>0.3605885395904271</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="BG21">
-        <v>0.3605885395904271</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="BH21">
-        <v>0.3320378183099915</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="BI21">
-        <v>0.3034870970295558</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="BJ21">
-        <v>0.3034870970295558</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="BK21">
-        <v>0.3034870970295558</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="BL21">
-        <v>0.3034870970295558</v>
+        <v>0.3982712664592757</v>
       </c>
       <c r="BM21">
-        <v>0.3034870970295558</v>
+        <v>0.3796900172305871</v>
       </c>
       <c r="BN21">
-        <v>0.3034870970295558</v>
+        <v>0.297141805513517</v>
       </c>
       <c r="BO21">
-        <v>0.3034870970295558</v>
+        <v>0.297141805513517</v>
       </c>
       <c r="BP21">
-        <v>0.3034870970295558</v>
+        <v>0.297141805513517</v>
       </c>
       <c r="BQ21">
-        <v>0.2674569308724929</v>
+        <v>0.297141805513517</v>
       </c>
       <c r="BR21">
-        <v>0.2314267647154299</v>
+        <v>0.297141805513517</v>
       </c>
       <c r="BS21">
-        <v>0.2314267647154299</v>
+        <v>0.297141805513517</v>
       </c>
       <c r="BT21">
-        <v>0.2314267647154299</v>
+        <v>0.297141805513517</v>
       </c>
       <c r="BU21">
-        <v>0.2314267647154299</v>
+        <v>0.297141805513517</v>
       </c>
       <c r="BV21">
-        <v>0.2314267647154299</v>
+        <v>0.297141805513517</v>
       </c>
       <c r="BW21">
-        <v>0.2314267647154299</v>
+        <v>0.297141805513517</v>
       </c>
       <c r="BX21">
-        <v>0.2314267647154299</v>
+        <v>0.2686787606602832</v>
       </c>
       <c r="BY21">
-        <v>0.2314267647154299</v>
+        <v>0.2402157158070494</v>
       </c>
       <c r="BZ21">
-        <v>0.2314267647154299</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CA21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CB21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CC21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CD21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CE21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CF21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CG21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CH21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CI21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CJ21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CK21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CL21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CM21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CN21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CO21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CP21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CQ21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CR21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
       </c>
       <c r="CS21">
-        <v>0.2036561184270317</v>
+        <v>0.2117526709538157</v>
+      </c>
+    </row>
+    <row r="22" spans="1:97">
+      <c r="A22" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B22">
+        <v>0.2</v>
+      </c>
+      <c r="C22">
+        <v>0.2</v>
+      </c>
+      <c r="D22">
+        <v>0.2</v>
+      </c>
+      <c r="E22">
+        <v>0.2</v>
+      </c>
+      <c r="F22">
+        <v>0.2</v>
+      </c>
+      <c r="G22">
+        <v>0.2</v>
+      </c>
+      <c r="H22">
+        <v>0.26</v>
+      </c>
+      <c r="I22">
+        <v>0.26</v>
+      </c>
+      <c r="J22">
+        <v>0.26</v>
+      </c>
+      <c r="K22">
+        <v>0.26</v>
+      </c>
+      <c r="L22">
+        <v>0.32</v>
+      </c>
+      <c r="M22">
+        <v>0.32</v>
+      </c>
+      <c r="N22">
+        <v>0.32</v>
+      </c>
+      <c r="O22">
+        <v>0.32</v>
+      </c>
+      <c r="P22">
+        <v>0.32</v>
+      </c>
+      <c r="Q22">
+        <v>0.38</v>
+      </c>
+      <c r="R22">
+        <v>0.38</v>
+      </c>
+      <c r="S22">
+        <v>0.38</v>
+      </c>
+      <c r="T22">
+        <v>0.38</v>
+      </c>
+      <c r="U22">
+        <v>0.38</v>
+      </c>
+      <c r="V22">
+        <v>0.38</v>
+      </c>
+      <c r="W22">
+        <v>0.38</v>
+      </c>
+      <c r="X22">
+        <v>0.44</v>
+      </c>
+      <c r="Y22">
+        <v>0.44</v>
+      </c>
+      <c r="Z22">
+        <v>0.44</v>
+      </c>
+      <c r="AA22">
+        <v>0.44</v>
+      </c>
+      <c r="AB22">
+        <v>0.5</v>
+      </c>
+      <c r="AC22">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AD22">
+        <v>0.5380117751607604</v>
+      </c>
+      <c r="AE22">
+        <v>0.5160235503215221</v>
+      </c>
+      <c r="AF22">
+        <v>0.4940353254822837</v>
+      </c>
+      <c r="AG22">
+        <v>0.4940353254822837</v>
+      </c>
+      <c r="AH22">
+        <v>0.4940353254822837</v>
+      </c>
+      <c r="AI22">
+        <v>0.4737064233041311</v>
+      </c>
+      <c r="AJ22">
+        <v>0.4533775211259785</v>
+      </c>
+      <c r="AK22">
+        <v>0.4330486189478258</v>
+      </c>
+      <c r="AL22">
+        <v>0.4127197167696732</v>
+      </c>
+      <c r="AM22">
+        <v>0.4127197167696732</v>
+      </c>
+      <c r="AN22">
+        <v>0.4127197167696732</v>
+      </c>
+      <c r="AO22">
+        <v>0.4127197167696732</v>
+      </c>
+      <c r="AP22">
+        <v>0.4127197167696732</v>
+      </c>
+      <c r="AQ22">
+        <v>0.4127197167696732</v>
+      </c>
+      <c r="AR22">
+        <v>0.4127197167696732</v>
+      </c>
+      <c r="AS22">
+        <v>0.4127197167696732</v>
+      </c>
+      <c r="AT22">
+        <v>0.4127197167696732</v>
+      </c>
+      <c r="AU22">
+        <v>0.4127197167696732</v>
+      </c>
+      <c r="AV22">
+        <v>0.4127197167696732</v>
+      </c>
+      <c r="AW22">
+        <v>0.4127197167696732</v>
+      </c>
+      <c r="AX22">
+        <v>0.4127197167696732</v>
+      </c>
+      <c r="AY22">
+        <v>0.4127197167696732</v>
+      </c>
+      <c r="AZ22">
+        <v>0.384761049820442</v>
+      </c>
+      <c r="BA22">
+        <v>0.3568023828712109</v>
+      </c>
+      <c r="BB22">
+        <v>0.3288437159219796</v>
+      </c>
+      <c r="BC22">
+        <v>0.3288437159219796</v>
+      </c>
+      <c r="BD22">
+        <v>0.3288437159219796</v>
+      </c>
+      <c r="BE22">
+        <v>0.3288437159219796</v>
+      </c>
+      <c r="BF22">
+        <v>0.3288437159219796</v>
+      </c>
+      <c r="BG22">
+        <v>0.3288437159219797</v>
+      </c>
+      <c r="BH22">
+        <v>0.3288437159219797</v>
+      </c>
+      <c r="BI22">
+        <v>0.3102535645989814</v>
+      </c>
+      <c r="BJ22">
+        <v>0.2916634132759831</v>
+      </c>
+      <c r="BK22">
+        <v>0.2916634132759831</v>
+      </c>
+      <c r="BL22">
+        <v>0.2916634132759831</v>
+      </c>
+      <c r="BM22">
+        <v>0.2916634132759831</v>
+      </c>
+      <c r="BN22">
+        <v>0.2916634132759831</v>
+      </c>
+      <c r="BO22">
+        <v>0.2916634132759831</v>
+      </c>
+      <c r="BP22">
+        <v>0.2688612926110785</v>
+      </c>
+      <c r="BQ22">
+        <v>0.246059171946174</v>
+      </c>
+      <c r="BR22">
+        <v>0.246059171946174</v>
+      </c>
+      <c r="BS22">
+        <v>0.246059171946174</v>
+      </c>
+      <c r="BT22">
+        <v>0.246059171946174</v>
+      </c>
+      <c r="BU22">
+        <v>0.246059171946174</v>
+      </c>
+      <c r="BV22">
+        <v>0.246059171946174</v>
+      </c>
+      <c r="BW22">
+        <v>0.246059171946174</v>
+      </c>
+      <c r="BX22">
+        <v>0.246059171946174</v>
+      </c>
+      <c r="BY22">
+        <v>0.225012156532841</v>
+      </c>
+      <c r="BZ22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CA22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CB22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CC22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CD22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CE22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CF22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CG22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CH22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CI22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CJ22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CK22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CL22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CM22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CN22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CO22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CP22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CQ22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CR22">
+        <v>0.2039651411195081</v>
+      </c>
+      <c r="CS22">
+        <v>0.2039651411195081</v>
       </c>
     </row>
   </sheetData>

--- a/python/optimization_summary_slow_charging.xlsx
+++ b/python/optimization_summary_slow_charging.xlsx
@@ -899,52 +899,52 @@
         <v>4</v>
       </c>
       <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
         <v>2</v>
       </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
       <c r="N2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X2">
         <v>0</v>
@@ -973,55 +973,55 @@
         <v>4</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3">
+        <v>2</v>
+      </c>
+      <c r="V3">
+        <v>3</v>
+      </c>
+      <c r="W3">
         <v>1</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
       </c>
       <c r="X3">
         <v>0</v>
@@ -1056,49 +1056,49 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4">
         <v>0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4">
         <v>0</v>
@@ -1127,55 +1127,55 @@
         <v>4</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U5">
+        <v>4</v>
+      </c>
+      <c r="V5">
+        <v>2</v>
+      </c>
+      <c r="W5">
         <v>1</v>
-      </c>
-      <c r="V5">
-        <v>1</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
       </c>
       <c r="X5">
         <v>0</v>
@@ -1210,52 +1210,52 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
       <c r="R6">
+        <v>2</v>
+      </c>
+      <c r="S6">
+        <v>3</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>4</v>
+      </c>
+      <c r="V6">
+        <v>2</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
         <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>1</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>1</v>
       </c>
       <c r="Y6">
         <v>0</v>
@@ -1287,10 +1287,10 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>206.25</v>
       </c>
       <c r="C2">
-        <v>19.84126984126984</v>
+        <v>40.92261904761904</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1298,10 +1298,10 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>34</v>
+        <v>77.25</v>
       </c>
       <c r="C3">
-        <v>6.746031746031746</v>
+        <v>15.32738095238095</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1309,10 +1309,10 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>370</v>
+        <v>220.5</v>
       </c>
       <c r="C4">
-        <v>73.4126984126984</v>
+        <v>43.75</v>
       </c>
     </row>
   </sheetData>
@@ -1341,10 +1341,10 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>136</v>
+        <v>309</v>
       </c>
       <c r="C2">
-        <v>28.33333333333333</v>
+        <v>64.375</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1352,10 +1352,10 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>344</v>
+        <v>171</v>
       </c>
       <c r="C3">
-        <v>71.66666666666667</v>
+        <v>35.625</v>
       </c>
     </row>
   </sheetData>
@@ -1421,7 +1421,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>12679.75891301304</v>
+        <v>12599.48413018777</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1429,7 +1429,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>13423.48159247707</v>
+        <v>13290.55309865002</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1437,7 +1437,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>12564.22615746522</v>
+        <v>12514.36606270999</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1445,7 +1445,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>11285.79775020202</v>
+        <v>10973.22206773412</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1453,7 +1453,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>10663.18168846838</v>
+        <v>10675.13988535556</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1461,7 +1461,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>10451.26834452735</v>
+        <v>10718.65849530126</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1469,7 +1469,7 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>10257.64616763476</v>
+        <v>10374.1513842318</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1477,7 +1477,7 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>9735.872343978559</v>
+        <v>9627.243850672487</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1485,7 +1485,7 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>9067.172674055173</v>
+        <v>9387.394923386115</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1493,7 +1493,7 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>8333.373241902102</v>
+        <v>8951.173973685285</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1501,7 +1501,7 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>7663.666561516754</v>
+        <v>7590.563984462906</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1509,7 +1509,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>6939.632627900834</v>
+        <v>6919.126886168156</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1517,7 +1517,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>6332.21479229541</v>
+        <v>6707.959928052437</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1525,7 +1525,7 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>5834.334638743836</v>
+        <v>6308.62298977764</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1533,7 +1533,7 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>5649.57654334459</v>
+        <v>6353.175003454245</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1541,7 +1541,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>5610.410692096326</v>
+        <v>6747.967847770466</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1549,7 +1549,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>5427.403926373658</v>
+        <v>6392.88731799211</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1557,7 +1557,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>5260.082199844289</v>
+        <v>5895.476651788172</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1565,7 +1565,7 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>5173.332855419012</v>
+        <v>5355.412617025802</v>
       </c>
     </row>
   </sheetData>
@@ -1615,7 +1615,7 @@
         <v>21</v>
       </c>
       <c r="B5">
-        <v>875124.0000000002</v>
+        <v>2730491.999999998</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>23</v>
       </c>
       <c r="B7">
-        <v>27909124</v>
+        <v>29764492</v>
       </c>
     </row>
   </sheetData>
@@ -1957,274 +1957,274 @@
         <v>0.2</v>
       </c>
       <c r="H2">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="I2">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="J2">
+        <v>0.2</v>
+      </c>
+      <c r="K2">
+        <v>0.26</v>
+      </c>
+      <c r="L2">
+        <v>0.26</v>
+      </c>
+      <c r="M2">
         <v>0.32</v>
       </c>
-      <c r="K2">
+      <c r="N2">
+        <v>0.32</v>
+      </c>
+      <c r="O2">
+        <v>0.32</v>
+      </c>
+      <c r="P2">
+        <v>0.32</v>
+      </c>
+      <c r="Q2">
+        <v>0.32</v>
+      </c>
+      <c r="R2">
         <v>0.38</v>
       </c>
-      <c r="L2">
-        <v>0.38</v>
-      </c>
-      <c r="M2">
-        <v>0.38</v>
-      </c>
-      <c r="N2">
-        <v>0.38</v>
-      </c>
-      <c r="O2">
-        <v>0.38</v>
-      </c>
-      <c r="P2">
-        <v>0.38</v>
-      </c>
-      <c r="Q2">
+      <c r="S2">
         <v>0.44</v>
       </c>
-      <c r="R2">
+      <c r="T2">
         <v>0.44</v>
       </c>
-      <c r="S2">
+      <c r="U2">
+        <v>0.44</v>
+      </c>
+      <c r="V2">
+        <v>0.44</v>
+      </c>
+      <c r="W2">
         <v>0.5</v>
       </c>
-      <c r="T2">
+      <c r="X2">
         <v>0.5</v>
       </c>
-      <c r="U2">
-        <v>0.5</v>
-      </c>
-      <c r="V2">
-        <v>0.5</v>
-      </c>
-      <c r="W2">
+      <c r="Y2">
         <v>0.5600000000000001</v>
       </c>
-      <c r="X2">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="Y2">
-        <v>0.62</v>
-      </c>
       <c r="Z2">
-        <v>0.68</v>
+        <v>0.532293592426056</v>
       </c>
       <c r="AA2">
-        <v>0.68</v>
+        <v>0.5045871848521121</v>
       </c>
       <c r="AB2">
-        <v>0.6612973578033278</v>
+        <v>0.476880777278168</v>
       </c>
       <c r="AC2">
-        <v>0.6425947156066555</v>
+        <v>0.536880777278168</v>
       </c>
       <c r="AD2">
-        <v>0.6238920734099832</v>
+        <v>0.5191903224071867</v>
       </c>
       <c r="AE2">
-        <v>0.6051894312133108</v>
+        <v>0.5014998675362055</v>
       </c>
       <c r="AF2">
-        <v>0.5864867890166385</v>
+        <v>0.4838094126652242</v>
       </c>
       <c r="AG2">
-        <v>0.5652652729419982</v>
+        <v>0.4661189577942429</v>
       </c>
       <c r="AH2">
-        <v>0.544043756867358</v>
+        <v>0.4484285029232616</v>
       </c>
       <c r="AI2">
-        <v>0.5228222407927176</v>
+        <v>0.4304776888240773</v>
       </c>
       <c r="AJ2">
-        <v>0.5016007247180773</v>
+        <v>0.412526874724893</v>
       </c>
       <c r="AK2">
-        <v>0.5016007247180773</v>
+        <v>0.3945760606257088</v>
       </c>
       <c r="AL2">
-        <v>0.5016007247180773</v>
+        <v>0.3766252465265244</v>
       </c>
       <c r="AM2">
-        <v>0.5016007247180773</v>
+        <v>0.3586744324273401</v>
       </c>
       <c r="AN2">
-        <v>0.5016007247180773</v>
+        <v>0.4186744324273401</v>
       </c>
       <c r="AO2">
-        <v>0.5016007247180773</v>
+        <v>0.4786744324273401</v>
       </c>
       <c r="AP2">
-        <v>0.5016007247180773</v>
+        <v>0.478674432427339</v>
       </c>
       <c r="AQ2">
-        <v>0.5016007247180773</v>
+        <v>0.478674432427339</v>
       </c>
       <c r="AR2">
-        <v>0.5016007247180773</v>
+        <v>0.4606771715219705</v>
       </c>
       <c r="AS2">
-        <v>0.5016007247180773</v>
+        <v>0.4426799106166019</v>
       </c>
       <c r="AT2">
-        <v>0.5016007247180773</v>
+        <v>0.4246826497112334</v>
       </c>
       <c r="AU2">
-        <v>0.5016007247180773</v>
+        <v>0.4066853888058649</v>
       </c>
       <c r="AV2">
-        <v>0.4744281462254267</v>
+        <v>0.3887854269872254</v>
       </c>
       <c r="AW2">
-        <v>0.4472555677327762</v>
+        <v>0.3708854651685859</v>
       </c>
       <c r="AX2">
-        <v>0.4200829892401257</v>
+        <v>0.3529855033499464</v>
       </c>
       <c r="AY2">
-        <v>0.4200829892401257</v>
+        <v>0.335085541531307</v>
       </c>
       <c r="AZ2">
-        <v>0.3973470339677133</v>
+        <v>0.395085541531307</v>
       </c>
       <c r="BA2">
-        <v>0.374611078695301</v>
+        <v>0.4550855415313074</v>
       </c>
       <c r="BB2">
-        <v>0.374611078695301</v>
+        <v>0.4358148432830151</v>
       </c>
       <c r="BC2">
-        <v>0.374611078695301</v>
+        <v>0.4165441450347229</v>
       </c>
       <c r="BD2">
-        <v>0.343704507136839</v>
+        <v>0.3972734467864307</v>
       </c>
       <c r="BE2">
-        <v>0.343704507136839</v>
+        <v>0.3780027485381385</v>
       </c>
       <c r="BF2">
-        <v>0.3203556284675187</v>
+        <v>0.3601155234287792</v>
       </c>
       <c r="BG2">
-        <v>0.2970067497981985</v>
+        <v>0.3422282983194198</v>
       </c>
       <c r="BH2">
-        <v>0.2970067497981985</v>
+        <v>0.3243410732100605</v>
       </c>
       <c r="BI2">
-        <v>0.2970067497981985</v>
+        <v>0.3064538481007011</v>
       </c>
       <c r="BJ2">
-        <v>0.2970067497981985</v>
+        <v>0.2885666229913418</v>
       </c>
       <c r="BK2">
-        <v>0.2970067497981985</v>
+        <v>0.2693778285911284</v>
       </c>
       <c r="BL2">
-        <v>0.2970067497981985</v>
+        <v>0.250189034190915</v>
       </c>
       <c r="BM2">
-        <v>0.2970067497981985</v>
+        <v>0.2310002397907017</v>
       </c>
       <c r="BN2">
-        <v>0.2970067497981985</v>
+        <v>0.2910002397907017</v>
       </c>
       <c r="BO2">
-        <v>0.2970067497981985</v>
+        <v>0.2674525374731269</v>
       </c>
       <c r="BP2">
-        <v>0.2970067497981985</v>
+        <v>0.2439048351555522</v>
       </c>
       <c r="BQ2">
-        <v>0.2970067497981985</v>
+        <v>0.3039048351555522</v>
       </c>
       <c r="BR2">
-        <v>0.2743359004041396</v>
+        <v>0.2861781302227294</v>
       </c>
       <c r="BS2">
-        <v>0.2516650510100815</v>
+        <v>0.2684514252899066</v>
       </c>
       <c r="BT2">
-        <v>0.2516650510100815</v>
+        <v>0.2507247203570838</v>
       </c>
       <c r="BU2">
-        <v>0.2516650510100815</v>
+        <v>0.232998015424261</v>
       </c>
       <c r="BV2">
-        <v>0.2516650510100815</v>
+        <v>0.2152713104914382</v>
       </c>
       <c r="BW2">
-        <v>0.2306101602092255</v>
+        <v>0.2152713104914382</v>
       </c>
       <c r="BX2">
-        <v>0.2095552694083694</v>
+        <v>0.2152713104914382</v>
       </c>
       <c r="BY2">
-        <v>0.2095552694083694</v>
+        <v>0.2152713104914382</v>
       </c>
       <c r="BZ2">
-        <v>0.2095552694083694</v>
+        <v>0.2152713104914382</v>
       </c>
       <c r="CA2">
-        <v>0.2695552694083694</v>
+        <v>0.2152713104914382</v>
       </c>
       <c r="CB2">
-        <v>0.2395126429610256</v>
+        <v>0.2152713104914382</v>
       </c>
       <c r="CC2">
-        <v>0.2094700165136817</v>
+        <v>0.2152713104914382</v>
       </c>
       <c r="CD2">
-        <v>0.2094700165136817</v>
+        <v>0.2152713104914382</v>
       </c>
       <c r="CE2">
-        <v>0.2694700165136813</v>
+        <v>0.2152713104914382</v>
       </c>
       <c r="CF2">
-        <v>0.2694700165136813</v>
+        <v>0.2752713104914382</v>
       </c>
       <c r="CG2">
-        <v>0.2694700165136813</v>
+        <v>0.2752713104914382</v>
       </c>
       <c r="CH2">
-        <v>0.2694700165136813</v>
+        <v>0.2752713104914382</v>
       </c>
       <c r="CI2">
-        <v>0.2694700165136813</v>
+        <v>0.2752713104914382</v>
       </c>
       <c r="CJ2">
-        <v>0.2694700165136813</v>
+        <v>0.2752713104914382</v>
       </c>
       <c r="CK2">
-        <v>0.2694700165136813</v>
+        <v>0.2540205223144222</v>
       </c>
       <c r="CL2">
-        <v>0.2694700165136813</v>
+        <v>0.2327697341374061</v>
       </c>
       <c r="CM2">
-        <v>0.2694700165136813</v>
+        <v>0.2115189459603901</v>
       </c>
       <c r="CN2">
-        <v>0.2365274489466466</v>
+        <v>0.2115189459603901</v>
       </c>
       <c r="CO2">
-        <v>0.2035848813796119</v>
+        <v>0.2115189459603901</v>
       </c>
       <c r="CP2">
-        <v>0.2035848813796119</v>
+        <v>0.2115189459603901</v>
       </c>
       <c r="CQ2">
-        <v>0.2035848813796119</v>
+        <v>0.2115189459603901</v>
       </c>
       <c r="CR2">
-        <v>0.2035848813796119</v>
+        <v>0.2115189459603901</v>
       </c>
       <c r="CS2">
-        <v>0.2035848813796119</v>
+        <v>0.2115189459603901</v>
       </c>
     </row>
     <row r="3" spans="1:97">
@@ -2244,7 +2244,7 @@
         <v>0.2</v>
       </c>
       <c r="F3">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="G3">
         <v>0.26</v>
@@ -2253,49 +2253,49 @@
         <v>0.26</v>
       </c>
       <c r="I3">
+        <v>0.26</v>
+      </c>
+      <c r="J3">
+        <v>0.26</v>
+      </c>
+      <c r="K3">
+        <v>0.26</v>
+      </c>
+      <c r="L3">
+        <v>0.26</v>
+      </c>
+      <c r="M3">
         <v>0.32</v>
       </c>
-      <c r="J3">
+      <c r="N3">
         <v>0.32</v>
       </c>
-      <c r="K3">
+      <c r="O3">
         <v>0.32</v>
-      </c>
-      <c r="L3">
-        <v>0.38</v>
-      </c>
-      <c r="M3">
-        <v>0.38</v>
-      </c>
-      <c r="N3">
-        <v>0.38</v>
-      </c>
-      <c r="O3">
-        <v>0.38</v>
       </c>
       <c r="P3">
         <v>0.38</v>
       </c>
       <c r="Q3">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="R3">
         <v>0.44</v>
       </c>
       <c r="S3">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="T3">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="U3">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="V3">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="W3">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="X3">
         <v>0.5</v>
@@ -2307,217 +2307,217 @@
         <v>0.5</v>
       </c>
       <c r="AA3">
-        <v>0.5</v>
+        <v>0.4806640571439741</v>
       </c>
       <c r="AB3">
-        <v>0.5600000000000001</v>
+        <v>0.4613281142879488</v>
       </c>
       <c r="AC3">
-        <v>0.5600000000000001</v>
+        <v>0.4419921714319237</v>
       </c>
       <c r="AD3">
-        <v>0.5600000000000001</v>
+        <v>0.4226562285758985</v>
       </c>
       <c r="AE3">
-        <v>0.5600000000000001</v>
+        <v>0.406332137524561</v>
       </c>
       <c r="AF3">
-        <v>0.5442138247966215</v>
+        <v>0.3900080464732236</v>
       </c>
       <c r="AG3">
-        <v>0.5284276495932435</v>
+        <v>0.3736839554218861</v>
       </c>
       <c r="AH3">
-        <v>0.5126414743898655</v>
+        <v>0.3573598643705486</v>
       </c>
       <c r="AI3">
-        <v>0.4968552991864876</v>
+        <v>0.3410357733192111</v>
       </c>
       <c r="AJ3">
-        <v>0.4810691239831095</v>
+        <v>0.3215774175233992</v>
       </c>
       <c r="AK3">
-        <v>0.4652829487797316</v>
+        <v>0.3021190617275873</v>
       </c>
       <c r="AL3">
-        <v>0.4652829487797316</v>
+        <v>0.2826607059317754</v>
       </c>
       <c r="AM3">
-        <v>0.4652829487797305</v>
+        <v>0.2632023501359635</v>
       </c>
       <c r="AN3">
-        <v>0.4652829487797305</v>
+        <v>0.2437439943401516</v>
       </c>
       <c r="AO3">
-        <v>0.4652829487797305</v>
+        <v>0.3037439943401516</v>
       </c>
       <c r="AP3">
-        <v>0.4652829487797305</v>
+        <v>0.3637439943401516</v>
       </c>
       <c r="AQ3">
-        <v>0.4652829487797305</v>
+        <v>0.4237439943401519</v>
       </c>
       <c r="AR3">
-        <v>0.4652829487797305</v>
+        <v>0.4237439943401519</v>
       </c>
       <c r="AS3">
-        <v>0.4652829487797305</v>
+        <v>0.4237439943401519</v>
       </c>
       <c r="AT3">
-        <v>0.4652829487797305</v>
+        <v>0.4837439943401519</v>
       </c>
       <c r="AU3">
-        <v>0.4619020869243086</v>
+        <v>0.4659422208935852</v>
       </c>
       <c r="AV3">
-        <v>0.4585212250688867</v>
+        <v>0.4481404474470185</v>
       </c>
       <c r="AW3">
-        <v>0.4551403632134648</v>
+        <v>0.4303386740004519</v>
       </c>
       <c r="AX3">
-        <v>0.4517595013580429</v>
+        <v>0.4125369005538853</v>
       </c>
       <c r="AY3">
-        <v>0.448378639502621</v>
+        <v>0.3932172601036166</v>
       </c>
       <c r="AZ3">
-        <v>0.4449977776471991</v>
+        <v>0.373897619653348</v>
       </c>
       <c r="BA3">
-        <v>0.4416169157917772</v>
+        <v>0.3545779792030794</v>
       </c>
       <c r="BB3">
-        <v>0.4416169157917772</v>
+        <v>0.3352583387528107</v>
       </c>
       <c r="BC3">
-        <v>0.4178067422722279</v>
+        <v>0.3352583387528107</v>
       </c>
       <c r="BD3">
-        <v>0.3939965687526785</v>
+        <v>0.3952583387528107</v>
       </c>
       <c r="BE3">
-        <v>0.3939965687526785</v>
+        <v>0.3767085222193005</v>
       </c>
       <c r="BF3">
-        <v>0.3939965687526797</v>
+        <v>0.3581587056857901</v>
       </c>
       <c r="BG3">
-        <v>0.3939965687526809</v>
+        <v>0.3396088891522798</v>
       </c>
       <c r="BH3">
-        <v>0.3939965687526809</v>
+        <v>0.3210590726187695</v>
       </c>
       <c r="BI3">
-        <v>0.3939965687526809</v>
+        <v>0.3025092560852591</v>
       </c>
       <c r="BJ3">
-        <v>0.3737306841718001</v>
+        <v>0.3025092560852591</v>
       </c>
       <c r="BK3">
-        <v>0.3534647995909193</v>
+        <v>0.2882283293277061</v>
       </c>
       <c r="BL3">
-        <v>0.3534647995909193</v>
+        <v>0.273947402570153</v>
       </c>
       <c r="BM3">
-        <v>0.3534647995909193</v>
+        <v>0.2596664758126</v>
       </c>
       <c r="BN3">
-        <v>0.3534647995909193</v>
+        <v>0.245385549055047</v>
       </c>
       <c r="BO3">
-        <v>0.3534647995909193</v>
+        <v>0.2311046222974939</v>
       </c>
       <c r="BP3">
-        <v>0.3534647995909193</v>
+        <v>0.2911046222974939</v>
       </c>
       <c r="BQ3">
-        <v>0.3174346334338564</v>
+        <v>0.26973808808743</v>
       </c>
       <c r="BR3">
-        <v>0.2814044672767934</v>
+        <v>0.2483715538773661</v>
       </c>
       <c r="BS3">
-        <v>0.2814044672767934</v>
+        <v>0.2270050196673022</v>
       </c>
       <c r="BT3">
-        <v>0.2814044672767934</v>
+        <v>0.2870050196673022</v>
       </c>
       <c r="BU3">
-        <v>0.2607988834852993</v>
+        <v>0.2617394311124572</v>
       </c>
       <c r="BV3">
-        <v>0.2607988834852993</v>
+        <v>0.2364738425576121</v>
       </c>
       <c r="BW3">
-        <v>0.2607988834852993</v>
+        <v>0.2364738425576121</v>
       </c>
       <c r="BX3">
-        <v>0.2607988834852993</v>
+        <v>0.2964738425576121</v>
       </c>
       <c r="BY3">
-        <v>0.2607988834852993</v>
+        <v>0.275764623318649</v>
       </c>
       <c r="BZ3">
-        <v>0.2607988834852993</v>
+        <v>0.255055404079686</v>
       </c>
       <c r="CA3">
-        <v>0.2330282371969012</v>
+        <v>0.2343461848407229</v>
       </c>
       <c r="CB3">
-        <v>0.2930282371969011</v>
+        <v>0.2136369656017599</v>
       </c>
       <c r="CC3">
-        <v>0.2707058749187146</v>
+        <v>0.2736369656017599</v>
       </c>
       <c r="CD3">
-        <v>0.2483835126405279</v>
+        <v>0.3336369656017599</v>
       </c>
       <c r="CE3">
-        <v>0.2259237420819774</v>
+        <v>0.3137772225483645</v>
       </c>
       <c r="CF3">
-        <v>0.203463971523427</v>
+        <v>0.2939174794949692</v>
       </c>
       <c r="CG3">
-        <v>0.203463971523427</v>
+        <v>0.2740577364415739</v>
       </c>
       <c r="CH3">
-        <v>0.203463971523427</v>
+        <v>0.2541979933881786</v>
       </c>
       <c r="CI3">
-        <v>0.203463971523427</v>
+        <v>0.2541979933881786</v>
       </c>
       <c r="CJ3">
-        <v>0.203463971523427</v>
+        <v>0.2541979933881786</v>
       </c>
       <c r="CK3">
-        <v>0.203463971523427</v>
+        <v>0.2541979933881786</v>
       </c>
       <c r="CL3">
-        <v>0.203463971523427</v>
+        <v>0.2541979933881786</v>
       </c>
       <c r="CM3">
-        <v>0.203463971523427</v>
+        <v>0.2271677713245309</v>
       </c>
       <c r="CN3">
-        <v>0.203463971523427</v>
+        <v>0.2001375492608821</v>
       </c>
       <c r="CO3">
-        <v>0.203463971523427</v>
+        <v>0.2001375492608821</v>
       </c>
       <c r="CP3">
-        <v>0.203463971523427</v>
+        <v>0.2001375492608821</v>
       </c>
       <c r="CQ3">
-        <v>0.203463971523427</v>
+        <v>0.2001375492608821</v>
       </c>
       <c r="CR3">
-        <v>0.203463971523427</v>
+        <v>0.2001375492608821</v>
       </c>
       <c r="CS3">
-        <v>0.203463971523427</v>
+        <v>0.2001375492608821</v>
       </c>
     </row>
     <row r="4" spans="1:97">
@@ -2531,13 +2531,13 @@
         <v>0.2</v>
       </c>
       <c r="D4">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="E4">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="F4">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="G4">
         <v>0.38</v>
@@ -2546,7 +2546,7 @@
         <v>0.38</v>
       </c>
       <c r="I4">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="J4">
         <v>0.44</v>
@@ -2561,22 +2561,22 @@
         <v>0.44</v>
       </c>
       <c r="N4">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O4">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="P4">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="Q4">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="R4">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="S4">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="T4">
         <v>0.5</v>
@@ -2588,229 +2588,229 @@
         <v>0.5</v>
       </c>
       <c r="W4">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="X4">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="Y4">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="Z4">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AA4">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AB4">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="AC4">
-        <v>0.6104333071067526</v>
+        <v>0.4809906393856638</v>
       </c>
       <c r="AD4">
-        <v>0.6008666142135062</v>
+        <v>0.4619812787713293</v>
       </c>
       <c r="AE4">
-        <v>0.59129992132026</v>
+        <v>0.4429719181569948</v>
       </c>
       <c r="AF4">
-        <v>0.5817332284270137</v>
+        <v>0.4239625575426602</v>
       </c>
       <c r="AG4">
-        <v>0.5721665355337674</v>
+        <v>0.4049531969283257</v>
       </c>
       <c r="AH4">
-        <v>0.562599842640521</v>
+        <v>0.3813040715180903</v>
       </c>
       <c r="AI4">
-        <v>0.5530331497472747</v>
+        <v>0.357654946107855</v>
       </c>
       <c r="AJ4">
-        <v>0.5249456792370554</v>
+        <v>0.3340058206976197</v>
       </c>
       <c r="AK4">
-        <v>0.496858208726836</v>
+        <v>0.3940058206976197</v>
       </c>
       <c r="AL4">
-        <v>0.4687707382166167</v>
+        <v>0.4540058206976197</v>
       </c>
       <c r="AM4">
-        <v>0.4687707382166167</v>
+        <v>0.4337088945195864</v>
       </c>
       <c r="AN4">
-        <v>0.4687707382166167</v>
+        <v>0.413411968341553</v>
       </c>
       <c r="AO4">
-        <v>0.4687707382166167</v>
+        <v>0.3931150421635196</v>
       </c>
       <c r="AP4">
-        <v>0.4687707382166167</v>
+        <v>0.3728181159854863</v>
       </c>
       <c r="AQ4">
-        <v>0.4687707382166167</v>
+        <v>0.432818115985486</v>
       </c>
       <c r="AR4">
-        <v>0.4687707382166167</v>
+        <v>0.492818115985486</v>
       </c>
       <c r="AS4">
-        <v>0.4687707382166167</v>
+        <v>0.4673907693564386</v>
       </c>
       <c r="AT4">
-        <v>0.4687707382166167</v>
+        <v>0.4419634227273911</v>
       </c>
       <c r="AU4">
-        <v>0.4687707382166167</v>
+        <v>0.4165360760983435</v>
       </c>
       <c r="AV4">
-        <v>0.4687707382166167</v>
+        <v>0.3927792753471431</v>
       </c>
       <c r="AW4">
-        <v>0.4687707382166167</v>
+        <v>0.3690224745959426</v>
       </c>
       <c r="AX4">
-        <v>0.4451372442361417</v>
+        <v>0.3452656738447422</v>
       </c>
       <c r="AY4">
-        <v>0.4215037502556667</v>
+        <v>0.4052656738447422</v>
       </c>
       <c r="AZ4">
-        <v>0.4215037502556667</v>
+        <v>0.387648201318392</v>
       </c>
       <c r="BA4">
-        <v>0.3858862326048152</v>
+        <v>0.3700307287920419</v>
       </c>
       <c r="BB4">
-        <v>0.3502687149539637</v>
+        <v>0.3524132562656917</v>
       </c>
       <c r="BC4">
-        <v>0.3502687149539637</v>
+        <v>0.3347957837393415</v>
       </c>
       <c r="BD4">
-        <v>0.3502687149539637</v>
+        <v>0.3171783112129914</v>
       </c>
       <c r="BE4">
-        <v>0.3133335114593242</v>
+        <v>0.3771783112129914</v>
       </c>
       <c r="BF4">
-        <v>0.2763983079646846</v>
+        <v>0.3524078790303181</v>
       </c>
       <c r="BG4">
-        <v>0.2763983079646846</v>
+        <v>0.3276374468476448</v>
       </c>
       <c r="BH4">
-        <v>0.2763983079646846</v>
+        <v>0.3876374468476448</v>
       </c>
       <c r="BI4">
-        <v>0.2763983079646846</v>
+        <v>0.367115239176771</v>
       </c>
       <c r="BJ4">
-        <v>0.2763983079646846</v>
+        <v>0.3465930315058973</v>
       </c>
       <c r="BK4">
-        <v>0.2763983079646846</v>
+        <v>0.3260708238350235</v>
       </c>
       <c r="BL4">
-        <v>0.2065442574288248</v>
+        <v>0.3113353165867008</v>
       </c>
       <c r="BM4">
-        <v>0.2065442574288248</v>
+        <v>0.296599809338378</v>
       </c>
       <c r="BN4">
-        <v>0.2065442574288248</v>
+        <v>0.2818643020900553</v>
       </c>
       <c r="BO4">
-        <v>0.2065442574288248</v>
+        <v>0.2671287948417325</v>
       </c>
       <c r="BP4">
-        <v>0.2065442574288248</v>
+        <v>0.2523932875934098</v>
       </c>
       <c r="BQ4">
-        <v>0.2065442574288248</v>
+        <v>0.2376577803450871</v>
       </c>
       <c r="BR4">
-        <v>0.2065442574288248</v>
+        <v>0.2229222730967644</v>
       </c>
       <c r="BS4">
-        <v>0.2065442574288248</v>
+        <v>0.2229222730967644</v>
       </c>
       <c r="BT4">
-        <v>0.2065442574288248</v>
+        <v>0.2829222730967643</v>
       </c>
       <c r="BU4">
-        <v>0.2065442574288248</v>
+        <v>0.2829222730967643</v>
       </c>
       <c r="BV4">
-        <v>0.2065442574288248</v>
+        <v>0.2829222730967643</v>
       </c>
       <c r="BW4">
-        <v>0.2065442574288248</v>
+        <v>0.2829222730967643</v>
       </c>
       <c r="BX4">
-        <v>0.2065442574288248</v>
+        <v>0.2829222730967643</v>
       </c>
       <c r="BY4">
-        <v>0.2065442574288248</v>
+        <v>0.2633234779175737</v>
       </c>
       <c r="BZ4">
-        <v>0.2065442574288248</v>
+        <v>0.2437246827383831</v>
       </c>
       <c r="CA4">
-        <v>0.2065442574288248</v>
+        <v>0.2241258875591924</v>
       </c>
       <c r="CB4">
-        <v>0.2065442574288248</v>
+        <v>0.2045270923800018</v>
       </c>
       <c r="CC4">
-        <v>0.2065442574288248</v>
+        <v>0.2045270923800018</v>
       </c>
       <c r="CD4">
-        <v>0.2065442574288248</v>
+        <v>0.2045270923800018</v>
       </c>
       <c r="CE4">
-        <v>0.2665442574288248</v>
+        <v>0.2045270923800018</v>
       </c>
       <c r="CF4">
-        <v>0.2337679312967763</v>
+        <v>0.2045270923800018</v>
       </c>
       <c r="CG4">
-        <v>0.2009916051647277</v>
+        <v>0.2045270923800018</v>
       </c>
       <c r="CH4">
-        <v>0.2009916051647277</v>
+        <v>0.2045270923800018</v>
       </c>
       <c r="CI4">
-        <v>0.2009916051647277</v>
+        <v>0.2045270923800018</v>
       </c>
       <c r="CJ4">
-        <v>0.2009916051647277</v>
+        <v>0.2045270923800018</v>
       </c>
       <c r="CK4">
-        <v>0.2009916051647277</v>
+        <v>0.2045270923800018</v>
       </c>
       <c r="CL4">
-        <v>0.2009916051647277</v>
+        <v>0.2045270923800018</v>
       </c>
       <c r="CM4">
-        <v>0.2009916051647277</v>
+        <v>0.2045270923800018</v>
       </c>
       <c r="CN4">
-        <v>0.2009916051647277</v>
+        <v>0.2045270923800018</v>
       </c>
       <c r="CO4">
-        <v>0.2009916051647277</v>
+        <v>0.2045270923800018</v>
       </c>
       <c r="CP4">
-        <v>0.2009916051647277</v>
+        <v>0.2045270923800018</v>
       </c>
       <c r="CQ4">
-        <v>0.2009916051647277</v>
+        <v>0.2045270923800018</v>
       </c>
       <c r="CR4">
-        <v>0.2009916051647277</v>
+        <v>0.2045270923800018</v>
       </c>
       <c r="CS4">
-        <v>0.2009916051647277</v>
+        <v>0.2045270923800018</v>
       </c>
     </row>
     <row r="5" spans="1:97">
@@ -2821,67 +2821,67 @@
         <v>0.2</v>
       </c>
       <c r="C5">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="D5">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="E5">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="F5">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="G5">
+        <v>0.2</v>
+      </c>
+      <c r="H5">
+        <v>0.26</v>
+      </c>
+      <c r="I5">
+        <v>0.26</v>
+      </c>
+      <c r="J5">
+        <v>0.26</v>
+      </c>
+      <c r="K5">
+        <v>0.26</v>
+      </c>
+      <c r="L5">
         <v>0.32</v>
       </c>
-      <c r="H5">
+      <c r="M5">
         <v>0.32</v>
       </c>
-      <c r="I5">
+      <c r="N5">
+        <v>0.32</v>
+      </c>
+      <c r="O5">
+        <v>0.32</v>
+      </c>
+      <c r="P5">
+        <v>0.32</v>
+      </c>
+      <c r="Q5">
+        <v>0.32</v>
+      </c>
+      <c r="R5">
+        <v>0.32</v>
+      </c>
+      <c r="S5">
+        <v>0.32</v>
+      </c>
+      <c r="T5">
+        <v>0.32</v>
+      </c>
+      <c r="U5">
         <v>0.38</v>
       </c>
-      <c r="J5">
+      <c r="V5">
         <v>0.38</v>
       </c>
-      <c r="K5">
+      <c r="W5">
         <v>0.38</v>
-      </c>
-      <c r="L5">
-        <v>0.38</v>
-      </c>
-      <c r="M5">
-        <v>0.44</v>
-      </c>
-      <c r="N5">
-        <v>0.44</v>
-      </c>
-      <c r="O5">
-        <v>0.44</v>
-      </c>
-      <c r="P5">
-        <v>0.44</v>
-      </c>
-      <c r="Q5">
-        <v>0.44</v>
-      </c>
-      <c r="R5">
-        <v>0.44</v>
-      </c>
-      <c r="S5">
-        <v>0.44</v>
-      </c>
-      <c r="T5">
-        <v>0.44</v>
-      </c>
-      <c r="U5">
-        <v>0.44</v>
-      </c>
-      <c r="V5">
-        <v>0.44</v>
-      </c>
-      <c r="W5">
-        <v>0.44</v>
       </c>
       <c r="X5">
         <v>0.44</v>
@@ -2890,220 +2890,220 @@
         <v>0.44</v>
       </c>
       <c r="Z5">
+        <v>0.44</v>
+      </c>
+      <c r="AA5">
         <v>0.5</v>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AB5">
-        <v>0.5375288550706145</v>
-      </c>
       <c r="AC5">
-        <v>0.5150577101412291</v>
+        <v>0.5419917451160107</v>
       </c>
       <c r="AD5">
-        <v>0.4925865652118436</v>
+        <v>0.5239834902320217</v>
       </c>
       <c r="AE5">
-        <v>0.4925865652118436</v>
+        <v>0.5059752353480329</v>
       </c>
       <c r="AF5">
-        <v>0.4743188838073036</v>
+        <v>0.487966980464044</v>
       </c>
       <c r="AG5">
-        <v>0.4560512024027638</v>
+        <v>0.4699587255800551</v>
       </c>
       <c r="AH5">
-        <v>0.4560512024027638</v>
+        <v>0.4451995432404751</v>
       </c>
       <c r="AI5">
-        <v>0.4560512024027638</v>
+        <v>0.420440360900895</v>
       </c>
       <c r="AJ5">
-        <v>0.4560512024027638</v>
+        <v>0.395681178561315</v>
       </c>
       <c r="AK5">
-        <v>0.4560512024027638</v>
+        <v>0.3710251383501217</v>
       </c>
       <c r="AL5">
-        <v>0.4560512024027638</v>
+        <v>0.3463690981389285</v>
       </c>
       <c r="AM5">
-        <v>0.4560512024027638</v>
+        <v>0.3217130579277353</v>
       </c>
       <c r="AN5">
-        <v>0.4560512024027638</v>
+        <v>0.3817130579277353</v>
       </c>
       <c r="AO5">
-        <v>0.4560512024027638</v>
+        <v>0.3817130579277353</v>
       </c>
       <c r="AP5">
-        <v>0.4560512024027633</v>
+        <v>0.3817130579277353</v>
       </c>
       <c r="AQ5">
-        <v>0.4560512024027633</v>
+        <v>0.3554747047204152</v>
       </c>
       <c r="AR5">
-        <v>0.4560512024027633</v>
+        <v>0.3292363515130952</v>
       </c>
       <c r="AS5">
-        <v>0.4511018577276827</v>
+        <v>0.3029979983057751</v>
       </c>
       <c r="AT5">
-        <v>0.4461525130526022</v>
+        <v>0.3629979983057751</v>
       </c>
       <c r="AU5">
-        <v>0.4412031683775216</v>
+        <v>0.3629979983057751</v>
       </c>
       <c r="AV5">
-        <v>0.4362538237024411</v>
+        <v>0.3629979983057751</v>
       </c>
       <c r="AW5">
-        <v>0.4313044790273605</v>
+        <v>0.4229979983057751</v>
       </c>
       <c r="AX5">
-        <v>0.4022553678161501</v>
+        <v>0.4053213607114324</v>
       </c>
       <c r="AY5">
-        <v>0.3732062566049397</v>
+        <v>0.3876447231170898</v>
       </c>
       <c r="AZ5">
-        <v>0.3732062566049397</v>
+        <v>0.3699680855227471</v>
       </c>
       <c r="BA5">
-        <v>0.3732062566049397</v>
+        <v>0.3522914479284045</v>
       </c>
       <c r="BB5">
-        <v>0.3732062566049397</v>
+        <v>0.4122914479284045</v>
       </c>
       <c r="BC5">
-        <v>0.3732062566049397</v>
+        <v>0.4122914479284045</v>
       </c>
       <c r="BD5">
-        <v>0.3406133239927991</v>
+        <v>0.4122914479284045</v>
       </c>
       <c r="BE5">
-        <v>0.3080203913806587</v>
+        <v>0.4122914479284045</v>
       </c>
       <c r="BF5">
-        <v>0.2754274587685182</v>
+        <v>0.4722914479284045</v>
       </c>
       <c r="BG5">
-        <v>0.2754274587685182</v>
+        <v>0.44867243213897</v>
       </c>
       <c r="BH5">
-        <v>0.2754274587685182</v>
+        <v>0.4250534163495354</v>
       </c>
       <c r="BI5">
-        <v>0.2754274587685182</v>
+        <v>0.4014344005601008</v>
       </c>
       <c r="BJ5">
-        <v>0.2754274587685182</v>
+        <v>0.3811456463035514</v>
       </c>
       <c r="BK5">
-        <v>0.2754274587685182</v>
+        <v>0.3608568920470019</v>
       </c>
       <c r="BL5">
-        <v>0.2754274587685182</v>
+        <v>0.3405681377904524</v>
       </c>
       <c r="BM5">
-        <v>0.2754274587685182</v>
+        <v>0.3188498972473898</v>
       </c>
       <c r="BN5">
-        <v>0.2754274587685182</v>
+        <v>0.2971316567043272</v>
       </c>
       <c r="BO5">
-        <v>0.2754274587685182</v>
+        <v>0.2811740388147313</v>
       </c>
       <c r="BP5">
-        <v>0.2380553944404421</v>
+        <v>0.2652164209251354</v>
       </c>
       <c r="BQ5">
-        <v>0.2006833301123661</v>
+        <v>0.2492588030355395</v>
       </c>
       <c r="BR5">
-        <v>0.2006833301123661</v>
+        <v>0.2333011851459436</v>
       </c>
       <c r="BS5">
-        <v>0.2006833301123661</v>
+        <v>0.2173435672563477</v>
       </c>
       <c r="BT5">
-        <v>0.2006833301123661</v>
+        <v>0.2173435672563477</v>
       </c>
       <c r="BU5">
-        <v>0.2006833301123661</v>
+        <v>0.2173435672563477</v>
       </c>
       <c r="BV5">
-        <v>0.2006833301123661</v>
+        <v>0.2173435672563477</v>
       </c>
       <c r="BW5">
-        <v>0.2006833301123661</v>
+        <v>0.2173435672563477</v>
       </c>
       <c r="BX5">
-        <v>0.2006833301123661</v>
+        <v>0.2173435672563477</v>
       </c>
       <c r="BY5">
-        <v>0.2006833301123661</v>
+        <v>0.2173435672563477</v>
       </c>
       <c r="BZ5">
-        <v>0.2006833301123661</v>
+        <v>0.2173435672563477</v>
       </c>
       <c r="CA5">
-        <v>0.2006833301123661</v>
+        <v>0.2173435672563477</v>
       </c>
       <c r="CB5">
-        <v>0.2006833301123661</v>
+        <v>0.2173435672563477</v>
       </c>
       <c r="CC5">
-        <v>0.2006833301123661</v>
+        <v>0.2173435672563477</v>
       </c>
       <c r="CD5">
-        <v>0.2006833301123661</v>
+        <v>0.2773435672563477</v>
       </c>
       <c r="CE5">
-        <v>0.2006833301123661</v>
+        <v>0.2522375776403168</v>
       </c>
       <c r="CF5">
-        <v>0.2006833301123661</v>
+        <v>0.2271315880242859</v>
       </c>
       <c r="CG5">
-        <v>0.2006833301123661</v>
+        <v>0.2271315880242859</v>
       </c>
       <c r="CH5">
-        <v>0.2006833301123661</v>
+        <v>0.2271315880242859</v>
       </c>
       <c r="CI5">
-        <v>0.2006833301123661</v>
+        <v>0.2271315880242859</v>
       </c>
       <c r="CJ5">
-        <v>0.2006833301123661</v>
+        <v>0.2271315880242859</v>
       </c>
       <c r="CK5">
-        <v>0.2006833301123665</v>
+        <v>0.2271315880242859</v>
       </c>
       <c r="CL5">
-        <v>0.2006833301123665</v>
+        <v>0.2271315880242859</v>
       </c>
       <c r="CM5">
-        <v>0.2006833301123665</v>
+        <v>0.2271315880242859</v>
       </c>
       <c r="CN5">
-        <v>0.2006833301123665</v>
+        <v>0.2271315880242859</v>
       </c>
       <c r="CO5">
-        <v>0.2006833301123665</v>
+        <v>0.2271315880242859</v>
       </c>
       <c r="CP5">
-        <v>0.2006833301123665</v>
+        <v>0.2271315880242859</v>
       </c>
       <c r="CQ5">
-        <v>0.2006833301123665</v>
+        <v>0.2271315880242859</v>
       </c>
       <c r="CR5">
-        <v>0.2006833301123665</v>
+        <v>0.2271315880242859</v>
       </c>
       <c r="CS5">
-        <v>0.2006833301123665</v>
+        <v>0.2271315880242859</v>
       </c>
     </row>
     <row r="6" spans="1:97">
@@ -3120,283 +3120,283 @@
         <v>0.2</v>
       </c>
       <c r="E6">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="F6">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="G6">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="H6">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="I6">
-        <v>0.2</v>
+        <v>0.44</v>
       </c>
       <c r="J6">
-        <v>0.2</v>
+        <v>0.44</v>
       </c>
       <c r="K6">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="L6">
-        <v>0.32</v>
+        <v>0.5</v>
       </c>
       <c r="M6">
-        <v>0.32</v>
+        <v>0.5</v>
       </c>
       <c r="N6">
-        <v>0.32</v>
+        <v>0.5</v>
       </c>
       <c r="O6">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="P6">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="Q6">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="R6">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S6">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T6">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="U6">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="V6">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="W6">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="X6">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="Y6">
-        <v>0.5600000000000001</v>
+        <v>0.5974543124930836</v>
       </c>
       <c r="Z6">
-        <v>0.5600000000000001</v>
+        <v>0.5749086249861677</v>
       </c>
       <c r="AA6">
-        <v>0.5600000000000001</v>
+        <v>0.5523629374792518</v>
       </c>
       <c r="AB6">
-        <v>0.5387768192193318</v>
+        <v>0.5298172499723359</v>
       </c>
       <c r="AC6">
-        <v>0.5175536384386697</v>
+        <v>0.589817249972336</v>
       </c>
       <c r="AD6">
-        <v>0.4963304576580075</v>
+        <v>0.5722315749363536</v>
       </c>
       <c r="AE6">
-        <v>0.4963304576580075</v>
+        <v>0.5546458999003714</v>
       </c>
       <c r="AF6">
-        <v>0.4782130915599899</v>
+        <v>0.537060224864389</v>
       </c>
       <c r="AG6">
-        <v>0.4600957254619721</v>
+        <v>0.5194745498284067</v>
       </c>
       <c r="AH6">
-        <v>0.4419783593639544</v>
+        <v>0.5018888747924244</v>
       </c>
       <c r="AI6">
-        <v>0.4419783593639544</v>
+        <v>0.5618888747924243</v>
       </c>
       <c r="AJ6">
-        <v>0.4419783593639544</v>
+        <v>0.6218888747924244</v>
       </c>
       <c r="AK6">
-        <v>0.4419783593639544</v>
+        <v>0.6818888747924243</v>
       </c>
       <c r="AL6">
-        <v>0.4419783593639544</v>
+        <v>0.6624473106835929</v>
       </c>
       <c r="AM6">
-        <v>0.4419783593639544</v>
+        <v>0.6430057465747613</v>
       </c>
       <c r="AN6">
-        <v>0.4419783593639544</v>
+        <v>0.6235641824659298</v>
       </c>
       <c r="AO6">
-        <v>0.4419783593639544</v>
+        <v>0.6041226183570982</v>
       </c>
       <c r="AP6">
-        <v>0.4419783593639544</v>
+        <v>0.5846810542482668</v>
       </c>
       <c r="AQ6">
-        <v>0.4419783593639544</v>
+        <v>0.5647164298033193</v>
       </c>
       <c r="AR6">
-        <v>0.4419783593639544</v>
+        <v>0.5447518053583716</v>
       </c>
       <c r="AS6">
-        <v>0.4419783593639544</v>
+        <v>0.524787180913424</v>
       </c>
       <c r="AT6">
-        <v>0.4419783593639544</v>
+        <v>0.5048225564684765</v>
       </c>
       <c r="AU6">
-        <v>0.4419783593639544</v>
+        <v>0.4861852753807923</v>
       </c>
       <c r="AV6">
-        <v>0.4419783593639544</v>
+        <v>0.4675479942931079</v>
       </c>
       <c r="AW6">
-        <v>0.4419783593639544</v>
+        <v>0.4489107132054236</v>
       </c>
       <c r="AX6">
-        <v>0.4419783593639544</v>
+        <v>0.4302734321177394</v>
       </c>
       <c r="AY6">
-        <v>0.4186610819687361</v>
+        <v>0.40746254280377</v>
       </c>
       <c r="AZ6">
-        <v>0.3953438045735179</v>
+        <v>0.3846516534898006</v>
       </c>
       <c r="BA6">
-        <v>0.3953438045735179</v>
+        <v>0.3618407641758312</v>
       </c>
       <c r="BB6">
-        <v>0.3735586256003169</v>
+        <v>0.4218407641758312</v>
       </c>
       <c r="BC6">
-        <v>0.3517734466271159</v>
+        <v>0.3982242468992727</v>
       </c>
       <c r="BD6">
-        <v>0.3517734466271159</v>
+        <v>0.374607729622714</v>
       </c>
       <c r="BE6">
-        <v>0.3517734466271159</v>
+        <v>0.3509912123461555</v>
       </c>
       <c r="BF6">
-        <v>0.3517734466271159</v>
+        <v>0.3509912123461555</v>
       </c>
       <c r="BG6">
-        <v>0.3517734466271159</v>
+        <v>0.3509912123461555</v>
       </c>
       <c r="BH6">
-        <v>0.3170377145465882</v>
+        <v>0.3273749307671746</v>
       </c>
       <c r="BI6">
-        <v>0.2823019824660605</v>
+        <v>0.3037586491881936</v>
       </c>
       <c r="BJ6">
-        <v>0.2475662503855328</v>
+        <v>0.2801423676092127</v>
       </c>
       <c r="BK6">
-        <v>0.2475662503855328</v>
+        <v>0.2651667826902731</v>
       </c>
       <c r="BL6">
-        <v>0.2475662503855328</v>
+        <v>0.2501911977713335</v>
       </c>
       <c r="BM6">
-        <v>0.2335818613975818</v>
+        <v>0.235215612852394</v>
       </c>
       <c r="BN6">
-        <v>0.2195974724096309</v>
+        <v>0.2202400279334544</v>
       </c>
       <c r="BO6">
-        <v>0.2056130834216799</v>
+        <v>0.2052644430145148</v>
       </c>
       <c r="BP6">
-        <v>0.2056130834216797</v>
+        <v>0.265264443014515</v>
       </c>
       <c r="BQ6">
-        <v>0.2056130834216797</v>
+        <v>0.265264443014515</v>
       </c>
       <c r="BR6">
-        <v>0.2056130834216797</v>
+        <v>0.325264443014515</v>
       </c>
       <c r="BS6">
-        <v>0.2056130834216797</v>
+        <v>0.325264443014515</v>
       </c>
       <c r="BT6">
-        <v>0.2056130834216797</v>
+        <v>0.3052249088269512</v>
       </c>
       <c r="BU6">
-        <v>0.2056130834216797</v>
+        <v>0.2851853746393874</v>
       </c>
       <c r="BV6">
-        <v>0.2056130834216797</v>
+        <v>0.2651458404518237</v>
       </c>
       <c r="BW6">
-        <v>0.2056130834216797</v>
+        <v>0.2451063062642598</v>
       </c>
       <c r="BX6">
-        <v>0.2056130834216797</v>
+        <v>0.2250667720766961</v>
       </c>
       <c r="BY6">
-        <v>0.2056130834216797</v>
+        <v>0.2250667720766961</v>
       </c>
       <c r="BZ6">
-        <v>0.2056130834216797</v>
+        <v>0.2850667720766961</v>
       </c>
       <c r="CA6">
-        <v>0.2056130834216797</v>
+        <v>0.2638811972776136</v>
       </c>
       <c r="CB6">
-        <v>0.2056130834216797</v>
+        <v>0.2426956224785311</v>
       </c>
       <c r="CC6">
-        <v>0.2056130834216797</v>
+        <v>0.2215100476794485</v>
       </c>
       <c r="CD6">
-        <v>0.2056130834216797</v>
+        <v>0.2003244728803661</v>
       </c>
       <c r="CE6">
-        <v>0.2056130834216797</v>
+        <v>0.2003244728803661</v>
       </c>
       <c r="CF6">
-        <v>0.2056130834216797</v>
+        <v>0.2003244728803661</v>
       </c>
       <c r="CG6">
-        <v>0.2056130834216797</v>
+        <v>0.2003244728803661</v>
       </c>
       <c r="CH6">
-        <v>0.2056130834216797</v>
+        <v>0.2003244728803661</v>
       </c>
       <c r="CI6">
-        <v>0.2056130834216797</v>
+        <v>0.2003244728803661</v>
       </c>
       <c r="CJ6">
-        <v>0.2056130834216797</v>
+        <v>0.2003244728803661</v>
       </c>
       <c r="CK6">
-        <v>0.2056130834216797</v>
+        <v>0.2003244728803661</v>
       </c>
       <c r="CL6">
-        <v>0.2056130834216797</v>
+        <v>0.2003244728803661</v>
       </c>
       <c r="CM6">
-        <v>0.2056130834216797</v>
+        <v>0.2003244728803661</v>
       </c>
       <c r="CN6">
-        <v>0.2056130834216797</v>
+        <v>0.2003244728803661</v>
       </c>
       <c r="CO6">
-        <v>0.2056130834216797</v>
+        <v>0.2003244728803661</v>
       </c>
       <c r="CP6">
-        <v>0.2056130834216797</v>
+        <v>0.2003244728803661</v>
       </c>
       <c r="CQ6">
-        <v>0.2056130834216797</v>
+        <v>0.2003244728803661</v>
       </c>
       <c r="CR6">
-        <v>0.2056130834216797</v>
+        <v>0.2003244728803661</v>
       </c>
       <c r="CS6">
-        <v>0.2056130834216797</v>
+        <v>0.2003244728803661</v>
       </c>
     </row>
     <row r="7" spans="1:97">
@@ -3410,13 +3410,13 @@
         <v>0.2</v>
       </c>
       <c r="D7">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="E7">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="F7">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="G7">
         <v>0.26</v>
@@ -3437,259 +3437,259 @@
         <v>0.32</v>
       </c>
       <c r="M7">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="N7">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="O7">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="P7">
-        <v>0.32</v>
+        <v>0.5</v>
       </c>
       <c r="Q7">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="R7">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S7">
-        <v>0.38</v>
+        <v>0.62</v>
       </c>
       <c r="T7">
-        <v>0.38</v>
+        <v>0.62</v>
       </c>
       <c r="U7">
-        <v>0.38</v>
+        <v>0.62</v>
       </c>
       <c r="V7">
-        <v>0.38</v>
+        <v>0.5893560560300939</v>
       </c>
       <c r="W7">
-        <v>0.38</v>
+        <v>0.5587121120601876</v>
       </c>
       <c r="X7">
-        <v>0.3600912170101561</v>
+        <v>0.5280681680902812</v>
       </c>
       <c r="Y7">
-        <v>0.3401824340203123</v>
+        <v>0.52806816809028</v>
       </c>
       <c r="Z7">
-        <v>0.3202736510304685</v>
+        <v>0.52806816809028</v>
       </c>
       <c r="AA7">
-        <v>0.3003648680406238</v>
+        <v>0.5880681680902801</v>
       </c>
       <c r="AB7">
-        <v>0.2804560850507781</v>
+        <v>0.5880681680902801</v>
       </c>
       <c r="AC7">
-        <v>0.3404560850507781</v>
+        <v>0.64806816809028</v>
       </c>
       <c r="AD7">
-        <v>0.3404560850507781</v>
+        <v>0.6276738329854848</v>
       </c>
       <c r="AE7">
-        <v>0.3208060091031095</v>
+        <v>0.6072794978806897</v>
       </c>
       <c r="AF7">
-        <v>0.3011559331554408</v>
+        <v>0.5868851627758945</v>
       </c>
       <c r="AG7">
-        <v>0.2815058572077722</v>
+        <v>0.5696899294029236</v>
       </c>
       <c r="AH7">
-        <v>0.2620008603706872</v>
+        <v>0.5524946960299527</v>
       </c>
       <c r="AI7">
-        <v>0.2424958635336022</v>
+        <v>0.5352994626569819</v>
       </c>
       <c r="AJ7">
-        <v>0.2229908666965172</v>
+        <v>0.518104229284011</v>
       </c>
       <c r="AK7">
-        <v>0.2034858698594322</v>
+        <v>0.5009089959110402</v>
       </c>
       <c r="AL7">
-        <v>0.2034858698594322</v>
+        <v>0.5609089959110403</v>
       </c>
       <c r="AM7">
-        <v>0.2034858698594322</v>
+        <v>0.5344073633588019</v>
       </c>
       <c r="AN7">
-        <v>0.2034858698594322</v>
+        <v>0.5079057308065635</v>
       </c>
       <c r="AO7">
-        <v>0.2034858698594322</v>
+        <v>0.4814040982543252</v>
       </c>
       <c r="AP7">
-        <v>0.2034858698594322</v>
+        <v>0.461689784514733</v>
       </c>
       <c r="AQ7">
-        <v>0.2034858698594322</v>
+        <v>0.441975470775141</v>
       </c>
       <c r="AR7">
-        <v>0.2034858698594322</v>
+        <v>0.4222611570355488</v>
       </c>
       <c r="AS7">
-        <v>0.2034858698594322</v>
+        <v>0.4025468432959567</v>
       </c>
       <c r="AT7">
-        <v>0.2034858698594322</v>
+        <v>0.4625468432959567</v>
       </c>
       <c r="AU7">
-        <v>0.2034858698594322</v>
+        <v>0.4372061506341364</v>
       </c>
       <c r="AV7">
-        <v>0.2034858698594322</v>
+        <v>0.4118654579723161</v>
       </c>
       <c r="AW7">
-        <v>0.2034858698594322</v>
+        <v>0.3865247653104957</v>
       </c>
       <c r="AX7">
-        <v>0.2034858698594322</v>
+        <v>0.3612462506974944</v>
       </c>
       <c r="AY7">
-        <v>0.2034858698594322</v>
+        <v>0.3359677360844932</v>
       </c>
       <c r="AZ7">
-        <v>0.2034858698594322</v>
+        <v>0.3106892214714919</v>
       </c>
       <c r="BA7">
-        <v>0.2034858698594322</v>
+        <v>0.3706892214714919</v>
       </c>
       <c r="BB7">
-        <v>0.2034858698594322</v>
+        <v>0.4306892214714919</v>
       </c>
       <c r="BC7">
-        <v>0.2034858698594322</v>
+        <v>0.4306892214714919</v>
       </c>
       <c r="BD7">
-        <v>0.2034858698594322</v>
+        <v>0.4053119614861212</v>
       </c>
       <c r="BE7">
-        <v>0.2034858698594322</v>
+        <v>0.3799347015007504</v>
       </c>
       <c r="BF7">
-        <v>0.2034858698594322</v>
+        <v>0.362241078351744</v>
       </c>
       <c r="BG7">
-        <v>0.2034858698594322</v>
+        <v>0.3445474552027375</v>
       </c>
       <c r="BH7">
-        <v>0.2034858698594322</v>
+        <v>0.326853832053731</v>
       </c>
       <c r="BI7">
-        <v>0.2034858698594322</v>
+        <v>0.3091602089047245</v>
       </c>
       <c r="BJ7">
-        <v>0.2034858698594322</v>
+        <v>0.3091602089047245</v>
       </c>
       <c r="BK7">
-        <v>0.2034858698594322</v>
+        <v>0.2900976317373815</v>
       </c>
       <c r="BL7">
-        <v>0.2034858698594322</v>
+        <v>0.2710350545700385</v>
       </c>
       <c r="BM7">
-        <v>0.2034858698594322</v>
+        <v>0.2519724774026954</v>
       </c>
       <c r="BN7">
-        <v>0.2034858698594322</v>
+        <v>0.3119724774026954</v>
       </c>
       <c r="BO7">
-        <v>0.2034858698594322</v>
+        <v>0.3719724774026954</v>
       </c>
       <c r="BP7">
-        <v>0.2034858698594322</v>
+        <v>0.3544348662898841</v>
       </c>
       <c r="BQ7">
-        <v>0.2034858698594322</v>
+        <v>0.3368972551770726</v>
       </c>
       <c r="BR7">
-        <v>0.2034858698594322</v>
+        <v>0.3193596440642613</v>
       </c>
       <c r="BS7">
-        <v>0.2034858698594322</v>
+        <v>0.3018220329514499</v>
       </c>
       <c r="BT7">
-        <v>0.2034858698594322</v>
+        <v>0.2842844218386386</v>
       </c>
       <c r="BU7">
-        <v>0.2034858698594322</v>
+        <v>0.2642551024172511</v>
       </c>
       <c r="BV7">
-        <v>0.2034858698594322</v>
+        <v>0.2442257829958639</v>
       </c>
       <c r="BW7">
-        <v>0.2034858698594322</v>
+        <v>0.2241964635744765</v>
       </c>
       <c r="BX7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="BY7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="BZ7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CA7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CB7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CC7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CD7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CE7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CF7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CG7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CH7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CI7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CJ7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CK7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CL7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CM7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CN7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CO7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CP7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CQ7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CR7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
       <c r="CS7">
-        <v>0.2034858698594322</v>
+        <v>0.2041671441530891</v>
       </c>
     </row>
     <row r="8" spans="1:97">
@@ -3703,7 +3703,7 @@
         <v>0.2</v>
       </c>
       <c r="D8">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="E8">
         <v>0.26</v>
@@ -3718,43 +3718,43 @@
         <v>0.26</v>
       </c>
       <c r="I8">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="J8">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="K8">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="L8">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="M8">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="N8">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="O8">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="P8">
         <v>0.32</v>
       </c>
       <c r="Q8">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="R8">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="S8">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="T8">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="U8">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="V8">
         <v>0.38</v>
@@ -3769,220 +3769,220 @@
         <v>0.38</v>
       </c>
       <c r="Z8">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AA8">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="AB8">
-        <v>0.38</v>
+        <v>0.4751563496256966</v>
       </c>
       <c r="AC8">
-        <v>0.44</v>
+        <v>0.4503126992514002</v>
       </c>
       <c r="AD8">
-        <v>0.4213019258919735</v>
+        <v>0.4254690488771037</v>
       </c>
       <c r="AE8">
-        <v>0.4026038517839489</v>
+        <v>0.4059184351568124</v>
       </c>
       <c r="AF8">
-        <v>0.3839057776759243</v>
+        <v>0.3863678214365211</v>
       </c>
       <c r="AG8">
-        <v>0.3652077035678997</v>
+        <v>0.3668172077162297</v>
       </c>
       <c r="AH8">
-        <v>0.3449736684042762</v>
+        <v>0.3495186422874488</v>
       </c>
       <c r="AI8">
-        <v>0.3247396332406527</v>
+        <v>0.3322200768586679</v>
       </c>
       <c r="AJ8">
-        <v>0.3045055980770293</v>
+        <v>0.3149215114298871</v>
       </c>
       <c r="AK8">
-        <v>0.3045055980770293</v>
+        <v>0.2976229460011061</v>
       </c>
       <c r="AL8">
-        <v>0.3045055980770293</v>
+        <v>0.3576229460011061</v>
       </c>
       <c r="AM8">
-        <v>0.3045055980770293</v>
+        <v>0.4176229460011061</v>
       </c>
       <c r="AN8">
-        <v>0.3045055980770293</v>
+        <v>0.3973324398391512</v>
       </c>
       <c r="AO8">
-        <v>0.3045055980770293</v>
+        <v>0.3770419336771962</v>
       </c>
       <c r="AP8">
-        <v>0.3045055980770293</v>
+        <v>0.3567514275152411</v>
       </c>
       <c r="AQ8">
-        <v>0.3045055980770293</v>
+        <v>0.3364609213532861</v>
       </c>
       <c r="AR8">
-        <v>0.3045055980770293</v>
+        <v>0.3161704151913312</v>
       </c>
       <c r="AS8">
-        <v>0.3045055980770293</v>
+        <v>0.3761704151913312</v>
       </c>
       <c r="AT8">
-        <v>0.3045055980770293</v>
+        <v>0.4361704151913312</v>
       </c>
       <c r="AU8">
-        <v>0.3045055980770293</v>
+        <v>0.4961704151913311</v>
       </c>
       <c r="AV8">
-        <v>0.3045055980770293</v>
+        <v>0.4767420195589711</v>
       </c>
       <c r="AW8">
-        <v>0.3045055980770293</v>
+        <v>0.457313623926611</v>
       </c>
       <c r="AX8">
-        <v>0.3045055980770293</v>
+        <v>0.4378852282942509</v>
       </c>
       <c r="AY8">
-        <v>0.3045055980770293</v>
+        <v>0.4184568326618908</v>
       </c>
       <c r="AZ8">
-        <v>0.3045055980770293</v>
+        <v>0.3989212204274773</v>
       </c>
       <c r="BA8">
-        <v>0.3045055980770293</v>
+        <v>0.3793856081930638</v>
       </c>
       <c r="BB8">
-        <v>0.2780885807000272</v>
+        <v>0.3598499959586503</v>
       </c>
       <c r="BC8">
-        <v>0.2780885807000272</v>
+        <v>0.3403143837242367</v>
       </c>
       <c r="BD8">
-        <v>0.2780885807000272</v>
+        <v>0.3207787714898233</v>
       </c>
       <c r="BE8">
-        <v>0.2780885807000272</v>
+        <v>0.3807787714898233</v>
       </c>
       <c r="BF8">
-        <v>0.2780885807000272</v>
+        <v>0.3619846318458732</v>
       </c>
       <c r="BG8">
-        <v>0.2780885807000272</v>
+        <v>0.3431904922019231</v>
       </c>
       <c r="BH8">
-        <v>0.2780885807000272</v>
+        <v>0.3243963525579731</v>
       </c>
       <c r="BI8">
-        <v>0.2780885807000272</v>
+        <v>0.3056022129140231</v>
       </c>
       <c r="BJ8">
-        <v>0.2780885807000272</v>
+        <v>0.2883529354133824</v>
       </c>
       <c r="BK8">
-        <v>0.2631776533756086</v>
+        <v>0.2711036579127418</v>
       </c>
       <c r="BL8">
-        <v>0.2631776533756086</v>
+        <v>0.2538543804121012</v>
       </c>
       <c r="BM8">
-        <v>0.2468625614419611</v>
+        <v>0.2366051029114606</v>
       </c>
       <c r="BN8">
-        <v>0.2305474695083135</v>
+        <v>0.2193558254108199</v>
       </c>
       <c r="BO8">
-        <v>0.2305474695083135</v>
+        <v>0.2793558254108263</v>
       </c>
       <c r="BP8">
-        <v>0.2305474695083135</v>
+        <v>0.2585601056571514</v>
       </c>
       <c r="BQ8">
-        <v>0.2305474695083135</v>
+        <v>0.2377643859034764</v>
       </c>
       <c r="BR8">
-        <v>0.2305474695083135</v>
+        <v>0.2169686661498014</v>
       </c>
       <c r="BS8">
-        <v>0.2305474695083135</v>
+        <v>0.2169686661498002</v>
       </c>
       <c r="BT8">
-        <v>0.2305474695083135</v>
+        <v>0.2169686661497983</v>
       </c>
       <c r="BU8">
-        <v>0.2305474695083135</v>
+        <v>0.216968666149795</v>
       </c>
       <c r="BV8">
-        <v>0.2305474695083135</v>
+        <v>0.216968666149795</v>
       </c>
       <c r="BW8">
-        <v>0.2305474695083135</v>
+        <v>0.216968666149795</v>
       </c>
       <c r="BX8">
-        <v>0.2305474695083135</v>
+        <v>0.216968666149795</v>
       </c>
       <c r="BY8">
-        <v>0.2305474695083135</v>
+        <v>0.216968666149795</v>
       </c>
       <c r="BZ8">
-        <v>0.2305474695083135</v>
+        <v>0.216968666149795</v>
       </c>
       <c r="CA8">
-        <v>0.2305474695083135</v>
+        <v>0.216968666149795</v>
       </c>
       <c r="CB8">
-        <v>0.2305474695083135</v>
+        <v>0.216968666149795</v>
       </c>
       <c r="CC8">
-        <v>0.2305474695083135</v>
+        <v>0.276968666149795</v>
       </c>
       <c r="CD8">
-        <v>0.2305474695083135</v>
+        <v>0.276968666149795</v>
       </c>
       <c r="CE8">
-        <v>0.2305474695083135</v>
+        <v>0.276968666149795</v>
       </c>
       <c r="CF8">
-        <v>0.2305474695083135</v>
+        <v>0.276968666149795</v>
       </c>
       <c r="CG8">
-        <v>0.2063948939563891</v>
+        <v>0.276968666149795</v>
       </c>
       <c r="CH8">
-        <v>0.2063948939563891</v>
+        <v>0.276968666149795</v>
       </c>
       <c r="CI8">
-        <v>0.2063948939563891</v>
+        <v>0.276968666149795</v>
       </c>
       <c r="CJ8">
-        <v>0.2063948939563891</v>
+        <v>0.276968666149795</v>
       </c>
       <c r="CK8">
-        <v>0.2063948939563891</v>
+        <v>0.3369686661497968</v>
       </c>
       <c r="CL8">
-        <v>0.2036746731148371</v>
+        <v>0.3369686661497968</v>
       </c>
       <c r="CM8">
-        <v>0.2009544522732852</v>
+        <v>0.3133897087005691</v>
       </c>
       <c r="CN8">
-        <v>0.2009544522732852</v>
+        <v>0.2898107512513413</v>
       </c>
       <c r="CO8">
-        <v>0.2009544522732852</v>
+        <v>0.2662317938021136</v>
       </c>
       <c r="CP8">
-        <v>0.2009544522732852</v>
+        <v>0.2426528363528858</v>
       </c>
       <c r="CQ8">
-        <v>0.2009544522732852</v>
+        <v>0.2426528363528858</v>
       </c>
       <c r="CR8">
-        <v>0.2009544522732852</v>
+        <v>0.2426528363528858</v>
       </c>
       <c r="CS8">
-        <v>0.2009544522732852</v>
+        <v>0.2426528363528858</v>
       </c>
     </row>
     <row r="9" spans="1:97">
@@ -3993,7 +3993,7 @@
         <v>0.2</v>
       </c>
       <c r="C9">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="D9">
         <v>0.26</v>
@@ -4002,19 +4002,19 @@
         <v>0.26</v>
       </c>
       <c r="F9">
+        <v>0.26</v>
+      </c>
+      <c r="G9">
+        <v>0.26</v>
+      </c>
+      <c r="H9">
+        <v>0.26</v>
+      </c>
+      <c r="I9">
         <v>0.32</v>
       </c>
-      <c r="G9">
+      <c r="J9">
         <v>0.32</v>
-      </c>
-      <c r="H9">
-        <v>0.38</v>
-      </c>
-      <c r="I9">
-        <v>0.38</v>
-      </c>
-      <c r="J9">
-        <v>0.38</v>
       </c>
       <c r="K9">
         <v>0.38</v>
@@ -4026,256 +4026,256 @@
         <v>0.38</v>
       </c>
       <c r="N9">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="O9">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="P9">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q9">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R9">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S9">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T9">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="U9">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="V9">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="W9">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="X9">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="Y9">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="Z9">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="AA9">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="AB9">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="AC9">
-        <v>0.5422304216716025</v>
+        <v>0.8</v>
       </c>
       <c r="AD9">
-        <v>0.5244608433432156</v>
+        <v>0.7771270144370408</v>
       </c>
       <c r="AE9">
-        <v>0.5066912650148272</v>
+        <v>0.7542540288740816</v>
       </c>
       <c r="AF9">
-        <v>0.4889216866864359</v>
+        <v>0.7313810433111223</v>
       </c>
       <c r="AG9">
-        <v>0.471152108358046</v>
+        <v>0.7133538346896253</v>
       </c>
       <c r="AH9">
-        <v>0.471152108358046</v>
+        <v>0.6953266260681282</v>
       </c>
       <c r="AI9">
-        <v>0.4577562424539473</v>
+        <v>0.6772994174466311</v>
       </c>
       <c r="AJ9">
-        <v>0.4443603765498485</v>
+        <v>0.6592722088251342</v>
       </c>
       <c r="AK9">
-        <v>0.4309645106457498</v>
+        <v>0.6412450002036371</v>
       </c>
       <c r="AL9">
-        <v>0.4175686447416511</v>
+        <v>0.6209489762129039</v>
       </c>
       <c r="AM9">
-        <v>0.4175686447416511</v>
+        <v>0.6006529522221707</v>
       </c>
       <c r="AN9">
-        <v>0.4175686447415992</v>
+        <v>0.5803569282314375</v>
       </c>
       <c r="AO9">
-        <v>0.4175686447415954</v>
+        <v>0.5600609042407044</v>
       </c>
       <c r="AP9">
-        <v>0.4175686447415954</v>
+        <v>0.5600609042407044</v>
       </c>
       <c r="AQ9">
-        <v>0.4175686447415954</v>
+        <v>0.5420220990688732</v>
       </c>
       <c r="AR9">
-        <v>0.4175686447415871</v>
+        <v>0.523983293897042</v>
       </c>
       <c r="AS9">
-        <v>0.4175686447415833</v>
+        <v>0.5059444887252108</v>
       </c>
       <c r="AT9">
-        <v>0.4175686447415796</v>
+        <v>0.4879056835533796</v>
       </c>
       <c r="AU9">
-        <v>0.4175686447415769</v>
+        <v>0.5479056835533769</v>
       </c>
       <c r="AV9">
-        <v>0.4175686447415741</v>
+        <v>0.5292684665373106</v>
       </c>
       <c r="AW9">
-        <v>0.4175686447415714</v>
+        <v>0.5106312495212445</v>
       </c>
       <c r="AX9">
-        <v>0.4175686447415698</v>
+        <v>0.4919940325051783</v>
       </c>
       <c r="AY9">
-        <v>0.417568644741567</v>
+        <v>0.4733568154891122</v>
       </c>
       <c r="AZ9">
-        <v>0.417568644741567</v>
+        <v>0.4547195984730461</v>
       </c>
       <c r="BA9">
-        <v>0.417568644741567</v>
+        <v>0.514719598473046</v>
       </c>
       <c r="BB9">
-        <v>0.417568644741567</v>
+        <v>0.4956401394137691</v>
       </c>
       <c r="BC9">
-        <v>0.417568644741567</v>
+        <v>0.4765606803544922</v>
       </c>
       <c r="BD9">
-        <v>0.417568644741567</v>
+        <v>0.4574812212952152</v>
       </c>
       <c r="BE9">
-        <v>0.417568644741567</v>
+        <v>0.4384017622359383</v>
       </c>
       <c r="BF9">
-        <v>0.417568644741567</v>
+        <v>0.4984017622359383</v>
       </c>
       <c r="BG9">
-        <v>0.417568644741567</v>
+        <v>0.4807975575206442</v>
       </c>
       <c r="BH9">
-        <v>0.417568644741567</v>
+        <v>0.4631933528053502</v>
       </c>
       <c r="BI9">
-        <v>0.417568644741567</v>
+        <v>0.4455891480900562</v>
       </c>
       <c r="BJ9">
-        <v>0.417568644741567</v>
+        <v>0.4279849433747622</v>
       </c>
       <c r="BK9">
-        <v>0.417568644741567</v>
+        <v>0.4103807386594681</v>
       </c>
       <c r="BL9">
-        <v>0.417568644741567</v>
+        <v>0.3885311791132542</v>
       </c>
       <c r="BM9">
-        <v>0.3802640773878935</v>
+        <v>0.3666816195670402</v>
       </c>
       <c r="BN9">
-        <v>0.3429595100342199</v>
+        <v>0.3432945219182291</v>
       </c>
       <c r="BO9">
-        <v>0.3429595100342199</v>
+        <v>0.3199074242694188</v>
       </c>
       <c r="BP9">
-        <v>0.3429595100342199</v>
+        <v>0.3041926364572261</v>
       </c>
       <c r="BQ9">
-        <v>0.3429595100342199</v>
+        <v>0.2884778486450336</v>
       </c>
       <c r="BR9">
-        <v>0.3429595100342199</v>
+        <v>0.272763060832841</v>
       </c>
       <c r="BS9">
-        <v>0.3429595100342199</v>
+        <v>0.2570482730206484</v>
       </c>
       <c r="BT9">
-        <v>0.3429595100342199</v>
+        <v>0.2413334852084558</v>
       </c>
       <c r="BU9">
-        <v>0.3429595100342199</v>
+        <v>0.2413334852084558</v>
       </c>
       <c r="BV9">
-        <v>0.3142560252716685</v>
+        <v>0.3013334852084558</v>
       </c>
       <c r="BW9">
-        <v>0.285552540509117</v>
+        <v>0.2808341203444563</v>
       </c>
       <c r="BX9">
-        <v>0.2487847432396542</v>
+        <v>0.2603347554804568</v>
       </c>
       <c r="BY9">
-        <v>0.2120169459701909</v>
+        <v>0.2398353906164572</v>
       </c>
       <c r="BZ9">
-        <v>0.2120169459701909</v>
+        <v>0.2193360257524577</v>
       </c>
       <c r="CA9">
-        <v>0.2120169459701909</v>
+        <v>0.219336025752459</v>
       </c>
       <c r="CB9">
-        <v>0.2120169459701904</v>
+        <v>0.219336025752459</v>
       </c>
       <c r="CC9">
-        <v>0.2120169459701904</v>
+        <v>0.219336025752459</v>
       </c>
       <c r="CD9">
-        <v>0.2092855918772766</v>
+        <v>0.279336025752459</v>
       </c>
       <c r="CE9">
-        <v>0.2065542377843627</v>
+        <v>0.339336025752459</v>
       </c>
       <c r="CF9">
-        <v>0.2065542377843627</v>
+        <v>0.3188264514917695</v>
       </c>
       <c r="CG9">
-        <v>0.2065542377843634</v>
+        <v>0.29831687723108</v>
       </c>
       <c r="CH9">
-        <v>0.2065542377843634</v>
+        <v>0.2778073029703905</v>
       </c>
       <c r="CI9">
-        <v>0.2065542377843634</v>
+        <v>0.257297728709701</v>
       </c>
       <c r="CJ9">
-        <v>0.2065542377843634</v>
+        <v>0.2367881544490115</v>
       </c>
       <c r="CK9">
-        <v>0.2065542377843634</v>
+        <v>0.2967881544490115</v>
       </c>
       <c r="CL9">
-        <v>0.2065542377843634</v>
+        <v>0.2967881544490115</v>
       </c>
       <c r="CM9">
-        <v>0.2065542377843634</v>
+        <v>0.2967881544490115</v>
       </c>
       <c r="CN9">
-        <v>0.2065542377843634</v>
+        <v>0.2751785561797167</v>
       </c>
       <c r="CO9">
-        <v>0.2665542377843634</v>
+        <v>0.2535689579104219</v>
       </c>
       <c r="CP9">
-        <v>0.2336116702173287</v>
+        <v>0.2319593596411271</v>
       </c>
       <c r="CQ9">
-        <v>0.2006691026502939</v>
+        <v>0.2103497613718323</v>
       </c>
       <c r="CR9">
-        <v>0.2006691026502939</v>
+        <v>0.2103497613718323</v>
       </c>
       <c r="CS9">
-        <v>0.2006691026502939</v>
+        <v>0.2103497613718323</v>
       </c>
     </row>
     <row r="10" spans="1:97">
@@ -4289,286 +4289,286 @@
         <v>0.2</v>
       </c>
       <c r="D10">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="E10">
         <v>0.26</v>
       </c>
       <c r="F10">
+        <v>0.26</v>
+      </c>
+      <c r="G10">
+        <v>0.26</v>
+      </c>
+      <c r="H10">
+        <v>0.26</v>
+      </c>
+      <c r="I10">
+        <v>0.26</v>
+      </c>
+      <c r="J10">
+        <v>0.26</v>
+      </c>
+      <c r="K10">
+        <v>0.26</v>
+      </c>
+      <c r="L10">
+        <v>0.26</v>
+      </c>
+      <c r="M10">
+        <v>0.26</v>
+      </c>
+      <c r="N10">
+        <v>0.26</v>
+      </c>
+      <c r="O10">
         <v>0.32</v>
       </c>
-      <c r="G10">
-        <v>0.32</v>
-      </c>
-      <c r="H10">
-        <v>0.32</v>
-      </c>
-      <c r="I10">
+      <c r="P10">
         <v>0.38</v>
       </c>
-      <c r="J10">
+      <c r="Q10">
+        <v>0.38</v>
+      </c>
+      <c r="R10">
+        <v>0.38</v>
+      </c>
+      <c r="S10">
+        <v>0.38</v>
+      </c>
+      <c r="T10">
+        <v>0.38</v>
+      </c>
+      <c r="U10">
         <v>0.44</v>
       </c>
-      <c r="K10">
-        <v>0.44</v>
-      </c>
-      <c r="L10">
-        <v>0.44</v>
-      </c>
-      <c r="M10">
-        <v>0.44</v>
-      </c>
-      <c r="N10">
+      <c r="V10">
         <v>0.5</v>
       </c>
-      <c r="O10">
+      <c r="W10">
+        <v>0.5</v>
+      </c>
+      <c r="X10">
         <v>0.5600000000000001</v>
       </c>
-      <c r="P10">
+      <c r="Y10">
         <v>0.62</v>
       </c>
-      <c r="Q10">
-        <v>0.62</v>
-      </c>
-      <c r="R10">
-        <v>0.62</v>
-      </c>
-      <c r="S10">
+      <c r="Z10">
         <v>0.68</v>
       </c>
-      <c r="T10">
-        <v>0.68</v>
-      </c>
-      <c r="U10">
-        <v>0.68</v>
-      </c>
-      <c r="V10">
+      <c r="AA10">
         <v>0.74</v>
       </c>
-      <c r="W10">
+      <c r="AB10">
         <v>0.74</v>
       </c>
-      <c r="X10">
-        <v>0.8</v>
-      </c>
-      <c r="Y10">
-        <v>0.8</v>
-      </c>
-      <c r="Z10">
-        <v>0.7811378983886593</v>
-      </c>
-      <c r="AA10">
-        <v>0.7622757967773179</v>
-      </c>
-      <c r="AB10">
-        <v>0.7434136951659767</v>
-      </c>
       <c r="AC10">
-        <v>0.7245515935546353</v>
+        <v>0.7177484817785501</v>
       </c>
       <c r="AD10">
-        <v>0.7089812901007391</v>
+        <v>0.6954969635571003</v>
       </c>
       <c r="AE10">
-        <v>0.6934109866468429</v>
+        <v>0.6732454453356503</v>
       </c>
       <c r="AF10">
-        <v>0.6778406831929467</v>
+        <v>0.6530820064911094</v>
       </c>
       <c r="AG10">
-        <v>0.6622703797390505</v>
+        <v>0.6329185676465683</v>
       </c>
       <c r="AH10">
-        <v>0.6467000762851542</v>
+        <v>0.6127551288020273</v>
       </c>
       <c r="AI10">
-        <v>0.6284397998224265</v>
+        <v>0.5932269623388868</v>
       </c>
       <c r="AJ10">
-        <v>0.6101795233596988</v>
+        <v>0.5736987958757463</v>
       </c>
       <c r="AK10">
-        <v>0.5919192468969712</v>
+        <v>0.5541706294126059</v>
       </c>
       <c r="AL10">
-        <v>0.5736589704342434</v>
+        <v>0.5346424629494654</v>
       </c>
       <c r="AM10">
-        <v>0.5553986939715158</v>
+        <v>0.5151142964863249</v>
       </c>
       <c r="AN10">
-        <v>0.5553986939715158</v>
+        <v>0.4952129550814078</v>
       </c>
       <c r="AO10">
-        <v>0.5553986939715158</v>
+        <v>0.4753116136764907</v>
       </c>
       <c r="AP10">
-        <v>0.5553986939715158</v>
+        <v>0.4554102722715736</v>
       </c>
       <c r="AQ10">
-        <v>0.5553986939715158</v>
+        <v>0.4355089308666565</v>
       </c>
       <c r="AR10">
-        <v>0.5553986939715158</v>
+        <v>0.4155910341030704</v>
       </c>
       <c r="AS10">
-        <v>0.5553986939715158</v>
+        <v>0.3956731373394844</v>
       </c>
       <c r="AT10">
-        <v>0.5553986939715158</v>
+        <v>0.3757552405758983</v>
       </c>
       <c r="AU10">
-        <v>0.5553986939715158</v>
+        <v>0.3558373438123123</v>
       </c>
       <c r="AV10">
-        <v>0.5553986939715158</v>
+        <v>0.337257001281166</v>
       </c>
       <c r="AW10">
-        <v>0.5553986939715158</v>
+        <v>0.3186766587500198</v>
       </c>
       <c r="AX10">
-        <v>0.5368887957298368</v>
+        <v>0.3000963162188737</v>
       </c>
       <c r="AY10">
-        <v>0.5368887957298368</v>
+        <v>0.2815159736877274</v>
       </c>
       <c r="AZ10">
-        <v>0.5368887957298368</v>
+        <v>0.2629356311565812</v>
       </c>
       <c r="BA10">
-        <v>0.5368887957298368</v>
+        <v>0.2629356311565812</v>
       </c>
       <c r="BB10">
-        <v>0.5368887957298368</v>
+        <v>0.2629356311565812</v>
       </c>
       <c r="BC10">
-        <v>0.5368887957298368</v>
+        <v>0.3229356311565812</v>
       </c>
       <c r="BD10">
-        <v>0.5368887957298368</v>
+        <v>0.3829356311565812</v>
       </c>
       <c r="BE10">
-        <v>0.509327590748287</v>
+        <v>0.3829356311565812</v>
       </c>
       <c r="BF10">
-        <v>0.4817663857667374</v>
+        <v>0.3829356311565812</v>
       </c>
       <c r="BG10">
-        <v>0.4817663857667374</v>
+        <v>0.3829356311565812</v>
       </c>
       <c r="BH10">
-        <v>0.4817663857667374</v>
+        <v>0.365154173166037</v>
       </c>
       <c r="BI10">
-        <v>0.4817663857667374</v>
+        <v>0.3473727151754927</v>
       </c>
       <c r="BJ10">
-        <v>0.4473217334264062</v>
+        <v>0.3295912571849485</v>
       </c>
       <c r="BK10">
-        <v>0.4128770810860751</v>
+        <v>0.3118097991944042</v>
       </c>
       <c r="BL10">
-        <v>0.3816508446431845</v>
+        <v>0.29402834120386</v>
       </c>
       <c r="BM10">
-        <v>0.350424608200294</v>
+        <v>0.2748952341388339</v>
       </c>
       <c r="BN10">
-        <v>0.350424608200294</v>
+        <v>0.2557621270738077</v>
       </c>
       <c r="BO10">
-        <v>0.350424608200294</v>
+        <v>0.2366290200087815</v>
       </c>
       <c r="BP10">
-        <v>0.350424608200294</v>
+        <v>0.2966290200087816</v>
       </c>
       <c r="BQ10">
-        <v>0.350424608200294</v>
+        <v>0.2966290200087813</v>
       </c>
       <c r="BR10">
-        <v>0.350424608200294</v>
+        <v>0.2778170377229974</v>
       </c>
       <c r="BS10">
-        <v>0.350424608200294</v>
+        <v>0.2590050554372136</v>
       </c>
       <c r="BT10">
-        <v>0.3126082669428175</v>
+        <v>0.2401930731514297</v>
       </c>
       <c r="BU10">
-        <v>0.2747919256853411</v>
+        <v>0.2213810908656458</v>
       </c>
       <c r="BV10">
-        <v>0.2747919256853411</v>
+        <v>0.202569108579862</v>
       </c>
       <c r="BW10">
-        <v>0.2490610404419049</v>
+        <v>0.202569108579862</v>
       </c>
       <c r="BX10">
-        <v>0.2490610404419049</v>
+        <v>0.202569108579862</v>
       </c>
       <c r="BY10">
-        <v>0.2490610404419049</v>
+        <v>0.202569108579862</v>
       </c>
       <c r="BZ10">
-        <v>0.2490610404419049</v>
+        <v>0.202569108579862</v>
       </c>
       <c r="CA10">
-        <v>0.2490610404419049</v>
+        <v>0.202569108579862</v>
       </c>
       <c r="CB10">
-        <v>0.2490610404419049</v>
+        <v>0.2625691085798618</v>
       </c>
       <c r="CC10">
-        <v>0.2490610404419049</v>
+        <v>0.2625691085798618</v>
       </c>
       <c r="CD10">
-        <v>0.2490610404419049</v>
+        <v>0.3225691085798618</v>
       </c>
       <c r="CE10">
-        <v>0.2490610404419054</v>
+        <v>0.3825691085798618</v>
       </c>
       <c r="CF10">
-        <v>0.2490610404419054</v>
+        <v>0.3615974896145728</v>
       </c>
       <c r="CG10">
-        <v>0.2267386781637188</v>
+        <v>0.3406258706492839</v>
       </c>
       <c r="CH10">
-        <v>0.2044163158855322</v>
+        <v>0.319654251683995</v>
       </c>
       <c r="CI10">
-        <v>0.2044163158855322</v>
+        <v>0.2986826327187061</v>
       </c>
       <c r="CJ10">
-        <v>0.2044163158855322</v>
+        <v>0.2686973102535549</v>
       </c>
       <c r="CK10">
-        <v>0.2044163158855322</v>
+        <v>0.2387119877884038</v>
       </c>
       <c r="CL10">
-        <v>0.2044163158855322</v>
+        <v>0.2087266653232527</v>
       </c>
       <c r="CM10">
-        <v>0.2044163158855322</v>
+        <v>0.2087266653232527</v>
       </c>
       <c r="CN10">
-        <v>0.2044163158855322</v>
+        <v>0.2087266653232527</v>
       </c>
       <c r="CO10">
-        <v>0.2044163158855322</v>
+        <v>0.2087266653232527</v>
       </c>
       <c r="CP10">
-        <v>0.2044163158855322</v>
+        <v>0.2087266653232527</v>
       </c>
       <c r="CQ10">
-        <v>0.2044163158855322</v>
+        <v>0.2087266653232527</v>
       </c>
       <c r="CR10">
-        <v>0.2044163158855322</v>
+        <v>0.2087266653232527</v>
       </c>
       <c r="CS10">
-        <v>0.2044163158855322</v>
+        <v>0.2087266653232527</v>
       </c>
     </row>
     <row r="11" spans="1:97">
@@ -4579,7 +4579,7 @@
         <v>0.2</v>
       </c>
       <c r="C11">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="D11">
         <v>0.26</v>
@@ -4606,40 +4606,40 @@
         <v>0.32</v>
       </c>
       <c r="L11">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="M11">
         <v>0.38</v>
       </c>
       <c r="N11">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="O11">
         <v>0.44</v>
       </c>
       <c r="P11">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="Q11">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="R11">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="S11">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="T11">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="U11">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="V11">
         <v>0.5</v>
       </c>
       <c r="W11">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="X11">
         <v>0.5600000000000001</v>
@@ -4648,220 +4648,220 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="Z11">
-        <v>0.5486415617055684</v>
+        <v>0.62</v>
       </c>
       <c r="AA11">
-        <v>0.537283123411137</v>
+        <v>0.62</v>
       </c>
       <c r="AB11">
-        <v>0.5259246851167055</v>
+        <v>0.68</v>
       </c>
       <c r="AC11">
-        <v>0.5145662468222741</v>
+        <v>0.6601193075693457</v>
       </c>
       <c r="AD11">
-        <v>0.5032078085278426</v>
+        <v>0.6402386151386924</v>
       </c>
       <c r="AE11">
-        <v>0.4918493702334111</v>
+        <v>0.6203579227080392</v>
       </c>
       <c r="AF11">
-        <v>0.4804909319389797</v>
+        <v>0.6004772302773861</v>
       </c>
       <c r="AG11">
-        <v>0.4691324936445482</v>
+        <v>0.5776055258388091</v>
       </c>
       <c r="AH11">
-        <v>0.4691324936445482</v>
+        <v>0.5547338214002321</v>
       </c>
       <c r="AI11">
-        <v>0.4691324936445482</v>
+        <v>0.5318621169616552</v>
       </c>
       <c r="AJ11">
-        <v>0.4691324936445482</v>
+        <v>0.5134615028990189</v>
       </c>
       <c r="AK11">
-        <v>0.4526316235931956</v>
+        <v>0.4950608888363828</v>
       </c>
       <c r="AL11">
-        <v>0.4361307535418431</v>
+        <v>0.4766602747737466</v>
       </c>
       <c r="AM11">
-        <v>0.4196298834904904</v>
+        <v>0.4582596607111089</v>
       </c>
       <c r="AN11">
-        <v>0.4196298834904904</v>
+        <v>0.5182596607111088</v>
       </c>
       <c r="AO11">
-        <v>0.4196298834904904</v>
+        <v>0.4937830199188439</v>
       </c>
       <c r="AP11">
-        <v>0.4196298834904904</v>
+        <v>0.4693063791265791</v>
       </c>
       <c r="AQ11">
-        <v>0.4196298834904904</v>
+        <v>0.4448297383343142</v>
       </c>
       <c r="AR11">
-        <v>0.4196298834904904</v>
+        <v>0.4253635272197601</v>
       </c>
       <c r="AS11">
-        <v>0.4196298834904904</v>
+        <v>0.4058973161052059</v>
       </c>
       <c r="AT11">
-        <v>0.4196298834904904</v>
+        <v>0.3864311049906518</v>
       </c>
       <c r="AU11">
-        <v>0.4196298834904904</v>
+        <v>0.3669648938760975</v>
       </c>
       <c r="AV11">
-        <v>0.3902111793655425</v>
+        <v>0.3474986827615433</v>
       </c>
       <c r="AW11">
-        <v>0.3607924752405945</v>
+        <v>0.3474986827615433</v>
       </c>
       <c r="AX11">
-        <v>0.3607924752405945</v>
+        <v>0.3474986827615433</v>
       </c>
       <c r="AY11">
-        <v>0.3607924752405945</v>
+        <v>0.4074986827615443</v>
       </c>
       <c r="AZ11">
-        <v>0.3607924752405945</v>
+        <v>0.3889002040009981</v>
       </c>
       <c r="BA11">
-        <v>0.3607924752405945</v>
+        <v>0.3703017252404517</v>
       </c>
       <c r="BB11">
-        <v>0.3607924752405945</v>
+        <v>0.3517032464799054</v>
       </c>
       <c r="BC11">
-        <v>0.3607924752405945</v>
+        <v>0.333104767719359</v>
       </c>
       <c r="BD11">
-        <v>0.3607924752405945</v>
+        <v>0.3145062889588127</v>
       </c>
       <c r="BE11">
-        <v>0.3607924752405945</v>
+        <v>0.3145062889588127</v>
       </c>
       <c r="BF11">
-        <v>0.3607924752405945</v>
+        <v>0.3745062889588127</v>
       </c>
       <c r="BG11">
-        <v>0.3607924752405945</v>
+        <v>0.4345062889588127</v>
       </c>
       <c r="BH11">
-        <v>0.3607924752405945</v>
+        <v>0.4091255951973653</v>
       </c>
       <c r="BI11">
-        <v>0.3607924752405945</v>
+        <v>0.3837449014359178</v>
       </c>
       <c r="BJ11">
-        <v>0.3607924752405945</v>
+        <v>0.3583642076744704</v>
       </c>
       <c r="BK11">
-        <v>0.3607924752405945</v>
+        <v>0.3431583570247252</v>
       </c>
       <c r="BL11">
-        <v>0.3607924752405945</v>
+        <v>0.3279525063749799</v>
       </c>
       <c r="BM11">
-        <v>0.3607924752405945</v>
+        <v>0.3127466557252346</v>
       </c>
       <c r="BN11">
-        <v>0.3607924752405945</v>
+        <v>0.2975408050754894</v>
       </c>
       <c r="BO11">
-        <v>0.3607924752405945</v>
+        <v>0.282334954425744</v>
       </c>
       <c r="BP11">
-        <v>0.2897916544298277</v>
+        <v>0.2671291037759988</v>
       </c>
       <c r="BQ11">
-        <v>0.2897916544298277</v>
+        <v>0.327129103775998</v>
       </c>
       <c r="BR11">
-        <v>0.2867306973566611</v>
+        <v>0.3105840403650258</v>
       </c>
       <c r="BS11">
-        <v>0.2867306973566611</v>
+        <v>0.2940389769540536</v>
       </c>
       <c r="BT11">
-        <v>0.2867306973566611</v>
+        <v>0.2774939135430814</v>
       </c>
       <c r="BU11">
-        <v>0.2867306973566611</v>
+        <v>0.2609488501321092</v>
       </c>
       <c r="BV11">
-        <v>0.2867306973566611</v>
+        <v>0.2444037867211371</v>
       </c>
       <c r="BW11">
-        <v>0.2867306973566611</v>
+        <v>0.2444037867211371</v>
       </c>
       <c r="BX11">
-        <v>0.2547049505573767</v>
+        <v>0.2444037867211371</v>
       </c>
       <c r="BY11">
-        <v>0.2226792037580924</v>
+        <v>0.2444037867211371</v>
       </c>
       <c r="BZ11">
-        <v>0.2226792037580924</v>
+        <v>0.2444037867211371</v>
       </c>
       <c r="CA11">
-        <v>0.2226792037580924</v>
+        <v>0.304403786721137</v>
       </c>
       <c r="CB11">
-        <v>0.2826792037580925</v>
+        <v>0.2843531285843829</v>
       </c>
       <c r="CC11">
-        <v>0.2826792037580925</v>
+        <v>0.2643024704476287</v>
       </c>
       <c r="CD11">
-        <v>0.2826792037580925</v>
+        <v>0.2442518123108745</v>
       </c>
       <c r="CE11">
-        <v>0.2615919779254638</v>
+        <v>0.2242011541741205</v>
       </c>
       <c r="CF11">
-        <v>0.2615919779254638</v>
+        <v>0.2041504960373663</v>
       </c>
       <c r="CG11">
-        <v>0.2615919779254638</v>
+        <v>0.2041504960373663</v>
       </c>
       <c r="CH11">
-        <v>0.2615919779254638</v>
+        <v>0.2041504960373668</v>
       </c>
       <c r="CI11">
-        <v>0.2615919779254638</v>
+        <v>0.2041504960373668</v>
       </c>
       <c r="CJ11">
-        <v>0.2615919779254638</v>
+        <v>0.2041504960373668</v>
       </c>
       <c r="CK11">
-        <v>0.2392685463907973</v>
+        <v>0.2641504960373668</v>
       </c>
       <c r="CL11">
-        <v>0.2169451148561308</v>
+        <v>0.2641504960373668</v>
       </c>
       <c r="CM11">
-        <v>0.2169451148561308</v>
+        <v>0.2427796373151021</v>
       </c>
       <c r="CN11">
-        <v>0.2169451148561308</v>
+        <v>0.2214087785928373</v>
       </c>
       <c r="CO11">
-        <v>0.2169451148561308</v>
+        <v>0.2000379198705726</v>
       </c>
       <c r="CP11">
-        <v>0.2169451148561308</v>
+        <v>0.2000379198705726</v>
       </c>
       <c r="CQ11">
-        <v>0.2169451148561308</v>
+        <v>0.2000379198705726</v>
       </c>
       <c r="CR11">
-        <v>0.2169451148561308</v>
+        <v>0.2000379198705726</v>
       </c>
       <c r="CS11">
-        <v>0.2169451148561308</v>
+        <v>0.2000379198705726</v>
       </c>
     </row>
     <row r="12" spans="1:97">
@@ -4875,34 +4875,34 @@
         <v>0.2</v>
       </c>
       <c r="D12">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="E12">
+        <v>0.2</v>
+      </c>
+      <c r="F12">
+        <v>0.2</v>
+      </c>
+      <c r="G12">
+        <v>0.2</v>
+      </c>
+      <c r="H12">
+        <v>0.26</v>
+      </c>
+      <c r="I12">
+        <v>0.26</v>
+      </c>
+      <c r="J12">
+        <v>0.26</v>
+      </c>
+      <c r="K12">
+        <v>0.26</v>
+      </c>
+      <c r="L12">
+        <v>0.26</v>
+      </c>
+      <c r="M12">
         <v>0.32</v>
-      </c>
-      <c r="F12">
-        <v>0.32</v>
-      </c>
-      <c r="G12">
-        <v>0.32</v>
-      </c>
-      <c r="H12">
-        <v>0.32</v>
-      </c>
-      <c r="I12">
-        <v>0.32</v>
-      </c>
-      <c r="J12">
-        <v>0.32</v>
-      </c>
-      <c r="K12">
-        <v>0.38</v>
-      </c>
-      <c r="L12">
-        <v>0.38</v>
-      </c>
-      <c r="M12">
-        <v>0.38</v>
       </c>
       <c r="N12">
         <v>0.38</v>
@@ -4911,250 +4911,250 @@
         <v>0.38</v>
       </c>
       <c r="P12">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="Q12">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="R12">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="S12">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="T12">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="U12">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V12">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="W12">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="X12">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="Y12">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="Z12">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="AA12">
-        <v>0.5405900293249486</v>
+        <v>0.6610821607085587</v>
       </c>
       <c r="AB12">
-        <v>0.5211800586498972</v>
+        <v>0.6421643214171175</v>
       </c>
       <c r="AC12">
-        <v>0.501770087974846</v>
+        <v>0.6232464821256762</v>
       </c>
       <c r="AD12">
-        <v>0.4823601172997947</v>
+        <v>0.604328642834235</v>
       </c>
       <c r="AE12">
-        <v>0.4629501466247435</v>
+        <v>0.5854108035427938</v>
       </c>
       <c r="AF12">
-        <v>0.4374079292756606</v>
+        <v>0.5687913235935745</v>
       </c>
       <c r="AG12">
-        <v>0.4118657119265776</v>
+        <v>0.5521718436443551</v>
       </c>
       <c r="AH12">
-        <v>0.4118657119265776</v>
+        <v>0.5355523636951358</v>
       </c>
       <c r="AI12">
-        <v>0.4118657119265776</v>
+        <v>0.5189328837459165</v>
       </c>
       <c r="AJ12">
-        <v>0.4118657119265776</v>
+        <v>0.5023134037966972</v>
       </c>
       <c r="AK12">
-        <v>0.4118657119265776</v>
+        <v>0.5623134037966971</v>
       </c>
       <c r="AL12">
-        <v>0.4118657119265776</v>
+        <v>0.5435754223438147</v>
       </c>
       <c r="AM12">
-        <v>0.4118657119265776</v>
+        <v>0.5248374408909323</v>
       </c>
       <c r="AN12">
-        <v>0.3833999768374609</v>
+        <v>0.5060994594380498</v>
       </c>
       <c r="AO12">
-        <v>0.3549342417483441</v>
+        <v>0.4873614779851673</v>
       </c>
       <c r="AP12">
-        <v>0.3264685066592273</v>
+        <v>0.5473614779851673</v>
       </c>
       <c r="AQ12">
-        <v>0.3264685066592273</v>
+        <v>0.5473614779851673</v>
       </c>
       <c r="AR12">
-        <v>0.3264685066592273</v>
+        <v>0.6073614779851674</v>
       </c>
       <c r="AS12">
-        <v>0.3264685066592273</v>
+        <v>0.6673614779851673</v>
       </c>
       <c r="AT12">
-        <v>0.3264685066592273</v>
+        <v>0.6479467219963192</v>
       </c>
       <c r="AU12">
-        <v>0.3264685066592273</v>
+        <v>0.628531966007471</v>
       </c>
       <c r="AV12">
-        <v>0.3264685066592273</v>
+        <v>0.6091172100186227</v>
       </c>
       <c r="AW12">
-        <v>0.3264685066592273</v>
+        <v>0.5897024540297745</v>
       </c>
       <c r="AX12">
-        <v>0.3264685066592273</v>
+        <v>0.5706299834191434</v>
       </c>
       <c r="AY12">
-        <v>0.3264685066592273</v>
+        <v>0.5515575128085124</v>
       </c>
       <c r="AZ12">
-        <v>0.3264685066592273</v>
+        <v>0.5324850421978812</v>
       </c>
       <c r="BA12">
-        <v>0.3264685066592273</v>
+        <v>0.51341257158725</v>
       </c>
       <c r="BB12">
-        <v>0.3264685066592273</v>
+        <v>0.495762741378206</v>
       </c>
       <c r="BC12">
-        <v>0.2937088277125853</v>
+        <v>0.4781129111691619</v>
       </c>
       <c r="BD12">
-        <v>0.2609491487659433</v>
+        <v>0.4604630809601177</v>
       </c>
       <c r="BE12">
-        <v>0.2609491487659433</v>
+        <v>0.4428132507510736</v>
       </c>
       <c r="BF12">
-        <v>0.2253807544926562</v>
+        <v>0.4241238030643112</v>
       </c>
       <c r="BG12">
-        <v>0.2253807544926562</v>
+        <v>0.4054343553775489</v>
       </c>
       <c r="BH12">
-        <v>0.2253807544926562</v>
+        <v>0.3867449076907866</v>
       </c>
       <c r="BI12">
-        <v>0.2253807544926562</v>
+        <v>0.3680554600040242</v>
       </c>
       <c r="BJ12">
-        <v>0.2253807544926562</v>
+        <v>0.3493660123172618</v>
       </c>
       <c r="BK12">
-        <v>0.2253807544926562</v>
+        <v>0.3247808327483062</v>
       </c>
       <c r="BL12">
-        <v>0.2253807544926562</v>
+        <v>0.3001956531793504</v>
       </c>
       <c r="BM12">
-        <v>0.2253807544926562</v>
+        <v>0.2858305344297045</v>
       </c>
       <c r="BN12">
-        <v>0.2253807544926562</v>
+        <v>0.2714654156800586</v>
       </c>
       <c r="BO12">
-        <v>0.2253807544926562</v>
+        <v>0.2571002969304128</v>
       </c>
       <c r="BP12">
-        <v>0.2253807544926562</v>
+        <v>0.2427351781807668</v>
       </c>
       <c r="BQ12">
-        <v>0.2253807544926562</v>
+        <v>0.2283700594311209</v>
       </c>
       <c r="BR12">
-        <v>0.2253807544926562</v>
+        <v>0.2283700594311209</v>
       </c>
       <c r="BS12">
-        <v>0.2253807544926562</v>
+        <v>0.2283700594311209</v>
       </c>
       <c r="BT12">
-        <v>0.2253807544926562</v>
+        <v>0.2283700594311209</v>
       </c>
       <c r="BU12">
-        <v>0.2253807544926562</v>
+        <v>0.2283700594311209</v>
       </c>
       <c r="BV12">
-        <v>0.2253807544926562</v>
+        <v>0.2283700594311209</v>
       </c>
       <c r="BW12">
-        <v>0.2253807544926562</v>
+        <v>0.2283700594311209</v>
       </c>
       <c r="BX12">
-        <v>0.2253807544926562</v>
+        <v>0.2283700594311209</v>
       </c>
       <c r="BY12">
-        <v>0.2253807544926562</v>
+        <v>0.2283700594311209</v>
       </c>
       <c r="BZ12">
-        <v>0.2253807544926562</v>
+        <v>0.2283700594311209</v>
       </c>
       <c r="CA12">
-        <v>0.2253807544926562</v>
+        <v>0.2883700594311209</v>
       </c>
       <c r="CB12">
-        <v>0.2253807544926562</v>
+        <v>0.2883700594311209</v>
       </c>
       <c r="CC12">
-        <v>0.2253807544926562</v>
+        <v>0.2883700594311209</v>
       </c>
       <c r="CD12">
-        <v>0.2253807544926562</v>
+        <v>0.2883700594311209</v>
       </c>
       <c r="CE12">
-        <v>0.2253807544926562</v>
+        <v>0.3483700594311209</v>
       </c>
       <c r="CF12">
-        <v>0.2253807544926562</v>
+        <v>0.3483700594311209</v>
       </c>
       <c r="CG12">
-        <v>0.2253807544926562</v>
+        <v>0.3483700594311209</v>
       </c>
       <c r="CH12">
-        <v>0.2226192612797028</v>
+        <v>0.3483700594311209</v>
       </c>
       <c r="CI12">
-        <v>0.2198577680667494</v>
+        <v>0.325843060085355</v>
       </c>
       <c r="CJ12">
-        <v>0.2198577680667494</v>
+        <v>0.303316060739589</v>
       </c>
       <c r="CK12">
-        <v>0.2198577680667494</v>
+        <v>0.2807890613938231</v>
       </c>
       <c r="CL12">
-        <v>0.2198577680667494</v>
+        <v>0.2582620620480571</v>
       </c>
       <c r="CM12">
-        <v>0.2198577680667494</v>
+        <v>0.2582620620480571</v>
       </c>
       <c r="CN12">
-        <v>0.2198577680667494</v>
+        <v>0.2582620620480571</v>
       </c>
       <c r="CO12">
-        <v>0.2198577680667494</v>
+        <v>0.2582620620480571</v>
       </c>
       <c r="CP12">
-        <v>0.2198577680667494</v>
+        <v>0.2582620620480571</v>
       </c>
       <c r="CQ12">
-        <v>0.2198577680667494</v>
+        <v>0.2312318399844095</v>
       </c>
       <c r="CR12">
-        <v>0.2198577680667494</v>
+        <v>0.2042016179207618</v>
       </c>
       <c r="CS12">
-        <v>0.2198577680667494</v>
+        <v>0.2042016179207618</v>
       </c>
     </row>
     <row r="13" spans="1:97">
@@ -5180,274 +5180,274 @@
         <v>0.26</v>
       </c>
       <c r="H13">
+        <v>0.26</v>
+      </c>
+      <c r="I13">
+        <v>0.26</v>
+      </c>
+      <c r="J13">
+        <v>0.26</v>
+      </c>
+      <c r="K13">
+        <v>0.26</v>
+      </c>
+      <c r="L13">
+        <v>0.26</v>
+      </c>
+      <c r="M13">
+        <v>0.26</v>
+      </c>
+      <c r="N13">
+        <v>0.26</v>
+      </c>
+      <c r="O13">
+        <v>0.26</v>
+      </c>
+      <c r="P13">
+        <v>0.26</v>
+      </c>
+      <c r="Q13">
         <v>0.32</v>
       </c>
-      <c r="I13">
+      <c r="R13">
         <v>0.32</v>
       </c>
-      <c r="J13">
+      <c r="S13">
+        <v>0.32</v>
+      </c>
+      <c r="T13">
+        <v>0.32</v>
+      </c>
+      <c r="U13">
+        <v>0.32</v>
+      </c>
+      <c r="V13">
+        <v>0.32</v>
+      </c>
+      <c r="W13">
         <v>0.38</v>
       </c>
-      <c r="K13">
+      <c r="X13">
         <v>0.38</v>
       </c>
-      <c r="L13">
+      <c r="Y13">
+        <v>0.38</v>
+      </c>
+      <c r="Z13">
         <v>0.44</v>
       </c>
-      <c r="M13">
-        <v>0.44</v>
-      </c>
-      <c r="N13">
-        <v>0.44</v>
-      </c>
-      <c r="O13">
-        <v>0.44</v>
-      </c>
-      <c r="P13">
-        <v>0.44</v>
-      </c>
-      <c r="Q13">
-        <v>0.44</v>
-      </c>
-      <c r="R13">
+      <c r="AA13">
         <v>0.5</v>
       </c>
-      <c r="S13">
-        <v>0.5</v>
-      </c>
-      <c r="T13">
-        <v>0.5</v>
-      </c>
-      <c r="U13">
-        <v>0.5</v>
-      </c>
-      <c r="V13">
-        <v>0.5</v>
-      </c>
-      <c r="W13">
-        <v>0.5</v>
-      </c>
-      <c r="X13">
-        <v>0.5</v>
-      </c>
-      <c r="Y13">
-        <v>0.5</v>
-      </c>
-      <c r="Z13">
-        <v>0.5</v>
-      </c>
-      <c r="AA13">
-        <v>0.4811761303758739</v>
-      </c>
       <c r="AB13">
-        <v>0.4623522607517479</v>
+        <v>0.4755559715363664</v>
       </c>
       <c r="AC13">
-        <v>0.4435283911276218</v>
+        <v>0.4511119430727327</v>
       </c>
       <c r="AD13">
-        <v>0.4247045215034957</v>
+        <v>0.426667914609099</v>
       </c>
       <c r="AE13">
-        <v>0.4093858324055403</v>
+        <v>0.409570022585753</v>
       </c>
       <c r="AF13">
-        <v>0.3940671433075849</v>
+        <v>0.392472130562407</v>
       </c>
       <c r="AG13">
-        <v>0.3787484542096295</v>
+        <v>0.375374238539061</v>
       </c>
       <c r="AH13">
-        <v>0.3634297651116741</v>
+        <v>0.358276346515715</v>
       </c>
       <c r="AI13">
-        <v>0.3481110760137187</v>
+        <v>0.3411784544923691</v>
       </c>
       <c r="AJ13">
-        <v>0.3481110760137187</v>
+        <v>0.3149744875151255</v>
       </c>
       <c r="AK13">
-        <v>0.3481110760137187</v>
+        <v>0.2887705205378824</v>
       </c>
       <c r="AL13">
-        <v>0.3481110760137187</v>
+        <v>0.2625665535606392</v>
       </c>
       <c r="AM13">
-        <v>0.3481110760137187</v>
+        <v>0.3225665535606392</v>
       </c>
       <c r="AN13">
-        <v>0.3481110760137187</v>
+        <v>0.3028962936534551</v>
       </c>
       <c r="AO13">
-        <v>0.3481110760137187</v>
+        <v>0.283226033746271</v>
       </c>
       <c r="AP13">
-        <v>0.3481110760137187</v>
+        <v>0.263555773839087</v>
       </c>
       <c r="AQ13">
-        <v>0.3481110760137187</v>
+        <v>0.2438855139319029</v>
       </c>
       <c r="AR13">
-        <v>0.3481110760137187</v>
+        <v>0.2242152540247188</v>
       </c>
       <c r="AS13">
-        <v>0.3481110760137187</v>
+        <v>0.2842152540247188</v>
       </c>
       <c r="AT13">
-        <v>0.3481110760137187</v>
+        <v>0.3442152540247188</v>
       </c>
       <c r="AU13">
-        <v>0.3481110760137187</v>
+        <v>0.3442152540247188</v>
       </c>
       <c r="AV13">
-        <v>0.3481110760137187</v>
+        <v>0.4042152540247186</v>
       </c>
       <c r="AW13">
-        <v>0.3481110760137187</v>
+        <v>0.3806158466440042</v>
       </c>
       <c r="AX13">
-        <v>0.3481110760137187</v>
+        <v>0.3570164392632899</v>
       </c>
       <c r="AY13">
-        <v>0.3251876515865195</v>
+        <v>0.3334170318825757</v>
       </c>
       <c r="AZ13">
-        <v>0.3022642271593202</v>
+        <v>0.3934170318825757</v>
       </c>
       <c r="BA13">
-        <v>0.279340802732121</v>
+        <v>0.3934170318825757</v>
       </c>
       <c r="BB13">
-        <v>0.279340802732121</v>
+        <v>0.4534170318825756</v>
       </c>
       <c r="BC13">
-        <v>0.279340802732121</v>
+        <v>0.4534170318825756</v>
       </c>
       <c r="BD13">
-        <v>0.279340802732121</v>
+        <v>0.4347803884295643</v>
       </c>
       <c r="BE13">
-        <v>0.279340802732121</v>
+        <v>0.4161437449765532</v>
       </c>
       <c r="BF13">
-        <v>0.279340802732121</v>
+        <v>0.397507101523542</v>
       </c>
       <c r="BG13">
-        <v>0.279340802732121</v>
+        <v>0.3788704580705308</v>
       </c>
       <c r="BH13">
-        <v>0.279340802732121</v>
+        <v>0.3602338146175195</v>
       </c>
       <c r="BI13">
-        <v>0.2418496593983724</v>
+        <v>0.3430623465738526</v>
       </c>
       <c r="BJ13">
-        <v>0.2043585160646238</v>
+        <v>0.3258908785301857</v>
       </c>
       <c r="BK13">
-        <v>0.2043585160646238</v>
+        <v>0.3087194104865187</v>
       </c>
       <c r="BL13">
-        <v>0.2043585160646238</v>
+        <v>0.2915479424428519</v>
       </c>
       <c r="BM13">
-        <v>0.2043585160646238</v>
+        <v>0.2743764743991849</v>
       </c>
       <c r="BN13">
-        <v>0.2043585160646238</v>
+        <v>0.2596104806246349</v>
       </c>
       <c r="BO13">
-        <v>0.2043585160646238</v>
+        <v>0.244844486850085</v>
       </c>
       <c r="BP13">
-        <v>0.2043585160646238</v>
+        <v>0.230078493075535</v>
       </c>
       <c r="BQ13">
-        <v>0.2043585160646238</v>
+        <v>0.215312499300985</v>
       </c>
       <c r="BR13">
-        <v>0.2043585160646238</v>
+        <v>0.200546505526435</v>
       </c>
       <c r="BS13">
-        <v>0.2043585160646238</v>
+        <v>0.260546505526435</v>
       </c>
       <c r="BT13">
-        <v>0.2043585160646238</v>
+        <v>0.2605465055264348</v>
       </c>
       <c r="BU13">
-        <v>0.2043585160646238</v>
+        <v>0.2605465055264348</v>
       </c>
       <c r="BV13">
-        <v>0.2043585160646238</v>
+        <v>0.3205465055264348</v>
       </c>
       <c r="BW13">
-        <v>0.2043585160646238</v>
+        <v>0.302443620865362</v>
       </c>
       <c r="BX13">
-        <v>0.2043585160646238</v>
+        <v>0.2843407362042891</v>
       </c>
       <c r="BY13">
-        <v>0.2043585160646238</v>
+        <v>0.2662378515432162</v>
       </c>
       <c r="BZ13">
-        <v>0.2043585160646238</v>
+        <v>0.2481349668821434</v>
       </c>
       <c r="CA13">
-        <v>0.2043585160646238</v>
+        <v>0.2481349668821434</v>
       </c>
       <c r="CB13">
-        <v>0.2043585160646238</v>
+        <v>0.2481349668821434</v>
       </c>
       <c r="CC13">
-        <v>0.2043585160646238</v>
+        <v>0.2481349668821434</v>
       </c>
       <c r="CD13">
-        <v>0.2043585160646238</v>
+        <v>0.2481349668821434</v>
       </c>
       <c r="CE13">
-        <v>0.2043585160646238</v>
+        <v>0.2481349668821434</v>
       </c>
       <c r="CF13">
-        <v>0.2043585160646238</v>
+        <v>0.2481349668821434</v>
       </c>
       <c r="CG13">
-        <v>0.2043585160646238</v>
+        <v>0.2481349668821434</v>
       </c>
       <c r="CH13">
-        <v>0.2043585160646238</v>
+        <v>0.2481349668821434</v>
       </c>
       <c r="CI13">
-        <v>0.2043585160646238</v>
+        <v>0.2481349668821434</v>
       </c>
       <c r="CJ13">
-        <v>0.2043585160646238</v>
+        <v>0.2481349668821434</v>
       </c>
       <c r="CK13">
-        <v>0.2043585160646238</v>
+        <v>0.3081349668821434</v>
       </c>
       <c r="CL13">
-        <v>0.2043585160646238</v>
+        <v>0.3081349668821434</v>
       </c>
       <c r="CM13">
-        <v>0.2043585160646238</v>
+        <v>0.3081349668821434</v>
       </c>
       <c r="CN13">
-        <v>0.2043585160646238</v>
+        <v>0.2873805077394845</v>
       </c>
       <c r="CO13">
-        <v>0.2043585160646238</v>
+        <v>0.2666260485968256</v>
       </c>
       <c r="CP13">
-        <v>0.2043585160646238</v>
+        <v>0.2458715894541668</v>
       </c>
       <c r="CQ13">
-        <v>0.2043585160646238</v>
+        <v>0.2251171303115079</v>
       </c>
       <c r="CR13">
-        <v>0.2043585160646238</v>
+        <v>0.204362671168849</v>
       </c>
       <c r="CS13">
-        <v>0.2043585160646238</v>
+        <v>0.204362671168849</v>
       </c>
     </row>
     <row r="14" spans="1:97">
@@ -5464,55 +5464,55 @@
         <v>0.26</v>
       </c>
       <c r="E14">
+        <v>0.26</v>
+      </c>
+      <c r="F14">
+        <v>0.26</v>
+      </c>
+      <c r="G14">
+        <v>0.26</v>
+      </c>
+      <c r="H14">
+        <v>0.26</v>
+      </c>
+      <c r="I14">
         <v>0.32</v>
-      </c>
-      <c r="F14">
-        <v>0.32</v>
-      </c>
-      <c r="G14">
-        <v>0.32</v>
-      </c>
-      <c r="H14">
-        <v>0.38</v>
-      </c>
-      <c r="I14">
-        <v>0.38</v>
       </c>
       <c r="J14">
         <v>0.38</v>
       </c>
       <c r="K14">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="L14">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M14">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="N14">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="O14">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="P14">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="Q14">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="R14">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S14">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="T14">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="U14">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="V14">
         <v>0.62</v>
@@ -5521,226 +5521,226 @@
         <v>0.62</v>
       </c>
       <c r="X14">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="Y14">
-        <v>0.62</v>
+        <v>0.66095817854405</v>
       </c>
       <c r="Z14">
-        <v>0.68</v>
+        <v>0.6419163570881002</v>
       </c>
       <c r="AA14">
-        <v>0.68</v>
+        <v>0.6228745356321503</v>
       </c>
       <c r="AB14">
-        <v>0.68</v>
+        <v>0.6038327141762005</v>
       </c>
       <c r="AC14">
-        <v>0.68</v>
+        <v>0.5847908927202506</v>
       </c>
       <c r="AD14">
-        <v>0.6648658210516531</v>
+        <v>0.6447908927202503</v>
       </c>
       <c r="AE14">
-        <v>0.6497316421033053</v>
+        <v>0.6219185411027616</v>
       </c>
       <c r="AF14">
-        <v>0.6345974631549574</v>
+        <v>0.5990461894852727</v>
       </c>
       <c r="AG14">
-        <v>0.6194632842066096</v>
+        <v>0.5761738378677839</v>
       </c>
       <c r="AH14">
-        <v>0.6043291052582618</v>
+        <v>0.5585246006895316</v>
       </c>
       <c r="AI14">
-        <v>0.5891949263099139</v>
+        <v>0.5408753635112793</v>
       </c>
       <c r="AJ14">
-        <v>0.5891949263099139</v>
+        <v>0.523226126333027</v>
       </c>
       <c r="AK14">
-        <v>0.5891949263099139</v>
+        <v>0.5055768891547746</v>
       </c>
       <c r="AL14">
-        <v>0.5891949263099139</v>
+        <v>0.4879276519765223</v>
       </c>
       <c r="AM14">
-        <v>0.5891949263099139</v>
+        <v>0.5479276519765224</v>
       </c>
       <c r="AN14">
-        <v>0.5640545242626964</v>
+        <v>0.6079276519765223</v>
       </c>
       <c r="AO14">
-        <v>0.5389141222154789</v>
+        <v>0.5895459559489581</v>
       </c>
       <c r="AP14">
-        <v>0.5389141222154789</v>
+        <v>0.5711642599213937</v>
       </c>
       <c r="AQ14">
-        <v>0.5389141222154789</v>
+        <v>0.5527825638938294</v>
       </c>
       <c r="AR14">
-        <v>0.5110559753777918</v>
+        <v>0.5344008678662651</v>
       </c>
       <c r="AS14">
-        <v>0.4831978285401049</v>
+        <v>0.5160191718387007</v>
       </c>
       <c r="AT14">
-        <v>0.4553396817024179</v>
+        <v>0.5160191718387007</v>
       </c>
       <c r="AU14">
-        <v>0.4553396817024179</v>
+        <v>0.4922996012930057</v>
       </c>
       <c r="AV14">
-        <v>0.4553396817024179</v>
+        <v>0.4685800307473105</v>
       </c>
       <c r="AW14">
-        <v>0.4553396817024179</v>
+        <v>0.4448604602016153</v>
       </c>
       <c r="AX14">
-        <v>0.4553396817024179</v>
+        <v>0.5048604602016153</v>
       </c>
       <c r="AY14">
-        <v>0.4553396817024179</v>
+        <v>0.5648604602016153</v>
       </c>
       <c r="AZ14">
-        <v>0.4553396817024179</v>
+        <v>0.5457200437419936</v>
       </c>
       <c r="BA14">
-        <v>0.4553396817024179</v>
+        <v>0.5265796272823718</v>
       </c>
       <c r="BB14">
-        <v>0.4553396817024179</v>
+        <v>0.5074392108227499</v>
       </c>
       <c r="BC14">
-        <v>0.4553396817024179</v>
+        <v>0.4882987943631281</v>
       </c>
       <c r="BD14">
-        <v>0.4553396817024179</v>
+        <v>0.4698977066843245</v>
       </c>
       <c r="BE14">
-        <v>0.4553396817024179</v>
+        <v>0.451496619005521</v>
       </c>
       <c r="BF14">
-        <v>0.4553396817024179</v>
+        <v>0.4330955313267173</v>
       </c>
       <c r="BG14">
-        <v>0.4286196888114345</v>
+        <v>0.4146944436479137</v>
       </c>
       <c r="BH14">
-        <v>0.401899695920451</v>
+        <v>0.39629335596911</v>
       </c>
       <c r="BI14">
-        <v>0.401899695920451</v>
+        <v>0.3792783498757722</v>
       </c>
       <c r="BJ14">
-        <v>0.401899695920451</v>
+        <v>0.3622633437824343</v>
       </c>
       <c r="BK14">
-        <v>0.401899695920451</v>
+        <v>0.3452483376890965</v>
       </c>
       <c r="BL14">
-        <v>0.401899695920451</v>
+        <v>0.3282333315957586</v>
       </c>
       <c r="BM14">
-        <v>0.401899695920451</v>
+        <v>0.3112183255024207</v>
       </c>
       <c r="BN14">
-        <v>0.3761331828449474</v>
+        <v>0.2921830358874655</v>
       </c>
       <c r="BO14">
-        <v>0.3503666697694438</v>
+        <v>0.2731477462725104</v>
       </c>
       <c r="BP14">
-        <v>0.3221911811006466</v>
+        <v>0.2541124566575552</v>
       </c>
       <c r="BQ14">
-        <v>0.2940156924318495</v>
+        <v>0.2295048899046734</v>
       </c>
       <c r="BR14">
-        <v>0.2658402037630523</v>
+        <v>0.2048973231517917</v>
       </c>
       <c r="BS14">
-        <v>0.2658402037630523</v>
+        <v>0.2048973231517917</v>
       </c>
       <c r="BT14">
-        <v>0.2371877012444518</v>
+        <v>0.2048973231517917</v>
       </c>
       <c r="BU14">
-        <v>0.2085351987258514</v>
+        <v>0.2048973231517917</v>
       </c>
       <c r="BV14">
-        <v>0.2085351987258514</v>
+        <v>0.2048973231517917</v>
       </c>
       <c r="BW14">
-        <v>0.2085351987258514</v>
+        <v>0.2048973231517917</v>
       </c>
       <c r="BX14">
-        <v>0.2085351987258514</v>
+        <v>0.2048973231517917</v>
       </c>
       <c r="BY14">
-        <v>0.2085351987258514</v>
+        <v>0.2048973231517917</v>
       </c>
       <c r="BZ14">
-        <v>0.2085351987258514</v>
+        <v>0.2648973231517917</v>
       </c>
       <c r="CA14">
-        <v>0.2085351987258514</v>
+        <v>0.3248973231517917</v>
       </c>
       <c r="CB14">
-        <v>0.2085351987258514</v>
+        <v>0.296310379371816</v>
       </c>
       <c r="CC14">
-        <v>0.2085351987258514</v>
+        <v>0.2677234355918402</v>
       </c>
       <c r="CD14">
-        <v>0.2085351987258514</v>
+        <v>0.2391364918118644</v>
       </c>
       <c r="CE14">
-        <v>0.2085351987258514</v>
+        <v>0.2391364918118644</v>
       </c>
       <c r="CF14">
-        <v>0.2085351987258514</v>
+        <v>0.2991364918118644</v>
       </c>
       <c r="CG14">
-        <v>0.2085351987258514</v>
+        <v>0.276564576709096</v>
       </c>
       <c r="CH14">
-        <v>0.2085351987258514</v>
+        <v>0.2539926616063276</v>
       </c>
       <c r="CI14">
-        <v>0.2085351987258514</v>
+        <v>0.2314207465035591</v>
       </c>
       <c r="CJ14">
-        <v>0.2085351987258514</v>
+        <v>0.2088488314007906</v>
       </c>
       <c r="CK14">
-        <v>0.2085351987258514</v>
+        <v>0.2088488314007906</v>
       </c>
       <c r="CL14">
-        <v>0.2085351987258514</v>
+        <v>0.2088488314007906</v>
       </c>
       <c r="CM14">
-        <v>0.2085351987258514</v>
+        <v>0.2088488314007906</v>
       </c>
       <c r="CN14">
-        <v>0.2085351987258514</v>
+        <v>0.2088488314007906</v>
       </c>
       <c r="CO14">
-        <v>0.2085351987258514</v>
+        <v>0.2088488314007906</v>
       </c>
       <c r="CP14">
-        <v>0.2085351987258514</v>
+        <v>0.2088488314007906</v>
       </c>
       <c r="CQ14">
-        <v>0.2085351987258514</v>
+        <v>0.2088488314007906</v>
       </c>
       <c r="CR14">
-        <v>0.2085351987258514</v>
+        <v>0.2088488314007906</v>
       </c>
       <c r="CS14">
-        <v>0.2085351987258514</v>
+        <v>0.2088488314007906</v>
       </c>
     </row>
     <row r="15" spans="1:97">
@@ -5751,10 +5751,10 @@
         <v>0.2</v>
       </c>
       <c r="C15">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="D15">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="E15">
         <v>0.32</v>
@@ -5763,7 +5763,7 @@
         <v>0.32</v>
       </c>
       <c r="G15">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="H15">
         <v>0.38</v>
@@ -5775,265 +5775,265 @@
         <v>0.38</v>
       </c>
       <c r="K15">
+        <v>0.38</v>
+      </c>
+      <c r="L15">
+        <v>0.38</v>
+      </c>
+      <c r="M15">
+        <v>0.38</v>
+      </c>
+      <c r="N15">
+        <v>0.38</v>
+      </c>
+      <c r="O15">
+        <v>0.38</v>
+      </c>
+      <c r="P15">
+        <v>0.38</v>
+      </c>
+      <c r="Q15">
+        <v>0.38</v>
+      </c>
+      <c r="R15">
+        <v>0.38</v>
+      </c>
+      <c r="S15">
+        <v>0.38</v>
+      </c>
+      <c r="T15">
+        <v>0.38</v>
+      </c>
+      <c r="U15">
         <v>0.44</v>
       </c>
-      <c r="L15">
+      <c r="V15">
         <v>0.44</v>
       </c>
-      <c r="M15">
+      <c r="W15">
         <v>0.44</v>
       </c>
-      <c r="N15">
+      <c r="X15">
         <v>0.44</v>
       </c>
-      <c r="O15">
-        <v>0.44</v>
-      </c>
-      <c r="P15">
-        <v>0.44</v>
-      </c>
-      <c r="Q15">
+      <c r="Y15">
         <v>0.5</v>
       </c>
-      <c r="R15">
+      <c r="Z15">
         <v>0.5</v>
       </c>
-      <c r="S15">
+      <c r="AA15">
         <v>0.5</v>
       </c>
-      <c r="T15">
+      <c r="AB15">
         <v>0.5</v>
       </c>
-      <c r="U15">
+      <c r="AC15">
         <v>0.5</v>
       </c>
-      <c r="V15">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="W15">
-        <v>0.5378754765360211</v>
-      </c>
-      <c r="X15">
-        <v>0.5157509530720421</v>
-      </c>
-      <c r="Y15">
-        <v>0.4936264296080631</v>
-      </c>
-      <c r="Z15">
-        <v>0.4715019061440842</v>
-      </c>
-      <c r="AA15">
-        <v>0.5315019061440842</v>
-      </c>
-      <c r="AB15">
-        <v>0.5315019061440842</v>
-      </c>
-      <c r="AC15">
-        <v>0.5315019061440842</v>
-      </c>
       <c r="AD15">
-        <v>0.5315019061440842</v>
+        <v>0.4814846543815774</v>
       </c>
       <c r="AE15">
-        <v>0.5315019061440842</v>
+        <v>0.4629693087631548</v>
       </c>
       <c r="AF15">
-        <v>0.5315019061440842</v>
+        <v>0.4444539631447321</v>
       </c>
       <c r="AG15">
-        <v>0.5315019061440842</v>
+        <v>0.4259386175263094</v>
       </c>
       <c r="AH15">
-        <v>0.5315019061440842</v>
+        <v>0.4064836382954061</v>
       </c>
       <c r="AI15">
-        <v>0.5315019061440842</v>
+        <v>0.3870286590645027</v>
       </c>
       <c r="AJ15">
-        <v>0.5315019061440842</v>
+        <v>0.3675736798335994</v>
       </c>
       <c r="AK15">
-        <v>0.5315019061440842</v>
+        <v>0.3481187006026961</v>
       </c>
       <c r="AL15">
-        <v>0.51273511419416</v>
+        <v>0.3286637213717927</v>
       </c>
       <c r="AM15">
-        <v>0.4939683222442358</v>
+        <v>0.3886637213717927</v>
       </c>
       <c r="AN15">
-        <v>0.4752015302943116</v>
+        <v>0.3703376285930194</v>
       </c>
       <c r="AO15">
-        <v>0.4564347383443874</v>
+        <v>0.3520115358142462</v>
       </c>
       <c r="AP15">
-        <v>0.4564347383443874</v>
+        <v>0.333685443035473</v>
       </c>
       <c r="AQ15">
-        <v>0.4564347383443874</v>
+        <v>0.3153593502566997</v>
       </c>
       <c r="AR15">
-        <v>0.4564347383443874</v>
+        <v>0.3153593502566997</v>
       </c>
       <c r="AS15">
-        <v>0.4564347383443874</v>
+        <v>0.2973846236934544</v>
       </c>
       <c r="AT15">
-        <v>0.4564347383443874</v>
+        <v>0.279409897130209</v>
       </c>
       <c r="AU15">
-        <v>0.4564347383443874</v>
+        <v>0.2614351705669637</v>
       </c>
       <c r="AV15">
-        <v>0.4564347383443874</v>
+        <v>0.2434604440037183</v>
       </c>
       <c r="AW15">
-        <v>0.4564347383443874</v>
+        <v>0.225485717440473</v>
       </c>
       <c r="AX15">
-        <v>0.4564347383443874</v>
+        <v>0.285485717440473</v>
       </c>
       <c r="AY15">
-        <v>0.4564347383443874</v>
+        <v>0.345485717440473</v>
       </c>
       <c r="AZ15">
-        <v>0.4564347383443874</v>
+        <v>0.405485717440473</v>
       </c>
       <c r="BA15">
-        <v>0.4349389677481126</v>
+        <v>0.3817068006011861</v>
       </c>
       <c r="BB15">
-        <v>0.4134431971518378</v>
+        <v>0.3579278837618992</v>
       </c>
       <c r="BC15">
-        <v>0.4134431971518378</v>
+        <v>0.3341489669226124</v>
       </c>
       <c r="BD15">
-        <v>0.4134431971518378</v>
+        <v>0.3341489669226124</v>
       </c>
       <c r="BE15">
-        <v>0.4134431971518378</v>
+        <v>0.3941489669226124</v>
       </c>
       <c r="BF15">
-        <v>0.3833227870562395</v>
+        <v>0.3941489669226124</v>
       </c>
       <c r="BG15">
-        <v>0.3532023769606412</v>
+        <v>0.3757448001442907</v>
       </c>
       <c r="BH15">
-        <v>0.3532023769606412</v>
+        <v>0.3573406333659689</v>
       </c>
       <c r="BI15">
-        <v>0.3532023769606412</v>
+        <v>0.3389364665876471</v>
       </c>
       <c r="BJ15">
-        <v>0.3532023769606412</v>
+        <v>0.3205322998093253</v>
       </c>
       <c r="BK15">
-        <v>0.3373641209554557</v>
+        <v>0.3021281330310036</v>
       </c>
       <c r="BL15">
-        <v>0.3215258649502702</v>
+        <v>0.2860240746508129</v>
       </c>
       <c r="BM15">
-        <v>0.3215258649502702</v>
+        <v>0.2699200162706223</v>
       </c>
       <c r="BN15">
-        <v>0.3215258649502702</v>
+        <v>0.2538159578904317</v>
       </c>
       <c r="BO15">
-        <v>0.3044527121113758</v>
+        <v>0.237711899510241</v>
       </c>
       <c r="BP15">
-        <v>0.2873795592724812</v>
+        <v>0.2216078411300504</v>
       </c>
       <c r="BQ15">
-        <v>0.2873795592724812</v>
+        <v>0.2816078411300504</v>
       </c>
       <c r="BR15">
-        <v>0.2873795592724812</v>
+        <v>0.256245508993386</v>
       </c>
       <c r="BS15">
-        <v>0.2873795592724812</v>
+        <v>0.2308831768567216</v>
       </c>
       <c r="BT15">
-        <v>0.2596055848992115</v>
+        <v>0.2908831768567216</v>
       </c>
       <c r="BU15">
-        <v>0.2318316105259417</v>
+        <v>0.3508831768567216</v>
       </c>
       <c r="BV15">
-        <v>0.204057636152672</v>
+        <v>0.331082775008085</v>
       </c>
       <c r="BW15">
-        <v>0.204057636152672</v>
+        <v>0.3112823731594483</v>
       </c>
       <c r="BX15">
-        <v>0.204057636152672</v>
+        <v>0.2914819713108117</v>
       </c>
       <c r="BY15">
-        <v>0.204057636152672</v>
+        <v>0.2716815694621751</v>
       </c>
       <c r="BZ15">
-        <v>0.204057636152672</v>
+        <v>0.2518811676135385</v>
       </c>
       <c r="CA15">
-        <v>0.204057636152672</v>
+        <v>0.2264770035607196</v>
       </c>
       <c r="CB15">
-        <v>0.204057636152672</v>
+        <v>0.2010728395079007</v>
       </c>
       <c r="CC15">
-        <v>0.204057636152672</v>
+        <v>0.2010728395079007</v>
       </c>
       <c r="CD15">
-        <v>0.204057636152672</v>
+        <v>0.2010728395079007</v>
       </c>
       <c r="CE15">
-        <v>0.204057636152672</v>
+        <v>0.2610728395079007</v>
       </c>
       <c r="CF15">
-        <v>0.204057636152672</v>
+        <v>0.3210728395079006</v>
       </c>
       <c r="CG15">
-        <v>0.204057636152672</v>
+        <v>0.3810728395079006</v>
       </c>
       <c r="CH15">
-        <v>0.204057636152672</v>
+        <v>0.3810728395079006</v>
       </c>
       <c r="CI15">
-        <v>0.204057636152672</v>
+        <v>0.3810728395079006</v>
       </c>
       <c r="CJ15">
-        <v>0.204057636152672</v>
+        <v>0.3606062248301035</v>
       </c>
       <c r="CK15">
-        <v>0.204057636152672</v>
+        <v>0.3401396101523064</v>
       </c>
       <c r="CL15">
-        <v>0.204057636152672</v>
+        <v>0.3196729954745094</v>
       </c>
       <c r="CM15">
-        <v>0.204057636152672</v>
+        <v>0.2992063807967124</v>
       </c>
       <c r="CN15">
-        <v>0.204057636152672</v>
+        <v>0.2787397661189153</v>
       </c>
       <c r="CO15">
-        <v>0.204057636152672</v>
+        <v>0.2561685729578874</v>
       </c>
       <c r="CP15">
-        <v>0.204057636152672</v>
+        <v>0.2335973797968594</v>
       </c>
       <c r="CQ15">
-        <v>0.204057636152672</v>
+        <v>0.2110261866358314</v>
       </c>
       <c r="CR15">
-        <v>0.204057636152672</v>
+        <v>0.2110261866358314</v>
       </c>
       <c r="CS15">
-        <v>0.204057636152672</v>
+        <v>0.2110261866358314</v>
       </c>
     </row>
     <row r="16" spans="1:97">
@@ -6053,280 +6053,280 @@
         <v>0.2</v>
       </c>
       <c r="F16">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="G16">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="H16">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="I16">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="J16">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="K16">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="L16">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="M16">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="N16">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="O16">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="P16">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="Q16">
-        <v>0.32</v>
+        <v>0.5</v>
       </c>
       <c r="R16">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="S16">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="T16">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="U16">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V16">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W16">
-        <v>0.5</v>
+        <v>0.5371265374535482</v>
       </c>
       <c r="X16">
-        <v>0.5</v>
+        <v>0.5142530749070979</v>
       </c>
       <c r="Y16">
-        <v>0.5</v>
+        <v>0.4913796123606475</v>
       </c>
       <c r="Z16">
-        <v>0.5</v>
+        <v>0.4685061498141971</v>
       </c>
       <c r="AA16">
-        <v>0.5</v>
+        <v>0.4685061498141982</v>
       </c>
       <c r="AB16">
-        <v>0.5</v>
+        <v>0.4685061498141982</v>
       </c>
       <c r="AC16">
-        <v>0.5</v>
+        <v>0.4512255099191195</v>
       </c>
       <c r="AD16">
-        <v>0.5</v>
+        <v>0.4339448700240406</v>
       </c>
       <c r="AE16">
-        <v>0.4815700555806904</v>
+        <v>0.4166642301289618</v>
       </c>
       <c r="AF16">
-        <v>0.4631401111613822</v>
+        <v>0.3993835902338829</v>
       </c>
       <c r="AG16">
-        <v>0.444710166742074</v>
+        <v>0.3807802161647421</v>
       </c>
       <c r="AH16">
-        <v>0.4262802223227657</v>
+        <v>0.3621768420956012</v>
       </c>
       <c r="AI16">
-        <v>0.4078502779034575</v>
+        <v>0.3435734680264603</v>
       </c>
       <c r="AJ16">
-        <v>0.4078502779034575</v>
+        <v>0.3249700939573195</v>
       </c>
       <c r="AK16">
-        <v>0.4078502779034575</v>
+        <v>0.3063667198881786</v>
       </c>
       <c r="AL16">
-        <v>0.4078502779034575</v>
+        <v>0.2863555211450407</v>
       </c>
       <c r="AM16">
-        <v>0.4078502779034575</v>
+        <v>0.2663443224019028</v>
       </c>
       <c r="AN16">
-        <v>0.4078502779034575</v>
+        <v>0.2463331236587648</v>
       </c>
       <c r="AO16">
-        <v>0.4078502779034575</v>
+        <v>0.2263219249156269</v>
       </c>
       <c r="AP16">
-        <v>0.4078502779034575</v>
+        <v>0.2863219249156269</v>
       </c>
       <c r="AQ16">
-        <v>0.4078502779034575</v>
+        <v>0.3463219249156264</v>
       </c>
       <c r="AR16">
-        <v>0.4078502779034575</v>
+        <v>0.4063219249156264</v>
       </c>
       <c r="AS16">
-        <v>0.4078502779034575</v>
+        <v>0.3827056433366455</v>
       </c>
       <c r="AT16">
-        <v>0.4033336254315714</v>
+        <v>0.3590893617576645</v>
       </c>
       <c r="AU16">
-        <v>0.3988169729596853</v>
+        <v>0.3354730801786837</v>
       </c>
       <c r="AV16">
-        <v>0.3943003204877991</v>
+        <v>0.3354730801786837</v>
       </c>
       <c r="AW16">
-        <v>0.389783668015913</v>
+        <v>0.3354730801786837</v>
       </c>
       <c r="AX16">
-        <v>0.3852670155440269</v>
+        <v>0.3354730801786837</v>
       </c>
       <c r="AY16">
-        <v>0.3852670155440269</v>
+        <v>0.3354730801786838</v>
       </c>
       <c r="AZ16">
-        <v>0.3852670155440269</v>
+        <v>0.3354730801786838</v>
       </c>
       <c r="BA16">
-        <v>0.3852670155440269</v>
+        <v>0.3354730801786838</v>
       </c>
       <c r="BB16">
-        <v>0.3852670155440269</v>
+        <v>0.3169984456084818</v>
       </c>
       <c r="BC16">
-        <v>0.3852670155440269</v>
+        <v>0.2985238110382798</v>
       </c>
       <c r="BD16">
-        <v>0.3852670155440271</v>
+        <v>0.2800491764680778</v>
       </c>
       <c r="BE16">
-        <v>0.3852670155440271</v>
+        <v>0.2615745418978758</v>
       </c>
       <c r="BF16">
-        <v>0.3852670155440271</v>
+        <v>0.2430999073276738</v>
       </c>
       <c r="BG16">
-        <v>0.3852670155440271</v>
+        <v>0.3030999073276737</v>
       </c>
       <c r="BH16">
-        <v>0.3567162942635915</v>
+        <v>0.3630999073276737</v>
       </c>
       <c r="BI16">
-        <v>0.3281655729831559</v>
+        <v>0.3377677816842309</v>
       </c>
       <c r="BJ16">
-        <v>0.3281655729831559</v>
+        <v>0.3124356560407881</v>
       </c>
       <c r="BK16">
-        <v>0.3281655729831559</v>
+        <v>0.2871035303973453</v>
       </c>
       <c r="BL16">
-        <v>0.3041548717879045</v>
+        <v>0.2680678214343758</v>
       </c>
       <c r="BM16">
-        <v>0.2801441705926532</v>
+        <v>0.2490321124714062</v>
       </c>
       <c r="BN16">
-        <v>0.2561334693974019</v>
+        <v>0.2299964035084366</v>
       </c>
       <c r="BO16">
-        <v>0.2561334693974019</v>
+        <v>0.2899964035084366</v>
       </c>
       <c r="BP16">
-        <v>0.2561334693974019</v>
+        <v>0.2899964035084366</v>
       </c>
       <c r="BQ16">
-        <v>0.2561334693974019</v>
+        <v>0.3499964035084366</v>
       </c>
       <c r="BR16">
-        <v>0.2561334693974019</v>
+        <v>0.4099964035084366</v>
       </c>
       <c r="BS16">
-        <v>0.2561334693974019</v>
+        <v>0.3909367757772454</v>
       </c>
       <c r="BT16">
-        <v>0.2561334693974019</v>
+        <v>0.3718771480460542</v>
       </c>
       <c r="BU16">
-        <v>0.2561334693974019</v>
+        <v>0.3528175203148629</v>
       </c>
       <c r="BV16">
-        <v>0.2561334693974019</v>
+        <v>0.3337578925836717</v>
       </c>
       <c r="BW16">
-        <v>0.2561334693974019</v>
+        <v>0.3146982648524805</v>
       </c>
       <c r="BX16">
-        <v>0.2561334693974019</v>
+        <v>0.293805560581858</v>
       </c>
       <c r="BY16">
-        <v>0.2315790004819591</v>
+        <v>0.2729128563112355</v>
       </c>
       <c r="BZ16">
-        <v>0.2915790004819591</v>
+        <v>0.252020152040613</v>
       </c>
       <c r="CA16">
-        <v>0.2705241096811035</v>
+        <v>0.2311274477699905</v>
       </c>
       <c r="CB16">
-        <v>0.2494692188802475</v>
+        <v>0.2911274477699905</v>
       </c>
       <c r="CC16">
-        <v>0.2494692188802475</v>
+        <v>0.2911274477699905</v>
       </c>
       <c r="CD16">
-        <v>0.2494692188802475</v>
+        <v>0.2911274477699905</v>
       </c>
       <c r="CE16">
-        <v>0.2494692188802475</v>
+        <v>0.2911274477699905</v>
       </c>
       <c r="CF16">
-        <v>0.2494692188802475</v>
+        <v>0.2911274477699905</v>
       </c>
       <c r="CG16">
-        <v>0.2494692188802475</v>
+        <v>0.2911274477699905</v>
       </c>
       <c r="CH16">
-        <v>0.2494692188802475</v>
+        <v>0.2911274477699905</v>
       </c>
       <c r="CI16">
-        <v>0.2494692188802475</v>
+        <v>0.2911274477699905</v>
       </c>
       <c r="CJ16">
-        <v>0.2494692188802473</v>
+        <v>0.2911274477699905</v>
       </c>
       <c r="CK16">
-        <v>0.2494692188802473</v>
+        <v>0.2911274477699905</v>
       </c>
       <c r="CL16">
-        <v>0.2494692188802473</v>
+        <v>0.2911274477699905</v>
       </c>
       <c r="CM16">
-        <v>0.2257580689563737</v>
+        <v>0.2911274477699905</v>
       </c>
       <c r="CN16">
-        <v>0.2020469190325001</v>
+        <v>0.2611572071069113</v>
       </c>
       <c r="CO16">
-        <v>0.2020469190325001</v>
+        <v>0.231186966443832</v>
       </c>
       <c r="CP16">
-        <v>0.2020469190325001</v>
+        <v>0.2012167257807527</v>
       </c>
       <c r="CQ16">
-        <v>0.2020469190325001</v>
+        <v>0.2012167257807527</v>
       </c>
       <c r="CR16">
-        <v>0.2020469190325001</v>
+        <v>0.2012167257807527</v>
       </c>
       <c r="CS16">
-        <v>0.2020469190325001</v>
+        <v>0.2012167257807527</v>
       </c>
     </row>
     <row r="17" spans="1:97">
@@ -6355,271 +6355,271 @@
         <v>0.2</v>
       </c>
       <c r="I17">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="J17">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="K17">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="L17">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="M17">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="N17">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="O17">
+        <v>0.2</v>
+      </c>
+      <c r="P17">
+        <v>0.2</v>
+      </c>
+      <c r="Q17">
+        <v>0.2</v>
+      </c>
+      <c r="R17">
+        <v>0.2</v>
+      </c>
+      <c r="S17">
+        <v>0.2</v>
+      </c>
+      <c r="T17">
+        <v>0.2</v>
+      </c>
+      <c r="U17">
+        <v>0.2</v>
+      </c>
+      <c r="V17">
+        <v>0.2</v>
+      </c>
+      <c r="W17">
+        <v>0.2</v>
+      </c>
+      <c r="X17">
+        <v>0.26</v>
+      </c>
+      <c r="Y17">
         <v>0.32</v>
       </c>
-      <c r="P17">
+      <c r="Z17">
         <v>0.32</v>
       </c>
-      <c r="Q17">
+      <c r="AA17">
         <v>0.32</v>
       </c>
-      <c r="R17">
+      <c r="AB17">
         <v>0.38</v>
       </c>
-      <c r="S17">
+      <c r="AC17">
         <v>0.44</v>
       </c>
-      <c r="T17">
+      <c r="AD17">
         <v>0.5</v>
       </c>
-      <c r="U17">
-        <v>0.5</v>
-      </c>
-      <c r="V17">
-        <v>0.5</v>
-      </c>
-      <c r="W17">
-        <v>0.5</v>
-      </c>
-      <c r="X17">
-        <v>0.5</v>
-      </c>
-      <c r="Y17">
-        <v>0.4783365331301933</v>
-      </c>
-      <c r="Z17">
-        <v>0.4566730662603888</v>
-      </c>
-      <c r="AA17">
-        <v>0.4350095993905843</v>
-      </c>
-      <c r="AB17">
-        <v>0.4133461325207798</v>
-      </c>
-      <c r="AC17">
-        <v>0.3931275536447311</v>
-      </c>
-      <c r="AD17">
-        <v>0.3729089747686823</v>
-      </c>
       <c r="AE17">
-        <v>0.3526903958926336</v>
+        <v>0.4803923371573829</v>
       </c>
       <c r="AF17">
-        <v>0.3366469654416295</v>
+        <v>0.460784674314766</v>
       </c>
       <c r="AG17">
-        <v>0.3206035349906253</v>
+        <v>0.441177011472149</v>
       </c>
       <c r="AH17">
-        <v>0.3045601045396211</v>
+        <v>0.501177011472149</v>
       </c>
       <c r="AI17">
-        <v>0.288516674088617</v>
+        <v>0.4814195903198167</v>
       </c>
       <c r="AJ17">
-        <v>0.2724732436376128</v>
+        <v>0.4616621691674843</v>
       </c>
       <c r="AK17">
-        <v>0.2724732436376128</v>
+        <v>0.4419047480151518</v>
       </c>
       <c r="AL17">
-        <v>0.2724732436376128</v>
+        <v>0.4221473268628194</v>
       </c>
       <c r="AM17">
-        <v>0.2724732436375227</v>
+        <v>0.4821473268628194</v>
       </c>
       <c r="AN17">
-        <v>0.2724732436375227</v>
+        <v>0.4821473268628194</v>
       </c>
       <c r="AO17">
-        <v>0.2724732436375227</v>
+        <v>0.4558092257528792</v>
       </c>
       <c r="AP17">
-        <v>0.2724732436375227</v>
+        <v>0.429471124642939</v>
       </c>
       <c r="AQ17">
-        <v>0.2724732436375227</v>
+        <v>0.4031330235329988</v>
       </c>
       <c r="AR17">
-        <v>0.2724732436375227</v>
+        <v>0.4631330235329988</v>
       </c>
       <c r="AS17">
-        <v>0.2724732436375227</v>
+        <v>0.5231330235329988</v>
       </c>
       <c r="AT17">
-        <v>0.2724732436375227</v>
+        <v>0.5038635149544448</v>
       </c>
       <c r="AU17">
-        <v>0.2724732436375104</v>
+        <v>0.484594006375891</v>
       </c>
       <c r="AV17">
-        <v>0.2724732436375104</v>
+        <v>0.465324497797337</v>
       </c>
       <c r="AW17">
-        <v>0.2724732436375104</v>
+        <v>0.4460549892187831</v>
       </c>
       <c r="AX17">
-        <v>0.2724732436375104</v>
+        <v>0.4267854806402291</v>
       </c>
       <c r="AY17">
-        <v>0.2724732436375104</v>
+        <v>0.401421367088647</v>
       </c>
       <c r="AZ17">
-        <v>0.2724732436375089</v>
+        <v>0.376057253537065</v>
       </c>
       <c r="BA17">
-        <v>0.2724732436375089</v>
+        <v>0.350693139985483</v>
       </c>
       <c r="BB17">
-        <v>0.2724732436375089</v>
+        <v>0.325328214142134</v>
       </c>
       <c r="BC17">
-        <v>0.2724732436375089</v>
+        <v>0.299963288298785</v>
       </c>
       <c r="BD17">
-        <v>0.2724732436375089</v>
+        <v>0.2808186188761151</v>
       </c>
       <c r="BE17">
-        <v>0.2724732436375089</v>
+        <v>0.2616739494534452</v>
       </c>
       <c r="BF17">
-        <v>0.2724732436375089</v>
+        <v>0.2425292800307748</v>
       </c>
       <c r="BG17">
-        <v>0.2724732436375089</v>
+        <v>0.2233846106081049</v>
       </c>
       <c r="BH17">
-        <v>0.2724732436375089</v>
+        <v>0.2833846106081049</v>
       </c>
       <c r="BI17">
-        <v>0.2724732436375089</v>
+        <v>0.2667477306998265</v>
       </c>
       <c r="BJ17">
-        <v>0.2724732436375089</v>
+        <v>0.2501108507915482</v>
       </c>
       <c r="BK17">
-        <v>0.2724732436375104</v>
+        <v>0.2334739708832698</v>
       </c>
       <c r="BL17">
-        <v>0.2724732436375104</v>
+        <v>0.2168370909749915</v>
       </c>
       <c r="BM17">
-        <v>0.2724732436375104</v>
+        <v>0.2002002110667132</v>
       </c>
       <c r="BN17">
-        <v>0.2724732436375104</v>
+        <v>0.2002002110667132</v>
       </c>
       <c r="BO17">
-        <v>0.2724732436375104</v>
+        <v>0.2602002110667136</v>
       </c>
       <c r="BP17">
-        <v>0.2724732436375149</v>
+        <v>0.2367155258198188</v>
       </c>
       <c r="BQ17">
-        <v>0.272473243637518</v>
+        <v>0.213230840572924</v>
       </c>
       <c r="BR17">
-        <v>0.2724732436375201</v>
+        <v>0.2732308405729241</v>
       </c>
       <c r="BS17">
-        <v>0.2724732436375218</v>
+        <v>0.3332308405729241</v>
       </c>
       <c r="BT17">
-        <v>0.2724732436375237</v>
+        <v>0.3096703868413563</v>
       </c>
       <c r="BU17">
-        <v>0.2367853916683621</v>
+        <v>0.2861099331097884</v>
       </c>
       <c r="BV17">
-        <v>0.2010975396992006</v>
+        <v>0.2625494793782207</v>
       </c>
       <c r="BW17">
-        <v>0.2010975396992018</v>
+        <v>0.2625494793782207</v>
       </c>
       <c r="BX17">
-        <v>0.2010975396992018</v>
+        <v>0.2625494793782207</v>
       </c>
       <c r="BY17">
-        <v>0.2010975396992018</v>
+        <v>0.2625494793782207</v>
       </c>
       <c r="BZ17">
-        <v>0.2010975396992018</v>
+        <v>0.3225494793782206</v>
       </c>
       <c r="CA17">
-        <v>0.2010975396992012</v>
+        <v>0.3825494793782204</v>
       </c>
       <c r="CB17">
-        <v>0.2010975396992012</v>
+        <v>0.3615803886839147</v>
       </c>
       <c r="CC17">
-        <v>0.2010975396992012</v>
+        <v>0.340611297989609</v>
       </c>
       <c r="CD17">
-        <v>0.2010975396992012</v>
+        <v>0.3196422072953032</v>
       </c>
       <c r="CE17">
-        <v>0.2010975396992012</v>
+        <v>0.2986731166009975</v>
       </c>
       <c r="CF17">
-        <v>0.2010975396992012</v>
+        <v>0.3586731166009976</v>
       </c>
       <c r="CG17">
-        <v>0.2010975396992012</v>
+        <v>0.337658910380337</v>
       </c>
       <c r="CH17">
-        <v>0.2010975396992012</v>
+        <v>0.3166447041596763</v>
       </c>
       <c r="CI17">
-        <v>0.2010975396992012</v>
+        <v>0.2956304979390157</v>
       </c>
       <c r="CJ17">
-        <v>0.2010975396992012</v>
+        <v>0.2743223554100151</v>
       </c>
       <c r="CK17">
-        <v>0.2010975396992012</v>
+        <v>0.2530142128810145</v>
       </c>
       <c r="CL17">
-        <v>0.2010975396992012</v>
+        <v>0.2317060703520139</v>
       </c>
       <c r="CM17">
-        <v>0.2010975396992012</v>
+        <v>0.2103979278230133</v>
       </c>
       <c r="CN17">
-        <v>0.2010975396992012</v>
+        <v>0.2103979278230133</v>
       </c>
       <c r="CO17">
-        <v>0.2010975396992012</v>
+        <v>0.2103979278230133</v>
       </c>
       <c r="CP17">
-        <v>0.2010975396992012</v>
+        <v>0.2103979278230133</v>
       </c>
       <c r="CQ17">
-        <v>0.2010975396992012</v>
+        <v>0.2103979278230133</v>
       </c>
       <c r="CR17">
-        <v>0.2010975396992012</v>
+        <v>0.2103979278230133</v>
       </c>
       <c r="CS17">
-        <v>0.2010975396992012</v>
+        <v>0.2103979278230133</v>
       </c>
     </row>
     <row r="18" spans="1:97">
@@ -6630,289 +6630,289 @@
         <v>0.2</v>
       </c>
       <c r="C18">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="D18">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="E18">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="F18">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="G18">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="H18">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="I18">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="J18">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="K18">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="L18">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="M18">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="N18">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="O18">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="P18">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="Q18">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="R18">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S18">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T18">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U18">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V18">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W18">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="X18">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="Y18">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="Z18">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="AA18">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="AB18">
-        <v>0.541205722703498</v>
+        <v>0.6615037225630592</v>
       </c>
       <c r="AC18">
-        <v>0.5224114454070048</v>
+        <v>0.6430074451261208</v>
       </c>
       <c r="AD18">
-        <v>0.5036171681105107</v>
+        <v>0.6245111676891825</v>
       </c>
       <c r="AE18">
-        <v>0.4848228908140172</v>
+        <v>0.6060148902522442</v>
       </c>
       <c r="AF18">
-        <v>0.4660286135175221</v>
+        <v>0.5875186128153058</v>
       </c>
       <c r="AG18">
-        <v>0.4660286135175221</v>
+        <v>0.5651650145644485</v>
       </c>
       <c r="AH18">
-        <v>0.4466403510494152</v>
+        <v>0.542811416313591</v>
       </c>
       <c r="AI18">
-        <v>0.4272520885813084</v>
+        <v>0.5204578180627336</v>
       </c>
       <c r="AJ18">
-        <v>0.4272520885813084</v>
+        <v>0.4959811772704688</v>
       </c>
       <c r="AK18">
-        <v>0.4272520885812885</v>
+        <v>0.4715045364782039</v>
       </c>
       <c r="AL18">
-        <v>0.427252088581285</v>
+        <v>0.4451110956076275</v>
       </c>
       <c r="AM18">
-        <v>0.4272520885812814</v>
+        <v>0.4187176547370511</v>
       </c>
       <c r="AN18">
-        <v>0.4272520885812814</v>
+        <v>0.4187176547370511</v>
       </c>
       <c r="AO18">
-        <v>0.4272520885812814</v>
+        <v>0.4787176547370511</v>
       </c>
       <c r="AP18">
-        <v>0.4272520885812814</v>
+        <v>0.4584315617293762</v>
       </c>
       <c r="AQ18">
-        <v>0.4272520885812814</v>
+        <v>0.4381454687217012</v>
       </c>
       <c r="AR18">
-        <v>0.4272520885812814</v>
+        <v>0.4178593757140261</v>
       </c>
       <c r="AS18">
-        <v>0.4272520885812814</v>
+        <v>0.3975732827063512</v>
       </c>
       <c r="AT18">
-        <v>0.4272520885812814</v>
+        <v>0.3783681405131529</v>
       </c>
       <c r="AU18">
-        <v>0.4272520885812525</v>
+        <v>0.3591629983199546</v>
       </c>
       <c r="AV18">
-        <v>0.4272520885812469</v>
+        <v>0.3399578561267564</v>
       </c>
       <c r="AW18">
-        <v>0.4272520885812463</v>
+        <v>0.3207527139335581</v>
       </c>
       <c r="AX18">
-        <v>0.4272520885812463</v>
+        <v>0.2979102827928086</v>
       </c>
       <c r="AY18">
-        <v>0.4272520885812455</v>
+        <v>0.2750678516520601</v>
       </c>
       <c r="AZ18">
-        <v>0.3957213183233718</v>
+        <v>0.2522254205113117</v>
       </c>
       <c r="BA18">
-        <v>0.395721318323371</v>
+        <v>0.3122254205113117</v>
       </c>
       <c r="BB18">
-        <v>0.395721318323371</v>
+        <v>0.3722254205113117</v>
       </c>
       <c r="BC18">
-        <v>0.395721318323371</v>
+        <v>0.3722254205113117</v>
       </c>
       <c r="BD18">
-        <v>0.3957213183233691</v>
+        <v>0.3543241287155449</v>
       </c>
       <c r="BE18">
-        <v>0.362961639376727</v>
+        <v>0.3364228369197781</v>
       </c>
       <c r="BF18">
-        <v>0.330201960430085</v>
+        <v>0.3185215451240113</v>
       </c>
       <c r="BG18">
-        <v>0.3302019604300833</v>
+        <v>0.3006202533282444</v>
       </c>
       <c r="BH18">
-        <v>0.3022145586675624</v>
+        <v>0.3606202533282444</v>
       </c>
       <c r="BI18">
-        <v>0.2742271569050415</v>
+        <v>0.3460717116133598</v>
       </c>
       <c r="BJ18">
-        <v>0.2462397551425206</v>
+        <v>0.3315231698984752</v>
       </c>
       <c r="BK18">
-        <v>0.2462397551425206</v>
+        <v>0.3169746281835906</v>
       </c>
       <c r="BL18">
-        <v>0.2462397551425206</v>
+        <v>0.302426086468706</v>
       </c>
       <c r="BM18">
-        <v>0.2462397551425193</v>
+        <v>0.2878775447538213</v>
       </c>
       <c r="BN18">
-        <v>0.2462397551425182</v>
+        <v>0.2716728672645969</v>
       </c>
       <c r="BO18">
-        <v>0.2462397551425182</v>
+        <v>0.2554681897753725</v>
       </c>
       <c r="BP18">
-        <v>0.2399887360082943</v>
+        <v>0.2392635122861481</v>
       </c>
       <c r="BQ18">
-        <v>0.2399887360082943</v>
+        <v>0.2230588347969237</v>
       </c>
       <c r="BR18">
-        <v>0.2399887360082943</v>
+        <v>0.2068541573076993</v>
       </c>
       <c r="BS18">
-        <v>0.2177635311293499</v>
+        <v>0.2668541573076993</v>
       </c>
       <c r="BT18">
-        <v>0.2177635311293499</v>
+        <v>0.2668541573076992</v>
       </c>
       <c r="BU18">
-        <v>0.2177635311293499</v>
+        <v>0.2668541573076992</v>
       </c>
       <c r="BV18">
-        <v>0.2177635311293499</v>
+        <v>0.2668541573076992</v>
       </c>
       <c r="BW18">
-        <v>0.2177635311293499</v>
+        <v>0.3268541573076992</v>
       </c>
       <c r="BX18">
-        <v>0.2177635311293499</v>
+        <v>0.3070275454647291</v>
       </c>
       <c r="BY18">
-        <v>0.2177635311293499</v>
+        <v>0.2872009336217589</v>
       </c>
       <c r="BZ18">
-        <v>0.2177635311293499</v>
+        <v>0.2673743217787888</v>
       </c>
       <c r="CA18">
-        <v>0.2177635311293499</v>
+        <v>0.2475477099358187</v>
       </c>
       <c r="CB18">
-        <v>0.2177635311293499</v>
+        <v>0.2277210980928486</v>
       </c>
       <c r="CC18">
-        <v>0.2007860073430107</v>
+        <v>0.2877210980928486</v>
       </c>
       <c r="CD18">
-        <v>0.2007860073430107</v>
+        <v>0.2877210980928486</v>
       </c>
       <c r="CE18">
-        <v>0.2007860073430107</v>
+        <v>0.2666512806686648</v>
       </c>
       <c r="CF18">
-        <v>0.2007860073430107</v>
+        <v>0.2455814632444809</v>
       </c>
       <c r="CG18">
-        <v>0.2007860073430107</v>
+        <v>0.2245116458202971</v>
       </c>
       <c r="CH18">
-        <v>0.2007860073430107</v>
+        <v>0.2034418283961133</v>
       </c>
       <c r="CI18">
-        <v>0.2007860073430107</v>
+        <v>0.2034418283961133</v>
       </c>
       <c r="CJ18">
-        <v>0.2007860073430107</v>
+        <v>0.2034418283961133</v>
       </c>
       <c r="CK18">
-        <v>0.2007860073430107</v>
+        <v>0.2034418283961133</v>
       </c>
       <c r="CL18">
-        <v>0.2007860073430107</v>
+        <v>0.2034418283961133</v>
       </c>
       <c r="CM18">
-        <v>0.2007860073430107</v>
+        <v>0.2034418283961133</v>
       </c>
       <c r="CN18">
-        <v>0.2007860073430107</v>
+        <v>0.2034418283961133</v>
       </c>
       <c r="CO18">
-        <v>0.2007860073430107</v>
+        <v>0.2034418283961133</v>
       </c>
       <c r="CP18">
-        <v>0.2007860073430107</v>
+        <v>0.2034418283961133</v>
       </c>
       <c r="CQ18">
-        <v>0.2007860073430107</v>
+        <v>0.2034418283961133</v>
       </c>
       <c r="CR18">
-        <v>0.2007860073430107</v>
+        <v>0.2034418283961133</v>
       </c>
       <c r="CS18">
-        <v>0.2007860073430107</v>
+        <v>0.2034418283961133</v>
       </c>
     </row>
     <row r="19" spans="1:97">
@@ -6932,46 +6932,46 @@
         <v>0.2</v>
       </c>
       <c r="F19">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="G19">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="H19">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="I19">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="J19">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="K19">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="L19">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="M19">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="N19">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="O19">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="P19">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="Q19">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="R19">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="S19">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="T19">
         <v>0.44</v>
@@ -6980,232 +6980,232 @@
         <v>0.44</v>
       </c>
       <c r="V19">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="W19">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="X19">
-        <v>0.44</v>
+        <v>0.4801563446718958</v>
       </c>
       <c r="Y19">
-        <v>0.5</v>
+        <v>0.4603126893437919</v>
       </c>
       <c r="Z19">
-        <v>0.5600000000000001</v>
+        <v>0.4404690340156878</v>
       </c>
       <c r="AA19">
-        <v>0.62</v>
+        <v>0.4206253786875839</v>
       </c>
       <c r="AB19">
-        <v>0.62</v>
+        <v>0.4007817233594799</v>
       </c>
       <c r="AC19">
-        <v>0.62</v>
+        <v>0.3778741163734529</v>
       </c>
       <c r="AD19">
-        <v>0.62</v>
+        <v>0.3549665093874259</v>
       </c>
       <c r="AE19">
-        <v>0.6029309994750058</v>
+        <v>0.3320589024013988</v>
       </c>
       <c r="AF19">
-        <v>0.5858619989500117</v>
+        <v>0.3139781220882585</v>
       </c>
       <c r="AG19">
-        <v>0.5668874531773287</v>
+        <v>0.2958973417751182</v>
       </c>
       <c r="AH19">
-        <v>0.5479129074046457</v>
+        <v>0.2778165614619778</v>
       </c>
       <c r="AI19">
-        <v>0.5479129074046457</v>
+        <v>0.2597357811488374</v>
       </c>
       <c r="AJ19">
-        <v>0.5479129074046457</v>
+        <v>0.241655000835697</v>
       </c>
       <c r="AK19">
-        <v>0.5479129074046457</v>
+        <v>0.3016550008356971</v>
       </c>
       <c r="AL19">
-        <v>0.5479129074046457</v>
+        <v>0.3616550008356971</v>
       </c>
       <c r="AM19">
-        <v>0.5479129074046457</v>
+        <v>0.34309403443692</v>
       </c>
       <c r="AN19">
-        <v>0.5479129074046457</v>
+        <v>0.3245330680381429</v>
       </c>
       <c r="AO19">
-        <v>0.5479129074046457</v>
+        <v>0.3059721016393658</v>
       </c>
       <c r="AP19">
-        <v>0.5479129074046457</v>
+        <v>0.2874111352405888</v>
       </c>
       <c r="AQ19">
-        <v>0.5421799540541861</v>
+        <v>0.3474111352405888</v>
       </c>
       <c r="AR19">
-        <v>0.5364470007037264</v>
+        <v>0.4074111352405888</v>
       </c>
       <c r="AS19">
-        <v>0.5307140473532669</v>
+        <v>0.4674111352405887</v>
       </c>
       <c r="AT19">
-        <v>0.5249810940028072</v>
+        <v>0.443703564114926</v>
       </c>
       <c r="AU19">
-        <v>0.5192481406523477</v>
+        <v>0.4199959929892633</v>
       </c>
       <c r="AV19">
-        <v>0.5192481406523477</v>
+        <v>0.3962884218636005</v>
       </c>
       <c r="AW19">
-        <v>0.4986596239192866</v>
+        <v>0.3710175033421103</v>
       </c>
       <c r="AX19">
-        <v>0.4780711071862256</v>
+        <v>0.34574658482062</v>
       </c>
       <c r="AY19">
-        <v>0.4780711071862256</v>
+        <v>0.3204756662991298</v>
       </c>
       <c r="AZ19">
-        <v>0.4448754603256553</v>
+        <v>0.3204756662991298</v>
       </c>
       <c r="BA19">
-        <v>0.411679813465085</v>
+        <v>0.3204756662991298</v>
       </c>
       <c r="BB19">
-        <v>0.3784841666045146</v>
+        <v>0.3204756662991298</v>
       </c>
       <c r="BC19">
-        <v>0.3784841666045146</v>
+        <v>0.3024541417664651</v>
       </c>
       <c r="BD19">
-        <v>0.3784841666045146</v>
+        <v>0.2844326172338004</v>
       </c>
       <c r="BE19">
-        <v>0.3784841666045146</v>
+        <v>0.2664110927011357</v>
       </c>
       <c r="BF19">
-        <v>0.3784841666045146</v>
+        <v>0.2483895681684711</v>
       </c>
       <c r="BG19">
-        <v>0.3784841666045146</v>
+        <v>0.2483895681684711</v>
       </c>
       <c r="BH19">
-        <v>0.3423731715780991</v>
+        <v>0.2483895681684711</v>
       </c>
       <c r="BI19">
-        <v>0.3423731715780991</v>
+        <v>0.2483895681684711</v>
       </c>
       <c r="BJ19">
-        <v>0.3423731715780991</v>
+        <v>0.3083895681684711</v>
       </c>
       <c r="BK19">
-        <v>0.3423731715780991</v>
+        <v>0.3083895681684711</v>
       </c>
       <c r="BL19">
-        <v>0.3423731715780991</v>
+        <v>0.3083895681684711</v>
       </c>
       <c r="BM19">
-        <v>0.3423731715780991</v>
+        <v>0.293915088271518</v>
       </c>
       <c r="BN19">
-        <v>0.3423731715780991</v>
+        <v>0.2794406083745649</v>
       </c>
       <c r="BO19">
-        <v>0.3423731715780991</v>
+        <v>0.2649661284776117</v>
       </c>
       <c r="BP19">
-        <v>0.3423731715780991</v>
+        <v>0.2504916485806585</v>
       </c>
       <c r="BQ19">
-        <v>0.3423731715780991</v>
+        <v>0.2360171686837055</v>
       </c>
       <c r="BR19">
-        <v>0.2627418387879069</v>
+        <v>0.2960171686837054</v>
       </c>
       <c r="BS19">
-        <v>0.2627418387879069</v>
+        <v>0.273046291248715</v>
       </c>
       <c r="BT19">
-        <v>0.2627418387879069</v>
+        <v>0.2500754138137245</v>
       </c>
       <c r="BU19">
-        <v>0.2627418387879069</v>
+        <v>0.3100754138137245</v>
       </c>
       <c r="BV19">
-        <v>0.2627418387879069</v>
+        <v>0.2899122019536837</v>
       </c>
       <c r="BW19">
-        <v>0.2627418387879069</v>
+        <v>0.2697489900936429</v>
       </c>
       <c r="BX19">
-        <v>0.2627418387879069</v>
+        <v>0.2495857782336021</v>
       </c>
       <c r="BY19">
-        <v>0.2627418387879069</v>
+        <v>0.2294225663735613</v>
       </c>
       <c r="BZ19">
-        <v>0.2627418387879069</v>
+        <v>0.2894225663735613</v>
       </c>
       <c r="CA19">
-        <v>0.2627418387879069</v>
+        <v>0.2894225663735613</v>
       </c>
       <c r="CB19">
-        <v>0.2627418387879069</v>
+        <v>0.3494225663735613</v>
       </c>
       <c r="CC19">
-        <v>0.2627418387879069</v>
+        <v>0.3284548830665524</v>
       </c>
       <c r="CD19">
-        <v>0.2627418387879069</v>
+        <v>0.3074871997595435</v>
       </c>
       <c r="CE19">
-        <v>0.2627418387879069</v>
+        <v>0.2865195164525346</v>
       </c>
       <c r="CF19">
-        <v>0.2627418387879069</v>
+        <v>0.2655518331455257</v>
       </c>
       <c r="CG19">
-        <v>0.2627418387879069</v>
+        <v>0.2655518331455257</v>
       </c>
       <c r="CH19">
-        <v>0.2627418387879069</v>
+        <v>0.2655518331455257</v>
       </c>
       <c r="CI19">
-        <v>0.2627418387879069</v>
+        <v>0.2442144876027506</v>
       </c>
       <c r="CJ19">
-        <v>0.231634449365141</v>
+        <v>0.2228771420599756</v>
       </c>
       <c r="CK19">
-        <v>0.2005270599423751</v>
+        <v>0.2015397965172005</v>
       </c>
       <c r="CL19">
-        <v>0.2005270599423751</v>
+        <v>0.2015397965172005</v>
       </c>
       <c r="CM19">
-        <v>0.2005270599423751</v>
+        <v>0.2015397965172005</v>
       </c>
       <c r="CN19">
-        <v>0.2005270599423751</v>
+        <v>0.2015397965172005</v>
       </c>
       <c r="CO19">
-        <v>0.2005270599423751</v>
+        <v>0.2015397965172005</v>
       </c>
       <c r="CP19">
-        <v>0.2005270599423751</v>
+        <v>0.2015397965172005</v>
       </c>
       <c r="CQ19">
-        <v>0.2005270599423751</v>
+        <v>0.2015397965172005</v>
       </c>
       <c r="CR19">
-        <v>0.2005270599423751</v>
+        <v>0.2015397965172005</v>
       </c>
       <c r="CS19">
-        <v>0.2005270599423751</v>
+        <v>0.2015397965172005</v>
       </c>
     </row>
     <row r="20" spans="1:97">
@@ -7237,22 +7237,22 @@
         <v>0.26</v>
       </c>
       <c r="J20">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="K20">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="L20">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="M20">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="N20">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="O20">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="P20">
         <v>0.38</v>
@@ -7273,7 +7273,7 @@
         <v>0.38</v>
       </c>
       <c r="V20">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="W20">
         <v>0.44</v>
@@ -7285,220 +7285,220 @@
         <v>0.44</v>
       </c>
       <c r="Z20">
-        <v>0.44</v>
+        <v>0.4214151267680153</v>
       </c>
       <c r="AA20">
-        <v>0.44</v>
+        <v>0.4028302535360306</v>
       </c>
       <c r="AB20">
-        <v>0.44</v>
+        <v>0.3842453803040459</v>
       </c>
       <c r="AC20">
-        <v>0.44</v>
+        <v>0.3656605070720612</v>
       </c>
       <c r="AD20">
-        <v>0.44</v>
+        <v>0.3470756338400765</v>
       </c>
       <c r="AE20">
-        <v>0.44</v>
+        <v>0.3296733196657039</v>
       </c>
       <c r="AF20">
-        <v>0.4164800186063271</v>
+        <v>0.3122710054913312</v>
       </c>
       <c r="AG20">
-        <v>0.3929600372126542</v>
+        <v>0.2948686913169587</v>
       </c>
       <c r="AH20">
-        <v>0.3694400558189813</v>
+        <v>0.277466377142586</v>
       </c>
       <c r="AI20">
-        <v>0.3694400558189813</v>
+        <v>0.2600640629682134</v>
       </c>
       <c r="AJ20">
-        <v>0.3694400558189813</v>
+        <v>0.3200640629682134</v>
       </c>
       <c r="AK20">
-        <v>0.3694400558189813</v>
+        <v>0.380064062968214</v>
       </c>
       <c r="AL20">
-        <v>0.3694400558189813</v>
+        <v>0.380064062968214</v>
       </c>
       <c r="AM20">
-        <v>0.3694400558189813</v>
+        <v>0.3555874221759492</v>
       </c>
       <c r="AN20">
-        <v>0.3694400558189813</v>
+        <v>0.331110781383685</v>
       </c>
       <c r="AO20">
-        <v>0.3694400558189813</v>
+        <v>0.3066341405914202</v>
       </c>
       <c r="AP20">
-        <v>0.3694400558189813</v>
+        <v>0.3666341405914202</v>
       </c>
       <c r="AQ20">
-        <v>0.3694400558189813</v>
+        <v>0.3429749142923277</v>
       </c>
       <c r="AR20">
-        <v>0.3694400558189813</v>
+        <v>0.3193156879932351</v>
       </c>
       <c r="AS20">
-        <v>0.3694400558189813</v>
+        <v>0.2956564616941426</v>
       </c>
       <c r="AT20">
-        <v>0.3694400558189813</v>
+        <v>0.2956564616941426</v>
       </c>
       <c r="AU20">
-        <v>0.3694400558189813</v>
+        <v>0.2956564616941426</v>
       </c>
       <c r="AV20">
-        <v>0.3694400558189813</v>
+        <v>0.3556564616941409</v>
       </c>
       <c r="AW20">
-        <v>0.3694400558189813</v>
+        <v>0.3556564616941409</v>
       </c>
       <c r="AX20">
-        <v>0.3694400558189813</v>
+        <v>0.3370683184182693</v>
       </c>
       <c r="AY20">
-        <v>0.3694400558189813</v>
+        <v>0.3184801751423977</v>
       </c>
       <c r="AZ20">
-        <v>0.3694400558189813</v>
+        <v>0.299892031866526</v>
       </c>
       <c r="BA20">
-        <v>0.3694400558189813</v>
+        <v>0.2813038885906544</v>
       </c>
       <c r="BB20">
-        <v>0.3694400558189813</v>
+        <v>0.2627157453147827</v>
       </c>
       <c r="BC20">
-        <v>0.3694400558189813</v>
+        <v>0.2627157453147827</v>
       </c>
       <c r="BD20">
-        <v>0.3694400558189813</v>
+        <v>0.2627157453147827</v>
       </c>
       <c r="BE20">
-        <v>0.3456860830708955</v>
+        <v>0.2627157453147827</v>
       </c>
       <c r="BF20">
-        <v>0.3219321103228098</v>
+        <v>0.2627157453147827</v>
       </c>
       <c r="BG20">
-        <v>0.3219321103228098</v>
+        <v>0.3227157453147827</v>
       </c>
       <c r="BH20">
-        <v>0.3219321103228098</v>
+        <v>0.2974751747754488</v>
       </c>
       <c r="BI20">
-        <v>0.3219321103228098</v>
+        <v>0.2722346042361151</v>
       </c>
       <c r="BJ20">
-        <v>0.3219321103228098</v>
+        <v>0.2578117776959065</v>
       </c>
       <c r="BK20">
-        <v>0.3219321103228098</v>
+        <v>0.243388951155698</v>
       </c>
       <c r="BL20">
-        <v>0.3219321103228098</v>
+        <v>0.2289661246154895</v>
       </c>
       <c r="BM20">
-        <v>0.2937606720536345</v>
+        <v>0.214543298075281</v>
       </c>
       <c r="BN20">
-        <v>0.2937606720536345</v>
+        <v>0.2001204715350725</v>
       </c>
       <c r="BO20">
-        <v>0.2808560083746729</v>
+        <v>0.2601204715350725</v>
       </c>
       <c r="BP20">
-        <v>0.2679513446957114</v>
+        <v>0.320120471535072</v>
       </c>
       <c r="BQ20">
-        <v>0.2550466810167498</v>
+        <v>0.3027108458200247</v>
       </c>
       <c r="BR20">
-        <v>0.2550466810167498</v>
+        <v>0.2853012201049773</v>
       </c>
       <c r="BS20">
-        <v>0.2550466810167498</v>
+        <v>0.2678915943899299</v>
       </c>
       <c r="BT20">
-        <v>0.2550466810167498</v>
+        <v>0.2504819686748826</v>
       </c>
       <c r="BU20">
-        <v>0.2550466810167498</v>
+        <v>0.2330723429598353</v>
       </c>
       <c r="BV20">
-        <v>0.2550466810167498</v>
+        <v>0.2330723429598353</v>
       </c>
       <c r="BW20">
-        <v>0.2550466810167498</v>
+        <v>0.2330723429598353</v>
       </c>
       <c r="BX20">
-        <v>0.2550466810167498</v>
+        <v>0.2930723429598353</v>
       </c>
       <c r="BY20">
-        <v>0.2550466810167498</v>
+        <v>0.2656794222048525</v>
       </c>
       <c r="BZ20">
-        <v>0.252315326923836</v>
+        <v>0.2382865014498697</v>
       </c>
       <c r="CA20">
-        <v>0.2495839728309221</v>
+        <v>0.2382865014498696</v>
       </c>
       <c r="CB20">
-        <v>0.2495839728309221</v>
+        <v>0.2982865014498696</v>
       </c>
       <c r="CC20">
-        <v>0.2495839728309221</v>
+        <v>0.2788480802371832</v>
       </c>
       <c r="CD20">
-        <v>0.2495839728309221</v>
+        <v>0.2594096590244968</v>
       </c>
       <c r="CE20">
-        <v>0.2495839728309221</v>
+        <v>0.2399712378118104</v>
       </c>
       <c r="CF20">
-        <v>0.2495839728309221</v>
+        <v>0.220532816599124</v>
       </c>
       <c r="CG20">
-        <v>0.2495839728309221</v>
+        <v>0.220532816599124</v>
       </c>
       <c r="CH20">
-        <v>0.2495839728309221</v>
+        <v>0.220532816599124</v>
       </c>
       <c r="CI20">
-        <v>0.227333429780772</v>
+        <v>0.220532816599124</v>
       </c>
       <c r="CJ20">
-        <v>0.205082886730622</v>
+        <v>0.220532816599124</v>
       </c>
       <c r="CK20">
-        <v>0.205082886730622</v>
+        <v>0.220532816599124</v>
       </c>
       <c r="CL20">
-        <v>0.205082886730622</v>
+        <v>0.220532816599124</v>
       </c>
       <c r="CM20">
-        <v>0.205082886730622</v>
+        <v>0.220532816599124</v>
       </c>
       <c r="CN20">
-        <v>0.205082886730622</v>
+        <v>0.220532816599124</v>
       </c>
       <c r="CO20">
-        <v>0.2050828867306218</v>
+        <v>0.220532816599124</v>
       </c>
       <c r="CP20">
-        <v>0.2050828867306218</v>
+        <v>0.220532816599124</v>
       </c>
       <c r="CQ20">
-        <v>0.2050828867306218</v>
+        <v>0.220532816599124</v>
       </c>
       <c r="CR20">
-        <v>0.2050828867306218</v>
+        <v>0.220532816599124</v>
       </c>
       <c r="CS20">
-        <v>0.2050828867306218</v>
+        <v>0.220532816599124</v>
       </c>
     </row>
     <row r="21" spans="1:97">
@@ -7521,28 +7521,28 @@
         <v>0.26</v>
       </c>
       <c r="G21">
+        <v>0.26</v>
+      </c>
+      <c r="H21">
+        <v>0.26</v>
+      </c>
+      <c r="I21">
+        <v>0.26</v>
+      </c>
+      <c r="J21">
+        <v>0.26</v>
+      </c>
+      <c r="K21">
+        <v>0.26</v>
+      </c>
+      <c r="L21">
+        <v>0.26</v>
+      </c>
+      <c r="M21">
         <v>0.32</v>
       </c>
-      <c r="H21">
+      <c r="N21">
         <v>0.32</v>
-      </c>
-      <c r="I21">
-        <v>0.32</v>
-      </c>
-      <c r="J21">
-        <v>0.32</v>
-      </c>
-      <c r="K21">
-        <v>0.32</v>
-      </c>
-      <c r="L21">
-        <v>0.32</v>
-      </c>
-      <c r="M21">
-        <v>0.38</v>
-      </c>
-      <c r="N21">
-        <v>0.38</v>
       </c>
       <c r="O21">
         <v>0.38</v>
@@ -7551,247 +7551,247 @@
         <v>0.38</v>
       </c>
       <c r="Q21">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="R21">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="S21">
         <v>0.44</v>
       </c>
       <c r="T21">
+        <v>0.44</v>
+      </c>
+      <c r="U21">
+        <v>0.44</v>
+      </c>
+      <c r="V21">
+        <v>0.44</v>
+      </c>
+      <c r="W21">
+        <v>0.44</v>
+      </c>
+      <c r="X21">
+        <v>0.44</v>
+      </c>
+      <c r="Y21">
+        <v>0.44</v>
+      </c>
+      <c r="Z21">
+        <v>0.44</v>
+      </c>
+      <c r="AA21">
+        <v>0.44</v>
+      </c>
+      <c r="AB21">
         <v>0.5</v>
       </c>
-      <c r="U21">
+      <c r="AC21">
+        <v>0.5</v>
+      </c>
+      <c r="AD21">
         <v>0.5600000000000001</v>
       </c>
-      <c r="V21">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="W21">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="X21">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="Y21">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="Z21">
-        <v>0.62</v>
-      </c>
-      <c r="AA21">
-        <v>0.62</v>
-      </c>
-      <c r="AB21">
-        <v>0.62</v>
-      </c>
-      <c r="AC21">
-        <v>0.6017424237088631</v>
-      </c>
-      <c r="AD21">
-        <v>0.583484847417732</v>
-      </c>
       <c r="AE21">
-        <v>0.5652272711266009</v>
+        <v>0.542811744665076</v>
       </c>
       <c r="AF21">
-        <v>0.5469696948354698</v>
+        <v>0.5256234893301518</v>
       </c>
       <c r="AG21">
-        <v>0.5275150984844407</v>
+        <v>0.5084352339952277</v>
       </c>
       <c r="AH21">
-        <v>0.5080605021334115</v>
+        <v>0.4912469786603036</v>
       </c>
       <c r="AI21">
-        <v>0.4886059057823823</v>
+        <v>0.4740587233253795</v>
       </c>
       <c r="AJ21">
-        <v>0.470538977917761</v>
+        <v>0.4537639539691753</v>
       </c>
       <c r="AK21">
-        <v>0.4524720500531397</v>
+        <v>0.433469184612971</v>
       </c>
       <c r="AL21">
-        <v>0.4344051221885183</v>
+        <v>0.4131744152567667</v>
       </c>
       <c r="AM21">
-        <v>0.416338194323897</v>
+        <v>0.3928796459005625</v>
       </c>
       <c r="AN21">
-        <v>0.3982712664592757</v>
+        <v>0.3725848765443582</v>
       </c>
       <c r="AO21">
-        <v>0.3982712664592757</v>
+        <v>0.4325848765443583</v>
       </c>
       <c r="AP21">
-        <v>0.3982712664592757</v>
+        <v>0.4130818914949776</v>
       </c>
       <c r="AQ21">
-        <v>0.3982712664592757</v>
+        <v>0.393578906445597</v>
       </c>
       <c r="AR21">
-        <v>0.3982712664592757</v>
+        <v>0.3740759213962164</v>
       </c>
       <c r="AS21">
-        <v>0.3982712664592757</v>
+        <v>0.3545729363468358</v>
       </c>
       <c r="AT21">
-        <v>0.3982712664592757</v>
+        <v>0.3350699512974552</v>
       </c>
       <c r="AU21">
-        <v>0.3982712664592757</v>
+        <v>0.3350699512974552</v>
       </c>
       <c r="AV21">
-        <v>0.3982712664592757</v>
+        <v>0.3350699512974552</v>
       </c>
       <c r="AW21">
-        <v>0.3982712664592757</v>
+        <v>0.3350699512974552</v>
       </c>
       <c r="AX21">
-        <v>0.3982712664592757</v>
+        <v>0.3164310632865238</v>
       </c>
       <c r="AY21">
-        <v>0.3982712664592757</v>
+        <v>0.2977921752755925</v>
       </c>
       <c r="AZ21">
-        <v>0.3982712664592757</v>
+        <v>0.2791532872646612</v>
       </c>
       <c r="BA21">
-        <v>0.3982712664592757</v>
+        <v>0.2605143992537298</v>
       </c>
       <c r="BB21">
-        <v>0.3982712664592757</v>
+        <v>0.2605143992537298</v>
       </c>
       <c r="BC21">
-        <v>0.3982712664592757</v>
+        <v>0.3205143992537298</v>
       </c>
       <c r="BD21">
-        <v>0.3982712664592757</v>
+        <v>0.3205143992537298</v>
       </c>
       <c r="BE21">
-        <v>0.3982712664592757</v>
+        <v>0.3805143992537298</v>
       </c>
       <c r="BF21">
-        <v>0.3982712664592757</v>
+        <v>0.3805143992537298</v>
       </c>
       <c r="BG21">
-        <v>0.3982712664592757</v>
+        <v>0.3805143992537298</v>
       </c>
       <c r="BH21">
-        <v>0.3982712664592757</v>
+        <v>0.3649580114019266</v>
       </c>
       <c r="BI21">
-        <v>0.3982712664592757</v>
+        <v>0.3494016235501235</v>
       </c>
       <c r="BJ21">
-        <v>0.3982712664592757</v>
+        <v>0.3338452356983203</v>
       </c>
       <c r="BK21">
-        <v>0.3982712664592757</v>
+        <v>0.3182888478465171</v>
       </c>
       <c r="BL21">
-        <v>0.3982712664592757</v>
+        <v>0.3027324599947139</v>
       </c>
       <c r="BM21">
-        <v>0.3796900172305871</v>
+        <v>0.3627324599947139</v>
       </c>
       <c r="BN21">
-        <v>0.297141805513517</v>
+        <v>0.3481268802731484</v>
       </c>
       <c r="BO21">
-        <v>0.297141805513517</v>
+        <v>0.3335213005515828</v>
       </c>
       <c r="BP21">
-        <v>0.297141805513517</v>
+        <v>0.3189157208300172</v>
       </c>
       <c r="BQ21">
-        <v>0.297141805513517</v>
+        <v>0.3043101411084516</v>
       </c>
       <c r="BR21">
-        <v>0.297141805513517</v>
+        <v>0.289704561386886</v>
       </c>
       <c r="BS21">
-        <v>0.297141805513517</v>
+        <v>0.2644904028094447</v>
       </c>
       <c r="BT21">
-        <v>0.297141805513517</v>
+        <v>0.2392762442320034</v>
       </c>
       <c r="BU21">
-        <v>0.297141805513517</v>
+        <v>0.2140620856545621</v>
       </c>
       <c r="BV21">
-        <v>0.297141805513517</v>
+        <v>0.2740620856545621</v>
       </c>
       <c r="BW21">
-        <v>0.297141805513517</v>
+        <v>0.2501303109911327</v>
       </c>
       <c r="BX21">
-        <v>0.2686787606602832</v>
+        <v>0.2261985363277032</v>
       </c>
       <c r="BY21">
-        <v>0.2402157158070494</v>
+        <v>0.2261985363277032</v>
       </c>
       <c r="BZ21">
-        <v>0.2117526709538157</v>
+        <v>0.2861985363277032</v>
       </c>
       <c r="CA21">
-        <v>0.2117526709538157</v>
+        <v>0.2666718227990312</v>
       </c>
       <c r="CB21">
-        <v>0.2117526709538157</v>
+        <v>0.2471451092703592</v>
       </c>
       <c r="CC21">
-        <v>0.2117526709538157</v>
+        <v>0.2276183957416872</v>
       </c>
       <c r="CD21">
-        <v>0.2117526709538157</v>
+        <v>0.2080916822130152</v>
       </c>
       <c r="CE21">
-        <v>0.2117526709538157</v>
+        <v>0.2080916822130152</v>
       </c>
       <c r="CF21">
-        <v>0.2117526709538157</v>
+        <v>0.2080916822130152</v>
       </c>
       <c r="CG21">
-        <v>0.2117526709538157</v>
+        <v>0.2080916822130152</v>
       </c>
       <c r="CH21">
-        <v>0.2117526709538157</v>
+        <v>0.2080916822130152</v>
       </c>
       <c r="CI21">
-        <v>0.2117526709538157</v>
+        <v>0.2680916822130152</v>
       </c>
       <c r="CJ21">
-        <v>0.2117526709538157</v>
+        <v>0.3280916822130152</v>
       </c>
       <c r="CK21">
-        <v>0.2117526709538157</v>
+        <v>0.3045328601041212</v>
       </c>
       <c r="CL21">
-        <v>0.2117526709538157</v>
+        <v>0.2809740379952274</v>
       </c>
       <c r="CM21">
-        <v>0.2117526709538157</v>
+        <v>0.2574152158863334</v>
       </c>
       <c r="CN21">
-        <v>0.2117526709538157</v>
+        <v>0.2338563937774395</v>
       </c>
       <c r="CO21">
-        <v>0.2117526709538157</v>
+        <v>0.2338563937774395</v>
       </c>
       <c r="CP21">
-        <v>0.2117526709538157</v>
+        <v>0.2338563937774395</v>
       </c>
       <c r="CQ21">
-        <v>0.2117526709538157</v>
+        <v>0.2338563937774395</v>
       </c>
       <c r="CR21">
-        <v>0.2117526709538157</v>
+        <v>0.2338563937774395</v>
       </c>
       <c r="CS21">
-        <v>0.2117526709538157</v>
+        <v>0.2338563937774395</v>
       </c>
     </row>
     <row r="22" spans="1:97">
@@ -7802,289 +7802,289 @@
         <v>0.2</v>
       </c>
       <c r="C22">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="D22">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="E22">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="F22">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="G22">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="H22">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="I22">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="J22">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="K22">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="L22">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="M22">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="N22">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="O22">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="P22">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="Q22">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="R22">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="S22">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="T22">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="U22">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="V22">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="W22">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="X22">
-        <v>0.44</v>
+        <v>0.4708117266380938</v>
       </c>
       <c r="Y22">
-        <v>0.44</v>
+        <v>0.4416234532761877</v>
       </c>
       <c r="Z22">
-        <v>0.44</v>
+        <v>0.4124351799142815</v>
       </c>
       <c r="AA22">
-        <v>0.44</v>
+        <v>0.3908095606924451</v>
       </c>
       <c r="AB22">
-        <v>0.5</v>
+        <v>0.3691839414706087</v>
       </c>
       <c r="AC22">
-        <v>0.5600000000000001</v>
+        <v>0.3475583222487723</v>
       </c>
       <c r="AD22">
-        <v>0.5380117751607604</v>
+        <v>0.3259327030269358</v>
       </c>
       <c r="AE22">
-        <v>0.5160235503215221</v>
+        <v>0.3859327030269358</v>
       </c>
       <c r="AF22">
-        <v>0.4940353254822837</v>
+        <v>0.3629858700581459</v>
       </c>
       <c r="AG22">
-        <v>0.4940353254822837</v>
+        <v>0.340039037089356</v>
       </c>
       <c r="AH22">
-        <v>0.4940353254822837</v>
+        <v>0.317092204120566</v>
       </c>
       <c r="AI22">
-        <v>0.4737064233041311</v>
+        <v>0.2914381923886483</v>
       </c>
       <c r="AJ22">
-        <v>0.4533775211259785</v>
+        <v>0.2657841806567305</v>
       </c>
       <c r="AK22">
-        <v>0.4330486189478258</v>
+        <v>0.2401301689248126</v>
       </c>
       <c r="AL22">
-        <v>0.4127197167696732</v>
+        <v>0.3001301689248127</v>
       </c>
       <c r="AM22">
-        <v>0.4127197167696732</v>
+        <v>0.3001301689248127</v>
       </c>
       <c r="AN22">
-        <v>0.4127197167696732</v>
+        <v>0.3601301689248127</v>
       </c>
       <c r="AO22">
-        <v>0.4127197167696732</v>
+        <v>0.4201301689248127</v>
       </c>
       <c r="AP22">
-        <v>0.4127197167696732</v>
+        <v>0.4801301689248127</v>
       </c>
       <c r="AQ22">
-        <v>0.4127197167696732</v>
+        <v>0.5401301689248127</v>
       </c>
       <c r="AR22">
-        <v>0.4127197167696732</v>
+        <v>0.520556086504517</v>
       </c>
       <c r="AS22">
-        <v>0.4127197167696732</v>
+        <v>0.5009820040842212</v>
       </c>
       <c r="AT22">
-        <v>0.4127197167696732</v>
+        <v>0.4814079216639254</v>
       </c>
       <c r="AU22">
-        <v>0.4127197167696732</v>
+        <v>0.4618338392436297</v>
       </c>
       <c r="AV22">
-        <v>0.4127197167696732</v>
+        <v>0.442259756823334</v>
       </c>
       <c r="AW22">
-        <v>0.4127197167696732</v>
+        <v>0.442259756823334</v>
       </c>
       <c r="AX22">
-        <v>0.4127197167696732</v>
+        <v>0.502259756823334</v>
       </c>
       <c r="AY22">
-        <v>0.4127197167696732</v>
+        <v>0.4846428855577922</v>
       </c>
       <c r="AZ22">
-        <v>0.384761049820442</v>
+        <v>0.4670260142922504</v>
       </c>
       <c r="BA22">
-        <v>0.3568023828712109</v>
+        <v>0.4494091430267086</v>
       </c>
       <c r="BB22">
-        <v>0.3288437159219796</v>
+        <v>0.4317922717611667</v>
       </c>
       <c r="BC22">
-        <v>0.3288437159219796</v>
+        <v>0.4317922717611667</v>
       </c>
       <c r="BD22">
-        <v>0.3288437159219796</v>
+        <v>0.4917922717611669</v>
       </c>
       <c r="BE22">
-        <v>0.3288437159219796</v>
+        <v>0.4681922725088752</v>
       </c>
       <c r="BF22">
-        <v>0.3288437159219796</v>
+        <v>0.4445922732565837</v>
       </c>
       <c r="BG22">
-        <v>0.3288437159219797</v>
+        <v>0.4209922740042921</v>
       </c>
       <c r="BH22">
-        <v>0.3288437159219797</v>
+        <v>0.4033247820437716</v>
       </c>
       <c r="BI22">
-        <v>0.3102535645989814</v>
+        <v>0.3856572900832511</v>
       </c>
       <c r="BJ22">
-        <v>0.2916634132759831</v>
+        <v>0.3679897981227306</v>
       </c>
       <c r="BK22">
-        <v>0.2916634132759831</v>
+        <v>0.3503223061622101</v>
       </c>
       <c r="BL22">
-        <v>0.2916634132759831</v>
+        <v>0.3326548142016895</v>
       </c>
       <c r="BM22">
-        <v>0.2916634132759831</v>
+        <v>0.3326548142016895</v>
       </c>
       <c r="BN22">
-        <v>0.2916634132759831</v>
+        <v>0.3926548142016895</v>
       </c>
       <c r="BO22">
-        <v>0.2916634132759831</v>
+        <v>0.3766295164081215</v>
       </c>
       <c r="BP22">
-        <v>0.2688612926110785</v>
+        <v>0.3606042186145536</v>
       </c>
       <c r="BQ22">
-        <v>0.246059171946174</v>
+        <v>0.3445789208209856</v>
       </c>
       <c r="BR22">
-        <v>0.246059171946174</v>
+        <v>0.3285536230274176</v>
       </c>
       <c r="BS22">
-        <v>0.246059171946174</v>
+        <v>0.3125283252338496</v>
       </c>
       <c r="BT22">
-        <v>0.246059171946174</v>
+        <v>0.2954704511125843</v>
       </c>
       <c r="BU22">
-        <v>0.246059171946174</v>
+        <v>0.278412576991319</v>
       </c>
       <c r="BV22">
-        <v>0.246059171946174</v>
+        <v>0.2613547028700536</v>
       </c>
       <c r="BW22">
-        <v>0.246059171946174</v>
+        <v>0.2442968287487883</v>
       </c>
       <c r="BX22">
-        <v>0.246059171946174</v>
+        <v>0.227238954627523</v>
       </c>
       <c r="BY22">
-        <v>0.225012156532841</v>
+        <v>0.227238954627523</v>
       </c>
       <c r="BZ22">
-        <v>0.2039651411195081</v>
+        <v>0.227238954627523</v>
       </c>
       <c r="CA22">
-        <v>0.2039651411195081</v>
+        <v>0.227238954627523</v>
       </c>
       <c r="CB22">
-        <v>0.2039651411195081</v>
+        <v>0.227238954627523</v>
       </c>
       <c r="CC22">
-        <v>0.2039651411195081</v>
+        <v>0.287238954627523</v>
       </c>
       <c r="CD22">
-        <v>0.2039651411195081</v>
+        <v>0.347238954627523</v>
       </c>
       <c r="CE22">
-        <v>0.2039651411195081</v>
+        <v>0.347238954627523</v>
       </c>
       <c r="CF22">
-        <v>0.2039651411195081</v>
+        <v>0.3186520108475472</v>
       </c>
       <c r="CG22">
-        <v>0.2039651411195081</v>
+        <v>0.2900650670675714</v>
       </c>
       <c r="CH22">
-        <v>0.2039651411195081</v>
+        <v>0.2614781232875957</v>
       </c>
       <c r="CI22">
-        <v>0.2039651411195081</v>
+        <v>0.2342197452246771</v>
       </c>
       <c r="CJ22">
-        <v>0.2039651411195081</v>
+        <v>0.2069613671617585</v>
       </c>
       <c r="CK22">
-        <v>0.2039651411195081</v>
+        <v>0.2069613671617585</v>
       </c>
       <c r="CL22">
-        <v>0.2039651411195081</v>
+        <v>0.2069613671617585</v>
       </c>
       <c r="CM22">
-        <v>0.2039651411195081</v>
+        <v>0.2069613671617585</v>
       </c>
       <c r="CN22">
-        <v>0.2039651411195081</v>
+        <v>0.2069613671617585</v>
       </c>
       <c r="CO22">
-        <v>0.2039651411195081</v>
+        <v>0.2069613671617585</v>
       </c>
       <c r="CP22">
-        <v>0.2039651411195081</v>
+        <v>0.2069613671617585</v>
       </c>
       <c r="CQ22">
-        <v>0.2039651411195081</v>
+        <v>0.2069613671617585</v>
       </c>
       <c r="CR22">
-        <v>0.2039651411195081</v>
+        <v>0.2069613671617585</v>
       </c>
       <c r="CS22">
-        <v>0.2039651411195081</v>
+        <v>0.2069613671617585</v>
       </c>
     </row>
   </sheetData>
